--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\CPEL_APP_V1\panel-proyectos\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\CPEL_APP_V1\cartera-mixtos\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332CAA9B-56F7-4566-89FE-84C8E5EE6EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43290F2B-0B49-43B5-A8DE-1FF8B7AB184C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="349">
   <si>
     <t>NO.</t>
   </si>
@@ -537,12 +537,6 @@
     <t>El Carmen, Campeche</t>
   </si>
   <si>
-    <t>133 MW</t>
-  </si>
-  <si>
-    <t>40 MW / 120 MWh (POR CONFIRMAR)</t>
-  </si>
-  <si>
     <t>CONCEPCIÓN MENDIZÁBAL MENDOZA FASE I, II &amp; III</t>
   </si>
   <si>
@@ -552,9 +546,6 @@
     <t>Nava, Coahuila</t>
   </si>
   <si>
-    <t>858 MW (POR CONFIRMAR)</t>
-  </si>
-  <si>
     <t>SIN DATO</t>
   </si>
   <si>
@@ -876,15 +867,6 @@
     <t>66.00%</t>
   </si>
   <si>
-    <t>59.00%</t>
-  </si>
-  <si>
-    <t>37.50%</t>
-  </si>
-  <si>
-    <t>15.00%</t>
-  </si>
-  <si>
     <t>33.00%</t>
   </si>
   <si>
@@ -972,12 +954,6 @@
     <t>79.60%</t>
   </si>
   <si>
-    <t>64.75%</t>
-  </si>
-  <si>
-    <t>63.60%</t>
-  </si>
-  <si>
     <t>74.00%</t>
   </si>
   <si>
@@ -1078,6 +1054,36 @@
   </si>
   <si>
     <t>86.30%</t>
+  </si>
+  <si>
+    <t>858 MW</t>
+  </si>
+  <si>
+    <t>257.4 MW / 772.2 MWh</t>
+  </si>
+  <si>
+    <t>125 MW</t>
+  </si>
+  <si>
+    <t>37.5 MW / 112.5 MWh</t>
+  </si>
+  <si>
+    <t>18 de septiembre de 2026</t>
+  </si>
+  <si>
+    <t>18.00%</t>
+  </si>
+  <si>
+    <t>19.40%</t>
+  </si>
+  <si>
+    <t>81.50%</t>
+  </si>
+  <si>
+    <t>69.00%</t>
+  </si>
+  <si>
+    <t>79.00%</t>
   </si>
 </sst>
 </file>
@@ -1554,28 +1560,28 @@
         <v>43</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>18</v>
@@ -1607,28 +1613,28 @@
         <v>49</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>20</v>
@@ -1660,28 +1666,28 @@
         <v>53</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="Q4" s="6" t="s">
         <v>20</v>
@@ -1713,28 +1719,28 @@
         <v>58</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N5" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="P5" s="6" t="s">
         <v>338</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>346</v>
       </c>
       <c r="Q5" s="6" t="s">
         <v>18</v>
@@ -1766,31 +1772,31 @@
         <v>63</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1819,28 +1825,28 @@
         <v>68</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Q7" s="6" t="s">
         <v>20</v>
@@ -1872,28 +1878,28 @@
         <v>72</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Q8" s="6" t="s">
         <v>20</v>
@@ -1925,28 +1931,28 @@
         <v>77</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>20</v>
@@ -1978,28 +1984,28 @@
         <v>81</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>20</v>
@@ -2031,31 +2037,31 @@
         <v>85</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2084,28 +2090,28 @@
         <v>89</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>20</v>
@@ -2137,31 +2143,31 @@
         <v>93</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2190,28 +2196,28 @@
         <v>98</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>280</v>
+        <v>344</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>282</v>
+        <v>345</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>20</v>
@@ -2243,28 +2249,28 @@
         <v>103</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>20</v>
@@ -2296,28 +2302,28 @@
         <v>107</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>20</v>
@@ -2349,28 +2355,28 @@
         <v>110</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>20</v>
@@ -2402,31 +2408,31 @@
         <v>114</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2455,28 +2461,28 @@
         <v>119</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>20</v>
@@ -2508,28 +2514,28 @@
         <v>123</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>20</v>
@@ -2561,28 +2567,28 @@
         <v>123</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>20</v>
@@ -2614,28 +2620,28 @@
         <v>129</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="Q22" s="6" t="s">
         <v>20</v>
@@ -2667,28 +2673,28 @@
         <v>133</v>
       </c>
       <c r="I23" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="L23" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="J23" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>203</v>
-      </c>
       <c r="M23" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="Q23" s="6" t="s">
         <v>18</v>
@@ -2720,28 +2726,28 @@
         <v>136</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="K24" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="K24" s="6" t="s">
-        <v>212</v>
-      </c>
       <c r="L24" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="Q24" s="6" t="s">
         <v>20</v>
@@ -2773,28 +2779,28 @@
         <v>141</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>20</v>
@@ -2826,28 +2832,28 @@
         <v>141</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="Q26" s="6" t="s">
         <v>20</v>
@@ -2879,31 +2885,31 @@
         <v>147</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2932,28 +2938,28 @@
         <v>150</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Q28" s="6" t="s">
         <v>20</v>
@@ -2985,31 +2991,31 @@
         <v>154</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3038,31 +3044,31 @@
         <v>157</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3091,28 +3097,28 @@
         <v>162</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="Q31" s="6" t="s">
         <v>18</v>
@@ -3123,52 +3129,52 @@
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>166</v>
+        <v>339</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>167</v>
+        <v>340</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>227</v>
+        <v>343</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>172</v>
+        <v>265</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>311</v>
+        <v>346</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>279</v>
+        <v>346</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>20</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3176,52 +3182,52 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>171</v>
+        <v>341</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>172</v>
+        <v>342</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>204</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>172</v>
+        <v>224</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>268</v>
+        <v>169</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>20</v>
+        <v>314</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3229,49 +3235,49 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>20</v>
@@ -3282,13 +3288,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>40</v>
@@ -3300,31 +3306,31 @@
         <v>118</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>20</v>
@@ -3341,7 +3347,7 @@
         <v>19</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>40</v>
@@ -3353,31 +3359,31 @@
         <v>118</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>20</v>
@@ -3388,13 +3394,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>40</v>
@@ -3406,31 +3412,31 @@
         <v>118</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>20</v>
@@ -3441,49 +3447,49 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>46</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>20</v>
@@ -3494,10 +3500,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>65</v>
@@ -3509,37 +3515,37 @@
         <v>70</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25"/>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\CPEL_APP_V1\cartera-mixtos\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\CPEL_APP_V2\cartera-mixtos\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43290F2B-0B49-43B5-A8DE-1FF8B7AB184C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879100F6-D0E1-4351-9FDD-14F44C4584E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="350">
   <si>
     <t>NO.</t>
   </si>
@@ -861,9 +861,6 @@
     <t>78.60%</t>
   </si>
   <si>
-    <t>75.50%</t>
-  </si>
-  <si>
     <t>66.00%</t>
   </si>
   <si>
@@ -1084,6 +1081,12 @@
   </si>
   <si>
     <t>79.00%</t>
+  </si>
+  <si>
+    <t>90.50%</t>
+  </si>
+  <si>
+    <t>89.50%</t>
   </si>
 </sst>
 </file>
@@ -1575,13 +1578,13 @@
         <v>235</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>18</v>
@@ -1628,13 +1631,13 @@
         <v>236</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>267</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>20</v>
@@ -1681,13 +1684,13 @@
         <v>237</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O4" s="6" t="s">
         <v>267</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q4" s="6" t="s">
         <v>20</v>
@@ -1734,13 +1737,13 @@
         <v>238</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="O5" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="P5" s="6" t="s">
         <v>337</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>338</v>
       </c>
       <c r="Q5" s="6" t="s">
         <v>18</v>
@@ -1790,13 +1793,13 @@
         <v>268</v>
       </c>
       <c r="O6" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="P6" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="P6" s="6" t="s">
-        <v>325</v>
-      </c>
       <c r="Q6" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1946,13 +1949,13 @@
         <v>242</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>20</v>
@@ -1999,13 +2002,13 @@
         <v>243</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>20</v>
@@ -2052,16 +2055,16 @@
         <v>244</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2105,13 +2108,13 @@
         <v>245</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>20</v>
@@ -2158,16 +2161,16 @@
         <v>246</v>
       </c>
       <c r="N13" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="O13" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="O13" s="6" t="s">
+      <c r="P13" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="P13" s="6" t="s">
-        <v>323</v>
-      </c>
       <c r="Q13" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2211,13 +2214,13 @@
         <v>247</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>20</v>
@@ -2264,13 +2267,13 @@
         <v>248</v>
       </c>
       <c r="N15" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="O15" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="O15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>279</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>20</v>
@@ -2317,13 +2320,13 @@
         <v>249</v>
       </c>
       <c r="N16" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="O16" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="O16" s="6" t="s">
+      <c r="P16" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>282</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>20</v>
@@ -2370,13 +2373,13 @@
         <v>250</v>
       </c>
       <c r="N17" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="O17" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="O17" s="6" t="s">
+      <c r="P17" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="P17" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>20</v>
@@ -2423,16 +2426,16 @@
         <v>251</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>303</v>
+        <v>348</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>274</v>
+        <v>336</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>272</v>
+        <v>349</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2476,13 +2479,13 @@
         <v>252</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O19" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="P19" s="6" t="s">
         <v>286</v>
-      </c>
-      <c r="P19" s="6" t="s">
-        <v>287</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>20</v>
@@ -2529,13 +2532,13 @@
         <v>253</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>269</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>20</v>
@@ -2582,13 +2585,13 @@
         <v>254</v>
       </c>
       <c r="N21" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="O21" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="O21" s="6" t="s">
+      <c r="P21" s="6" t="s">
         <v>291</v>
-      </c>
-      <c r="P21" s="6" t="s">
-        <v>292</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>20</v>
@@ -2635,13 +2638,13 @@
         <v>255</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>267</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q22" s="6" t="s">
         <v>20</v>
@@ -2688,13 +2691,13 @@
         <v>256</v>
       </c>
       <c r="N23" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="O23" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="O23" s="6" t="s">
+      <c r="P23" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="P23" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="Q23" s="6" t="s">
         <v>18</v>
@@ -2741,13 +2744,13 @@
         <v>257</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q24" s="6" t="s">
         <v>20</v>
@@ -2794,13 +2797,13 @@
         <v>258</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>20</v>
@@ -2847,13 +2850,13 @@
         <v>259</v>
       </c>
       <c r="N26" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="O26" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="O26" s="6" t="s">
+      <c r="P26" s="6" t="s">
         <v>300</v>
-      </c>
-      <c r="P26" s="6" t="s">
-        <v>301</v>
       </c>
       <c r="Q26" s="6" t="s">
         <v>20</v>
@@ -2903,13 +2906,13 @@
         <v>272</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3006,16 +3009,16 @@
         <v>262</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>268</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3059,16 +3062,16 @@
         <v>263</v>
       </c>
       <c r="N30" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="O30" s="6" t="s">
+      <c r="P30" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="P30" s="6" t="s">
-        <v>329</v>
-      </c>
       <c r="Q30" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3112,13 +3115,13 @@
         <v>264</v>
       </c>
       <c r="N31" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="O31" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="O31" s="6" t="s">
+      <c r="P31" s="6" t="s">
         <v>331</v>
-      </c>
-      <c r="P31" s="6" t="s">
-        <v>332</v>
       </c>
       <c r="Q31" s="6" t="s">
         <v>18</v>
@@ -3144,10 +3147,10 @@
         <v>168</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>339</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>340</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>189</v>
@@ -3159,22 +3162,22 @@
         <v>202</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>265</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3197,10 +3200,10 @@
         <v>165</v>
       </c>
       <c r="G33" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>341</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>342</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>189</v>
@@ -3218,16 +3221,16 @@
         <v>169</v>
       </c>
       <c r="N33" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="O33" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="O33" s="6" t="s">
+      <c r="P33" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="P33" s="6" t="s">
-        <v>348</v>
-      </c>
       <c r="Q33" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3271,13 +3274,13 @@
         <v>169</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O34" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="P34" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="P34" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>20</v>
@@ -3324,13 +3327,13 @@
         <v>169</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>20</v>
@@ -3377,13 +3380,13 @@
         <v>169</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>20</v>
@@ -3430,13 +3433,13 @@
         <v>169</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>20</v>
@@ -3483,13 +3486,13 @@
         <v>169</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>20</v>
@@ -3545,7 +3548,7 @@
         <v>273</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25"/>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\CPEL_APP_V2\cartera-mixtos\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879100F6-D0E1-4351-9FDD-14F44C4584E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C42DF2C-C8BF-40BA-95D9-F2C20F33E0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2435,7 +2435,7 @@
         <v>349</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>313</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\CPEL_APP_V2\cartera-mixtos\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C42DF2C-C8BF-40BA-95D9-F2C20F33E0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA0B562-9F8D-4205-8051-0F65F128B6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="356">
   <si>
     <t>NO.</t>
   </si>
@@ -894,12 +894,6 @@
     <t>52.80%</t>
   </si>
   <si>
-    <t>60.50%</t>
-  </si>
-  <si>
-    <t>68.10%</t>
-  </si>
-  <si>
     <t>71.50%</t>
   </si>
   <si>
@@ -909,24 +903,12 @@
     <t>72.50%</t>
   </si>
   <si>
-    <t>39.50%</t>
-  </si>
-  <si>
-    <t>65.90%</t>
-  </si>
-  <si>
     <t>69.50%</t>
   </si>
   <si>
-    <t>85.00%</t>
-  </si>
-  <si>
     <t>71.00%</t>
   </si>
   <si>
-    <t>82.20%</t>
-  </si>
-  <si>
     <t>62.00%</t>
   </si>
   <si>
@@ -1087,6 +1069,42 @@
   </si>
   <si>
     <t>89.50%</t>
+  </si>
+  <si>
+    <t>68.50%</t>
+  </si>
+  <si>
+    <t>62.50%</t>
+  </si>
+  <si>
+    <t>67.30%</t>
+  </si>
+  <si>
+    <t>78.80%</t>
+  </si>
+  <si>
+    <t>59.00%</t>
+  </si>
+  <si>
+    <t>67.00%</t>
+  </si>
+  <si>
+    <t>68.80%</t>
+  </si>
+  <si>
+    <t>90.00%</t>
+  </si>
+  <si>
+    <t>89.00%</t>
+  </si>
+  <si>
+    <t>89.80%</t>
+  </si>
+  <si>
+    <t>83.50%</t>
+  </si>
+  <si>
+    <t>SINDATO</t>
   </si>
 </sst>
 </file>
@@ -1106,24 +1124,29 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10.5"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1578,13 +1601,13 @@
         <v>235</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>18</v>
@@ -1631,13 +1654,13 @@
         <v>236</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>267</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>20</v>
@@ -1690,7 +1713,7 @@
         <v>267</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="Q4" s="6" t="s">
         <v>20</v>
@@ -1737,13 +1760,13 @@
         <v>238</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="Q5" s="6" t="s">
         <v>18</v>
@@ -1793,13 +1816,13 @@
         <v>268</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1949,13 +1972,13 @@
         <v>242</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>275</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>20</v>
@@ -2055,16 +2078,16 @@
         <v>244</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2108,13 +2131,13 @@
         <v>245</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>20</v>
@@ -2161,16 +2184,16 @@
         <v>246</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2214,13 +2237,13 @@
         <v>247</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>20</v>
@@ -2426,13 +2449,13 @@
         <v>251</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>18</v>
@@ -2479,13 +2502,13 @@
         <v>252</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>281</v>
+        <v>344</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>286</v>
+        <v>346</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>20</v>
@@ -2532,16 +2555,16 @@
         <v>253</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>287</v>
+        <v>341</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>288</v>
+        <v>347</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>20</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2585,13 +2608,13 @@
         <v>254</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>290</v>
+        <v>348</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>20</v>
@@ -2638,13 +2661,13 @@
         <v>255</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>279</v>
+        <v>340</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>292</v>
+        <v>350</v>
       </c>
       <c r="Q22" s="6" t="s">
         <v>20</v>
@@ -2691,13 +2714,13 @@
         <v>256</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>293</v>
+        <v>351</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>295</v>
+        <v>353</v>
       </c>
       <c r="Q23" s="6" t="s">
         <v>18</v>
@@ -2744,13 +2767,13 @@
         <v>257</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="Q24" s="6" t="s">
         <v>20</v>
@@ -2797,13 +2820,13 @@
         <v>258</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>20</v>
@@ -2850,13 +2873,13 @@
         <v>259</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="Q26" s="6" t="s">
         <v>20</v>
@@ -2906,13 +2929,13 @@
         <v>272</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3009,16 +3032,16 @@
         <v>262</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>268</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3062,16 +3085,16 @@
         <v>263</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3115,13 +3138,13 @@
         <v>264</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="Q31" s="6" t="s">
         <v>18</v>
@@ -3147,10 +3170,10 @@
         <v>168</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>189</v>
@@ -3162,22 +3185,22 @@
         <v>202</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>265</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3200,10 +3223,10 @@
         <v>165</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>189</v>
@@ -3218,19 +3241,19 @@
         <v>224</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>169</v>
+        <v>355</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3271,16 +3294,16 @@
         <v>169</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>169</v>
+        <v>355</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>280</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>20</v>
@@ -3324,7 +3347,7 @@
         <v>169</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>169</v>
+        <v>355</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>277</v>
@@ -3333,7 +3356,7 @@
         <v>270</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>20</v>
@@ -3377,16 +3400,16 @@
         <v>169</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>169</v>
+        <v>355</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>20</v>
@@ -3430,16 +3453,16 @@
         <v>169</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>169</v>
+        <v>355</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>20</v>
@@ -3483,16 +3506,16 @@
         <v>169</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>169</v>
+        <v>355</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>20</v>
@@ -3536,7 +3559,7 @@
         <v>169</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>169</v>
+        <v>355</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>272</v>
@@ -3548,7 +3571,7 @@
         <v>273</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25"/>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -66,7 +66,7 @@
     <t>Horas de Almacenamiento</t>
   </si>
   <si>
-    <t>Inicio de Construcción</t>
+    <t>Inicio de Inversión</t>
   </si>
   <si>
     <t>Fin de Construcción</t>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">   uses el formato de porcentaje de Excel (para evitar que 92 se vuelva 9200%).</t>
   </si>
   <si>
-    <t>• Fechas (Inicio de Construcción, Fin de Construcción, Fecha firma de contrato):</t>
+    <t>• Fechas (Inicio de Inversión, Fin de Construcción, Fecha firma de contrato):</t>
   </si>
   <si>
     <t xml:space="preserve">   escribe el formato AAAA-MM-DD como texto, ej. 2024-03-01. Esas columnas ya</t>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">   están formateadas como texto en esta plantilla — no cambies el formato de celda.</t>
   </si>
   <si>
-    <t>• Grupo de atención: una sola letra, A, B o C.</t>
+    <t>• Grupo de atención: ya no se captura; el sitio lo calcula con Parque (A: 85% o más; B: de 76% a menos de 85%; C: menos de 76%). Esta columna se ignora.</t>
   </si>
   <si>
     <t>Las dos filas de ejemplo (SAN PEDRO SOLAR, SUNORA) son datos de muestra —</t>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA0B562-9F8D-4205-8051-0F65F128B6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF479895-8063-4BA0-9A56-A9E34B541A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="357">
   <si>
     <t>NO.</t>
   </si>
@@ -867,42 +867,24 @@
     <t>33.00%</t>
   </si>
   <si>
-    <t>50.00%</t>
-  </si>
-  <si>
     <t>32.50%</t>
   </si>
   <si>
-    <t>46.50%</t>
-  </si>
-  <si>
     <t>73.00%</t>
   </si>
   <si>
     <t>58.00%</t>
   </si>
   <si>
-    <t>70.00%</t>
-  </si>
-  <si>
     <t>55.00%</t>
   </si>
   <si>
-    <t>44.00%</t>
-  </si>
-  <si>
-    <t>52.80%</t>
-  </si>
-  <si>
     <t>71.50%</t>
   </si>
   <si>
     <t>68.00%</t>
   </si>
   <si>
-    <t>72.50%</t>
-  </si>
-  <si>
     <t>69.50%</t>
   </si>
   <si>
@@ -912,18 +894,6 @@
     <t>62.00%</t>
   </si>
   <si>
-    <t>63.00%</t>
-  </si>
-  <si>
-    <t>61.50%</t>
-  </si>
-  <si>
-    <t>48.00%</t>
-  </si>
-  <si>
-    <t>58.80%</t>
-  </si>
-  <si>
     <t>77.80%</t>
   </si>
   <si>
@@ -1105,6 +1075,39 @@
   </si>
   <si>
     <t>SINDATO</t>
+  </si>
+  <si>
+    <t>28.00%</t>
+  </si>
+  <si>
+    <t>16.00%</t>
+  </si>
+  <si>
+    <t>25.60%</t>
+  </si>
+  <si>
+    <t>50.50%</t>
+  </si>
+  <si>
+    <t>54.50%</t>
+  </si>
+  <si>
+    <t>53.00%</t>
+  </si>
+  <si>
+    <t>54.60%</t>
+  </si>
+  <si>
+    <t>72.00%</t>
+  </si>
+  <si>
+    <t>42.50%</t>
+  </si>
+  <si>
+    <t>66.10%</t>
+  </si>
+  <si>
+    <t>65.60%</t>
   </si>
 </sst>
 </file>
@@ -1601,13 +1604,13 @@
         <v>235</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>18</v>
@@ -1654,13 +1657,13 @@
         <v>236</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>267</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>20</v>
@@ -1707,13 +1710,13 @@
         <v>237</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O4" s="6" t="s">
         <v>267</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Q4" s="6" t="s">
         <v>20</v>
@@ -1760,13 +1763,13 @@
         <v>238</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="Q5" s="6" t="s">
         <v>18</v>
@@ -1816,13 +1819,13 @@
         <v>268</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1972,13 +1975,13 @@
         <v>242</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>275</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>20</v>
@@ -2078,16 +2081,16 @@
         <v>244</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2131,13 +2134,13 @@
         <v>245</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>20</v>
@@ -2184,16 +2187,16 @@
         <v>246</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2237,13 +2240,13 @@
         <v>247</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>20</v>
@@ -2290,13 +2293,13 @@
         <v>248</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>276</v>
+        <v>346</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>277</v>
+        <v>347</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>278</v>
+        <v>348</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>20</v>
@@ -2343,13 +2346,13 @@
         <v>249</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>280</v>
+        <v>349</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>281</v>
+        <v>350</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>20</v>
@@ -2396,13 +2399,13 @@
         <v>250</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>283</v>
+        <v>351</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>284</v>
+        <v>352</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>20</v>
@@ -2449,13 +2452,13 @@
         <v>251</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>18</v>
@@ -2502,13 +2505,13 @@
         <v>252</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>20</v>
@@ -2555,16 +2558,16 @@
         <v>253</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2608,13 +2611,13 @@
         <v>254</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>20</v>
@@ -2661,13 +2664,13 @@
         <v>255</v>
       </c>
       <c r="N22" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="P22" s="6" t="s">
         <v>340</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="P22" s="6" t="s">
-        <v>350</v>
       </c>
       <c r="Q22" s="6" t="s">
         <v>20</v>
@@ -2714,13 +2717,13 @@
         <v>256</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="Q23" s="6" t="s">
         <v>18</v>
@@ -2767,13 +2770,13 @@
         <v>257</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="Q24" s="6" t="s">
         <v>20</v>
@@ -2820,13 +2823,13 @@
         <v>258</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>287</v>
+        <v>353</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>270</v>
+        <v>354</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>291</v>
+        <v>355</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>20</v>
@@ -2873,13 +2876,13 @@
         <v>259</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>294</v>
+        <v>356</v>
       </c>
       <c r="Q26" s="6" t="s">
         <v>20</v>
@@ -2929,13 +2932,13 @@
         <v>272</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3032,16 +3035,16 @@
         <v>262</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>268</v>
       </c>
       <c r="P29" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q29" s="6" t="s">
         <v>297</v>
-      </c>
-      <c r="Q29" s="6" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3085,16 +3088,16 @@
         <v>263</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3138,13 +3141,13 @@
         <v>264</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="Q31" s="6" t="s">
         <v>18</v>
@@ -3170,10 +3173,10 @@
         <v>168</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>189</v>
@@ -3185,22 +3188,22 @@
         <v>202</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>265</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3223,10 +3226,10 @@
         <v>165</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>189</v>
@@ -3241,19 +3244,19 @@
         <v>224</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3294,16 +3297,16 @@
         <v>169</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>20</v>
@@ -3347,16 +3350,16 @@
         <v>169</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>20</v>
@@ -3400,16 +3403,16 @@
         <v>169</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>20</v>
@@ -3453,16 +3456,16 @@
         <v>169</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>20</v>
@@ -3506,16 +3509,16 @@
         <v>169</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>20</v>
@@ -3559,7 +3562,7 @@
         <v>169</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>272</v>
@@ -3571,7 +3574,7 @@
         <v>273</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25"/>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF479895-8063-4BA0-9A56-A9E34B541A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB2936A-20F7-4FB9-8B96-6FE9FF2B758D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="356">
   <si>
     <t>NO.</t>
   </si>
@@ -876,9 +876,6 @@
     <t>58.00%</t>
   </si>
   <si>
-    <t>55.00%</t>
-  </si>
-  <si>
     <t>71.50%</t>
   </si>
   <si>
@@ -1092,12 +1089,6 @@
     <t>54.50%</t>
   </si>
   <si>
-    <t>53.00%</t>
-  </si>
-  <si>
-    <t>54.60%</t>
-  </si>
-  <si>
     <t>72.00%</t>
   </si>
   <si>
@@ -1108,6 +1099,12 @@
   </si>
   <si>
     <t>65.60%</t>
+  </si>
+  <si>
+    <t>52.00%</t>
+  </si>
+  <si>
+    <t>53.60%</t>
   </si>
 </sst>
 </file>
@@ -1604,13 +1601,13 @@
         <v>235</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>18</v>
@@ -1657,13 +1654,13 @@
         <v>236</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>267</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>20</v>
@@ -1716,7 +1713,7 @@
         <v>267</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q4" s="6" t="s">
         <v>20</v>
@@ -1763,13 +1760,13 @@
         <v>238</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O5" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="P5" s="6" t="s">
         <v>320</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>321</v>
       </c>
       <c r="Q5" s="6" t="s">
         <v>18</v>
@@ -1819,13 +1816,13 @@
         <v>268</v>
       </c>
       <c r="O6" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="P6" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="P6" s="6" t="s">
-        <v>308</v>
-      </c>
       <c r="Q6" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1975,13 +1972,13 @@
         <v>242</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>275</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>20</v>
@@ -2081,16 +2078,16 @@
         <v>244</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2134,13 +2131,13 @@
         <v>245</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>20</v>
@@ -2187,16 +2184,16 @@
         <v>246</v>
       </c>
       <c r="N13" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="O13" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="O13" s="6" t="s">
+      <c r="P13" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="P13" s="6" t="s">
-        <v>306</v>
-      </c>
       <c r="Q13" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2240,13 +2237,13 @@
         <v>247</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>20</v>
@@ -2293,13 +2290,13 @@
         <v>248</v>
       </c>
       <c r="N15" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="O15" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="O15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>347</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>348</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>20</v>
@@ -2349,10 +2346,10 @@
         <v>267</v>
       </c>
       <c r="O16" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="P16" s="6" t="s">
         <v>349</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>350</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>20</v>
@@ -2399,13 +2396,13 @@
         <v>250</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>20</v>
@@ -2452,13 +2449,13 @@
         <v>251</v>
       </c>
       <c r="N18" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>332</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>333</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>18</v>
@@ -2505,13 +2502,13 @@
         <v>252</v>
       </c>
       <c r="N19" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="O19" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="O19" s="6" t="s">
+      <c r="P19" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="P19" s="6" t="s">
-        <v>336</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>20</v>
@@ -2558,16 +2555,16 @@
         <v>253</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2611,13 +2608,13 @@
         <v>254</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="O21" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="P21" s="6" t="s">
         <v>338</v>
-      </c>
-      <c r="P21" s="6" t="s">
-        <v>339</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>20</v>
@@ -2664,13 +2661,13 @@
         <v>255</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q22" s="6" t="s">
         <v>20</v>
@@ -2717,13 +2714,13 @@
         <v>256</v>
       </c>
       <c r="N23" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="O23" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="O23" s="6" t="s">
+      <c r="P23" s="6" t="s">
         <v>342</v>
-      </c>
-      <c r="P23" s="6" t="s">
-        <v>343</v>
       </c>
       <c r="Q23" s="6" t="s">
         <v>18</v>
@@ -2770,13 +2767,13 @@
         <v>257</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q24" s="6" t="s">
         <v>20</v>
@@ -2823,13 +2820,13 @@
         <v>258</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>20</v>
@@ -2876,13 +2873,13 @@
         <v>259</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>269</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="Q26" s="6" t="s">
         <v>20</v>
@@ -2932,13 +2929,13 @@
         <v>272</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3035,16 +3032,16 @@
         <v>262</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>268</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3088,16 +3085,16 @@
         <v>263</v>
       </c>
       <c r="N30" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="O30" s="6" t="s">
+      <c r="P30" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="P30" s="6" t="s">
-        <v>312</v>
-      </c>
       <c r="Q30" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3141,13 +3138,13 @@
         <v>264</v>
       </c>
       <c r="N31" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="O31" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="O31" s="6" t="s">
+      <c r="P31" s="6" t="s">
         <v>314</v>
-      </c>
-      <c r="P31" s="6" t="s">
-        <v>315</v>
       </c>
       <c r="Q31" s="6" t="s">
         <v>18</v>
@@ -3173,10 +3170,10 @@
         <v>168</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>322</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>323</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>189</v>
@@ -3188,22 +3185,22 @@
         <v>202</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>265</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3226,10 +3223,10 @@
         <v>165</v>
       </c>
       <c r="G33" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>324</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>325</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>189</v>
@@ -3244,19 +3241,19 @@
         <v>224</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N33" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="O33" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="O33" s="6" t="s">
+      <c r="P33" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="P33" s="6" t="s">
-        <v>331</v>
-      </c>
       <c r="Q33" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3297,16 +3294,16 @@
         <v>169</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>278</v>
       </c>
       <c r="O34" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="P34" s="6" t="s">
         <v>289</v>
-      </c>
-      <c r="P34" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>20</v>
@@ -3350,7 +3347,7 @@
         <v>169</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>276</v>
@@ -3359,7 +3356,7 @@
         <v>270</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>20</v>
@@ -3403,16 +3400,16 @@
         <v>169</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>20</v>
@@ -3456,16 +3453,16 @@
         <v>169</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>20</v>
@@ -3509,16 +3506,16 @@
         <v>169</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>20</v>
@@ -3562,7 +3559,7 @@
         <v>169</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>272</v>
@@ -3574,7 +3571,7 @@
         <v>273</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25"/>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="366">
   <si>
     <t>NO.</t>
   </si>
@@ -1105,6 +1105,36 @@
   </si>
   <si>
     <t>53.60%</t>
+  </si>
+  <si>
+    <t>CONCEPCIÓN MENDIZÁBAL MENDOZA FASE I</t>
+  </si>
+  <si>
+    <t>339 MW</t>
+  </si>
+  <si>
+    <t>101.7 MW / 305.1 MWh</t>
+  </si>
+  <si>
+    <t>$381,545,675.00</t>
+  </si>
+  <si>
+    <t>CONCEPCIÓN MENDIZÁBAL MENDOZA FASE II</t>
+  </si>
+  <si>
+    <t>180 MW</t>
+  </si>
+  <si>
+    <t>54 MW / 162 MWh</t>
+  </si>
+  <si>
+    <t>$198,977,154.00</t>
+  </si>
+  <si>
+    <t>CONCEPCIÓN MENDIZÁBAL MENDOZA FASE III</t>
+  </si>
+  <si>
+    <t>$376,737,492.00</t>
   </si>
 </sst>
 </file>
@@ -1486,7 +1516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
@@ -3155,10 +3185,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>166</v>
+        <v>356</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>166</v>
+        <v>356</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>167</v>
@@ -3170,10 +3200,10 @@
         <v>168</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>189</v>
@@ -3188,16 +3218,16 @@
         <v>325</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>265</v>
+        <v>359</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="Q32" s="6" t="s">
         <v>296</v>
@@ -3208,49 +3238,49 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>163</v>
+        <v>360</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>163</v>
+        <v>360</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>189</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>224</v>
+        <v>325</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>328</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="Q33" s="6" t="s">
         <v>296</v>
@@ -3261,52 +3291,52 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>170</v>
+        <v>364</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>170</v>
+        <v>364</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>173</v>
+        <v>357</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>174</v>
+        <v>358</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>169</v>
+        <v>325</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>20</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3314,52 +3344,52 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>118</v>
+        <v>323</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>177</v>
+        <v>324</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>344</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>270</v>
+        <v>329</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>20</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3367,34 +3397,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>40</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>187</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>169</v>
@@ -3403,13 +3433,13 @@
         <v>344</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>20</v>
@@ -3420,10 +3450,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>176</v>
@@ -3456,13 +3486,13 @@
         <v>344</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>20</v>
@@ -3473,34 +3503,34 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>187</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="L38" s="6" t="s">
         <v>169</v>
@@ -3509,13 +3539,13 @@
         <v>344</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>20</v>
@@ -3526,34 +3556,34 @@
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>65</v>
+        <v>176</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="I39" s="6" t="s">
         <v>187</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="L39" s="6" t="s">
         <v>169</v>
@@ -3562,22 +3592,128 @@
         <v>344</v>
       </c>
       <c r="N39" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q39" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q40" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="N41" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="O39" s="6" t="s">
+      <c r="O41" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="P39" s="6" t="s">
+      <c r="P41" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="Q39" s="6" t="s">
+      <c r="Q41" s="6" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:Q1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q39">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q41">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="367">
   <si>
     <t>NO.</t>
   </si>
@@ -1135,6 +1135,9 @@
   </si>
   <si>
     <t>$376,737,492.00</t>
+  </si>
+  <si>
+    <t>82.50%</t>
   </si>
 </sst>
 </file>
@@ -3221,13 +3224,13 @@
         <v>359</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="Q32" s="6" t="s">
         <v>296</v>
@@ -3274,13 +3277,13 @@
         <v>363</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="Q33" s="6" t="s">
         <v>296</v>
@@ -3327,13 +3330,13 @@
         <v>365</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>285</v>
+        <v>366</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>285</v>
+        <v>366</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>285</v>
+        <v>366</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>296</v>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -567,7 +567,7 @@
     <t>CIMARRÓN SOLAR</t>
   </si>
   <si>
-    <t>CFQB Energy</t>
+    <t>CSQB Energy</t>
   </si>
   <si>
     <t>90 MW / 270 MWh (POR CONFIRMAR)</t>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hamed Ivan Huerta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB2936A-20F7-4FB9-8B96-6FE9FF2B758D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077716F2-1B15-436D-A0DD-239821F9A68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="1" r:id="rId1"/>
     <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyectos!$A$1:$Q$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyectos!$A$1:$P$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="360">
   <si>
     <t>NO.</t>
   </si>
@@ -87,21 +87,12 @@
     <t>Global</t>
   </si>
   <si>
-    <t>Grupo de atención</t>
-  </si>
-  <si>
     <t>SAN PEDRO SOLAR</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>SUNORA</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>Cómo editar este archivo</t>
   </si>
   <si>
@@ -537,9 +528,6 @@
     <t>El Carmen, Campeche</t>
   </si>
   <si>
-    <t>CONCEPCIÓN MENDIZÁBAL MENDOZA FASE I, II &amp; III</t>
-  </si>
-  <si>
     <t>Atlas Renewable Energy</t>
   </si>
   <si>
@@ -834,9 +822,6 @@
     <t>$147,073,578.90</t>
   </si>
   <si>
-    <t>$925,310,833.00</t>
-  </si>
-  <si>
     <t>75.00%</t>
   </si>
   <si>
@@ -909,27 +894,12 @@
     <t>55.40%</t>
   </si>
   <si>
-    <t>31.00%</t>
-  </si>
-  <si>
-    <t>49.50%</t>
-  </si>
-  <si>
-    <t>44.60%</t>
-  </si>
-  <si>
     <t>57.50%</t>
   </si>
   <si>
-    <t>51.00%</t>
-  </si>
-  <si>
     <t>10.00%</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>94.00%</t>
   </si>
   <si>
@@ -1002,12 +972,6 @@
     <t>86.30%</t>
   </si>
   <si>
-    <t>858 MW</t>
-  </si>
-  <si>
-    <t>257.4 MW / 772.2 MWh</t>
-  </si>
-  <si>
     <t>125 MW</t>
   </si>
   <si>
@@ -1138,6 +1102,21 @@
   </si>
   <si>
     <t>82.50%</t>
+  </si>
+  <si>
+    <t>35.00%</t>
+  </si>
+  <si>
+    <t>34.50%</t>
+  </si>
+  <si>
+    <t>41.00%</t>
+  </si>
+  <si>
+    <t>38.50%</t>
+  </si>
+  <si>
+    <t>40.50%</t>
   </si>
 </sst>
 </file>
@@ -1519,28 +1498,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="47.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="47.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1589,2134 +1567,2011 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="I4" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q4" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="I5" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="I6" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>68</v>
-      </c>
       <c r="I7" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q7" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>72</v>
-      </c>
       <c r="I8" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="I9" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q9" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>81</v>
-      </c>
       <c r="I10" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>85</v>
-      </c>
       <c r="I11" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>89</v>
-      </c>
       <c r="I12" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q12" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>93</v>
-      </c>
       <c r="I13" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="J13" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>200</v>
-      </c>
       <c r="M13" s="6" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>98</v>
-      </c>
       <c r="I14" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q14" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="H15" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="I15" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="I16" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q16" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="Q17" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>114</v>
-      </c>
       <c r="I18" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q18" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="I19" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q19" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="I20" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q20" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="Q21" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="I22" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="Q22" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H23" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>133</v>
-      </c>
       <c r="I23" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="Q23" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="Q24" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D25" s="6" t="s">
+      <c r="H25" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="I25" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="Q25" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D26" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="I26" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="Q26" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="H27" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>147</v>
-      </c>
       <c r="I27" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q27" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q28" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H29" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>154</v>
-      </c>
       <c r="I29" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q29" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q30" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="D31" s="6" t="s">
+      <c r="H31" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>162</v>
-      </c>
       <c r="I31" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="Q31" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="Q32" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="Q33" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="Q34" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="Q35" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>174</v>
-      </c>
       <c r="I36" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q36" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q37" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>291</v>
+        <v>355</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q38" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>293</v>
+        <v>357</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>270</v>
+        <v>358</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q39" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="H40" s="6" t="s">
+      <c r="I40" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="I40" s="6" t="s">
-        <v>187</v>
-      </c>
       <c r="J40" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q40" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q41" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A1:Q1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q41">
+  <autoFilter ref="A1:P1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P41">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
@@ -3727,103 +3582,103 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hamed Ivan Huerta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077716F2-1B15-436D-A0DD-239821F9A68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2830BA5-6E04-497D-BE6B-7C5D345F2F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="362">
   <si>
     <t>NO.</t>
   </si>
@@ -858,9 +858,6 @@
     <t>73.00%</t>
   </si>
   <si>
-    <t>58.00%</t>
-  </si>
-  <si>
     <t>71.50%</t>
   </si>
   <si>
@@ -888,12 +885,6 @@
     <t>74.00%</t>
   </si>
   <si>
-    <t>45.00%</t>
-  </si>
-  <si>
-    <t>55.40%</t>
-  </si>
-  <si>
     <t>57.50%</t>
   </si>
   <si>
@@ -1117,6 +1108,21 @@
   </si>
   <si>
     <t>40.50%</t>
+  </si>
+  <si>
+    <t>46.00%</t>
+  </si>
+  <si>
+    <t>23.00%</t>
+  </si>
+  <si>
+    <t>41.40%</t>
+  </si>
+  <si>
+    <t>13.00%</t>
+  </si>
+  <si>
+    <t>12.40%</t>
   </si>
 </sst>
 </file>
@@ -1609,13 +1615,13 @@
         <v>231</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1659,13 +1665,13 @@
         <v>232</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>262</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1715,7 +1721,7 @@
         <v>262</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1759,13 +1765,13 @@
         <v>234</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1812,10 +1818,10 @@
         <v>263</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1959,13 +1965,13 @@
         <v>238</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2059,13 +2065,13 @@
         <v>240</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2109,13 +2115,13 @@
         <v>241</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2159,13 +2165,13 @@
         <v>242</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2209,13 +2215,13 @@
         <v>243</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>265</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2259,13 +2265,13 @@
         <v>244</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2312,10 +2318,10 @@
         <v>262</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2362,10 +2368,10 @@
         <v>264</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2409,13 +2415,13 @@
         <v>247</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2459,13 +2465,13 @@
         <v>248</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2509,13 +2515,13 @@
         <v>249</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2559,13 +2565,13 @@
         <v>250</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="22" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2609,13 +2615,13 @@
         <v>251</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2659,13 +2665,13 @@
         <v>252</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="24" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2709,13 +2715,13 @@
         <v>253</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2759,13 +2765,13 @@
         <v>254</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2809,13 +2815,13 @@
         <v>255</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>264</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="27" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2862,10 +2868,10 @@
         <v>267</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2959,13 +2965,13 @@
         <v>258</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>263</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3009,13 +3015,13 @@
         <v>259</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="31" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3059,13 +3065,13 @@
         <v>260</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3073,10 +3079,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>163</v>
@@ -3088,10 +3094,10 @@
         <v>164</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>185</v>
@@ -3103,19 +3109,19 @@
         <v>198</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="33" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3123,10 +3129,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>163</v>
@@ -3138,10 +3144,10 @@
         <v>164</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>185</v>
@@ -3153,19 +3159,19 @@
         <v>198</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="34" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3173,10 +3179,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>163</v>
@@ -3188,10 +3194,10 @@
         <v>164</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>185</v>
@@ -3203,19 +3209,19 @@
         <v>198</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="35" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3238,10 +3244,10 @@
         <v>162</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>185</v>
@@ -3256,16 +3262,16 @@
         <v>220</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="36" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3306,16 +3312,16 @@
         <v>165</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>273</v>
+        <v>357</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>283</v>
+        <v>358</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>284</v>
+        <v>359</v>
       </c>
     </row>
     <row r="37" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3356,16 +3362,16 @@
         <v>165</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>271</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="38" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3406,16 +3412,16 @@
         <v>165</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>271</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="39" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3456,16 +3462,16 @@
         <v>165</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="40" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3506,16 +3512,16 @@
         <v>165</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>286</v>
+        <v>360</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>286</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3556,7 +3562,7 @@
         <v>165</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>267</v>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -567,7 +567,7 @@
     <t>SIERRA MADRE [EL CHORRO] (2DA RONDA)</t>
   </si>
   <si>
-    <t>Terralia</t>
+    <t>Enhol &amp; GEMEX</t>
   </si>
   <si>
     <t>Villa de Casas y Güemes, Tamaulipas</t>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hamed Ivan Huerta\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2830BA5-6E04-497D-BE6B-7C5D345F2F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FF66A1-8D24-418A-BCE9-92CDB994293D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="361">
   <si>
     <t>NO.</t>
   </si>
@@ -567,9 +567,6 @@
     <t>SIERRA MADRE [EL CHORRO] (2DA RONDA)</t>
   </si>
   <si>
-    <t>Enhol &amp; GEMEX</t>
-  </si>
-  <si>
     <t>Villa de Casas y Güemes, Tamaulipas</t>
   </si>
   <si>
@@ -585,9 +582,6 @@
     <t>117 MW (POR CONFIRMAR)</t>
   </si>
   <si>
-    <t>35.1 MW / 105.2 MWh (POR CONFIRMAR)</t>
-  </si>
-  <si>
     <t>3.00 (POR CONFIRMAR)</t>
   </si>
   <si>
@@ -600,9 +594,6 @@
     <t>4.00</t>
   </si>
   <si>
-    <t>3.26</t>
-  </si>
-  <si>
     <t>3.18</t>
   </si>
   <si>
@@ -729,9 +720,6 @@
     <t>01 de enero de 2028</t>
   </si>
   <si>
-    <t>01 de enero de 2030</t>
-  </si>
-  <si>
     <t>$93,931,093.40</t>
   </si>
   <si>
@@ -822,9 +810,6 @@
     <t>$147,073,578.90</t>
   </si>
   <si>
-    <t>75.00%</t>
-  </si>
-  <si>
     <t>55.50%</t>
   </si>
   <si>
@@ -837,15 +822,6 @@
     <t>25.00%</t>
   </si>
   <si>
-    <t>48.20%</t>
-  </si>
-  <si>
-    <t>79.50%</t>
-  </si>
-  <si>
-    <t>78.60%</t>
-  </si>
-  <si>
     <t>66.00%</t>
   </si>
   <si>
@@ -867,21 +843,9 @@
     <t>69.50%</t>
   </si>
   <si>
-    <t>71.00%</t>
-  </si>
-  <si>
     <t>62.00%</t>
   </si>
   <si>
-    <t>77.80%</t>
-  </si>
-  <si>
-    <t>80.50%</t>
-  </si>
-  <si>
-    <t>79.60%</t>
-  </si>
-  <si>
     <t>74.00%</t>
   </si>
   <si>
@@ -1026,9 +990,6 @@
     <t>83.50%</t>
   </si>
   <si>
-    <t>SINDATO</t>
-  </si>
-  <si>
     <t>28.00%</t>
   </si>
   <si>
@@ -1123,13 +1084,49 @@
   </si>
   <si>
     <t>12.40%</t>
+  </si>
+  <si>
+    <t>Enhol &amp; GEMEX [Terralia]</t>
+  </si>
+  <si>
+    <t>35.1 MW / 105.3 MWh (POR CONFIRMAR)</t>
+  </si>
+  <si>
+    <t>$161,106,071.70</t>
+  </si>
+  <si>
+    <t>61.50%</t>
+  </si>
+  <si>
+    <t>54.20%</t>
+  </si>
+  <si>
+    <t>86.00%</t>
+  </si>
+  <si>
+    <t>85.00%</t>
+  </si>
+  <si>
+    <t>85.80%</t>
+  </si>
+  <si>
+    <t>26.00%</t>
+  </si>
+  <si>
+    <t>52.40%</t>
+  </si>
+  <si>
+    <t>82.00%</t>
+  </si>
+  <si>
+    <t>87.50%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1166,6 +1163,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1189,10 +1193,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1202,9 +1207,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{BC78EB9C-0B95-49BA-A215-19B72E1CCE9C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1504,27 +1511,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="47.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="37.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1574,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1600,31 +1608,32 @@
         <v>40</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+      <c r="Q2" s="7"/>
+    </row>
+    <row r="3" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1650,31 +1659,31 @@
         <v>46</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1700,31 +1709,31 @@
         <v>50</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1750,31 +1759,31 @@
         <v>55</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1800,31 +1809,31 @@
         <v>60</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1850,31 +1859,31 @@
         <v>65</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>264</v>
+        <v>352</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1900,31 +1909,31 @@
         <v>69</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>264</v>
+        <v>352</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1950,31 +1959,31 @@
         <v>74</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2000,31 +2009,31 @@
         <v>78</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2050,31 +2059,31 @@
         <v>82</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2100,31 +2109,31 @@
         <v>86</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2150,31 +2159,31 @@
         <v>90</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -2200,31 +2209,31 @@
         <v>95</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2250,31 +2259,31 @@
         <v>100</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2300,31 +2309,31 @@
         <v>104</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2350,31 +2359,31 @@
         <v>107</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2400,31 +2409,31 @@
         <v>111</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2450,31 +2459,31 @@
         <v>116</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2500,31 +2509,31 @@
         <v>120</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2550,31 +2559,31 @@
         <v>120</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2600,31 +2609,31 @@
         <v>126</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2650,31 +2659,31 @@
         <v>130</v>
       </c>
       <c r="I23" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="L23" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="J23" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>196</v>
-      </c>
       <c r="M23" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2700,31 +2709,31 @@
         <v>133</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="K24" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="K24" s="6" t="s">
-        <v>205</v>
-      </c>
       <c r="L24" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2750,31 +2759,31 @@
         <v>138</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2800,31 +2809,31 @@
         <v>138</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2850,31 +2859,31 @@
         <v>144</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>267</v>
+        <v>354</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2900,31 +2909,31 @@
         <v>147</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>265</v>
+        <v>357</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2950,31 +2959,31 @@
         <v>151</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>279</v>
+        <v>359</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>263</v>
+        <v>359</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -3000,31 +3009,31 @@
         <v>154</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -3050,39 +3059,39 @@
         <v>159</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>163</v>
@@ -3094,45 +3103,45 @@
         <v>164</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>163</v>
@@ -3144,45 +3153,45 @@
         <v>164</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>163</v>
@@ -3194,37 +3203,37 @@
         <v>164</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -3244,37 +3253,37 @@
         <v>162</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -3300,31 +3309,31 @@
         <v>170</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>165</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>329</v>
+        <v>165</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -3350,31 +3359,31 @@
         <v>173</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L37" s="6" t="s">
         <v>165</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>329</v>
+        <v>165</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -3400,31 +3409,31 @@
         <v>173</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L38" s="6" t="s">
         <v>165</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>329</v>
+        <v>165</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -3450,31 +3459,31 @@
         <v>173</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L39" s="6" t="s">
         <v>165</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>329</v>
+        <v>165</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -3485,54 +3494,54 @@
         <v>175</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>176</v>
+        <v>349</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F40" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="H40" s="6" t="s">
-        <v>179</v>
-      </c>
       <c r="I40" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>230</v>
+        <v>165</v>
       </c>
       <c r="L40" s="6" t="s">
         <v>165</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>329</v>
+        <v>165</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>62</v>
@@ -3544,37 +3553,37 @@
         <v>67</v>
       </c>
       <c r="G41" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="I41" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>183</v>
-      </c>
       <c r="J41" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="L41" s="6" t="s">
         <v>165</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>329</v>
+        <v>165</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>267</v>
+        <v>360</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>261</v>
+        <v>360</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:P1" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P41">
@@ -3588,101 +3597,101 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>34</v>
       </c>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="365">
   <si>
     <t>NO.</t>
   </si>
@@ -1120,6 +1120,18 @@
   </si>
   <si>
     <t>82.75%</t>
+  </si>
+  <si>
+    <t>PRIORI</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>NoP</t>
+  </si>
+  <si>
+    <t>• PRIORI: escribe "P" si el proyecto es prioritario (aparece en el ranking del Resumen y su tarjeta se distingue) o "NoP" si no lo es.</t>
   </si>
 </sst>
 </file>
@@ -1582,6 +1594,9 @@
       <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="6" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="2" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -1632,7 +1647,9 @@
       <c r="P2" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="Q2"/>
+      <c r="Q2" s="1" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="3" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
@@ -1683,6 +1700,9 @@
       <c r="P3" s="1" t="s">
         <v>276</v>
       </c>
+      <c r="Q3" s="1" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="4" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1733,6 +1753,9 @@
       <c r="P4" s="5" t="s">
         <v>267</v>
       </c>
+      <c r="Q4" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1783,6 +1806,9 @@
       <c r="P5" s="5" t="s">
         <v>295</v>
       </c>
+      <c r="Q5" s="5" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1833,6 +1859,9 @@
       <c r="P6" s="5" t="s">
         <v>282</v>
       </c>
+      <c r="Q6" s="5" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1883,6 +1912,9 @@
       <c r="P7" s="5" t="s">
         <v>351</v>
       </c>
+      <c r="Q7" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1933,6 +1965,9 @@
       <c r="P8" s="5" t="s">
         <v>351</v>
       </c>
+      <c r="Q8" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1983,6 +2018,9 @@
       <c r="P9" s="5" t="s">
         <v>293</v>
       </c>
+      <c r="Q9" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2033,6 +2071,9 @@
       <c r="P10" s="5" t="s">
         <v>261</v>
       </c>
+      <c r="Q10" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2083,6 +2124,9 @@
       <c r="P11" s="5" t="s">
         <v>292</v>
       </c>
+      <c r="Q11" s="5" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2133,6 +2177,9 @@
       <c r="P12" s="5" t="s">
         <v>277</v>
       </c>
+      <c r="Q12" s="5" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2183,6 +2230,9 @@
       <c r="P13" s="5" t="s">
         <v>280</v>
       </c>
+      <c r="Q13" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2233,6 +2283,9 @@
       <c r="P14" s="5" t="s">
         <v>300</v>
       </c>
+      <c r="Q14" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2283,6 +2336,9 @@
       <c r="P15" s="5" t="s">
         <v>318</v>
       </c>
+      <c r="Q15" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -2333,6 +2389,9 @@
       <c r="P16" s="5" t="s">
         <v>320</v>
       </c>
+      <c r="Q16" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="17" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -2383,6 +2442,9 @@
       <c r="P17" s="5" t="s">
         <v>326</v>
       </c>
+      <c r="Q17" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="18" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -2433,6 +2495,9 @@
       <c r="P18" s="5" t="s">
         <v>305</v>
       </c>
+      <c r="Q18" s="5" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="19" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -2483,6 +2548,9 @@
       <c r="P19" s="5" t="s">
         <v>308</v>
       </c>
+      <c r="Q19" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="20" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -2533,6 +2601,9 @@
       <c r="P20" s="5" t="s">
         <v>309</v>
       </c>
+      <c r="Q20" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="21" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -2583,6 +2654,9 @@
       <c r="P21" s="5" t="s">
         <v>311</v>
       </c>
+      <c r="Q21" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="22" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -2633,6 +2707,9 @@
       <c r="P22" s="5" t="s">
         <v>312</v>
       </c>
+      <c r="Q22" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="23" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -2683,6 +2760,9 @@
       <c r="P23" s="5" t="s">
         <v>315</v>
       </c>
+      <c r="Q23" s="5" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="24" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -2733,6 +2813,9 @@
       <c r="P24" s="5" t="s">
         <v>283</v>
       </c>
+      <c r="Q24" s="5" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="25" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -2783,6 +2866,9 @@
       <c r="P25" s="5" t="s">
         <v>323</v>
       </c>
+      <c r="Q25" s="5" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="26" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -2833,6 +2919,9 @@
       <c r="P26" s="5" t="s">
         <v>324</v>
       </c>
+      <c r="Q26" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="27" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -2883,6 +2972,9 @@
       <c r="P27" s="5" t="s">
         <v>354</v>
       </c>
+      <c r="Q27" s="5" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="28" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
@@ -2933,6 +3025,9 @@
       <c r="P28" s="5" t="s">
         <v>356</v>
       </c>
+      <c r="Q28" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="29" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
@@ -2983,6 +3078,9 @@
       <c r="P29" s="5" t="s">
         <v>357</v>
       </c>
+      <c r="Q29" s="5" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="30" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
@@ -3033,6 +3131,9 @@
       <c r="P30" s="5" t="s">
         <v>286</v>
       </c>
+      <c r="Q30" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="31" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -3083,6 +3184,9 @@
       <c r="P31" s="5" t="s">
         <v>289</v>
       </c>
+      <c r="Q31" s="5" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="32" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
@@ -3133,6 +3237,9 @@
       <c r="P32" s="5" t="s">
         <v>359</v>
       </c>
+      <c r="Q32" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="33" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
@@ -3183,6 +3290,9 @@
       <c r="P33" s="5" t="s">
         <v>359</v>
       </c>
+      <c r="Q33" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="34" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
@@ -3233,6 +3343,9 @@
       <c r="P34" s="5" t="s">
         <v>360</v>
       </c>
+      <c r="Q34" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="35" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
@@ -3283,6 +3396,9 @@
       <c r="P35" s="5" t="s">
         <v>303</v>
       </c>
+      <c r="Q35" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="36" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
@@ -3333,6 +3449,9 @@
       <c r="P36" s="5" t="s">
         <v>344</v>
       </c>
+      <c r="Q36" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="37" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
@@ -3383,6 +3502,9 @@
       <c r="P37" s="5" t="s">
         <v>338</v>
       </c>
+      <c r="Q37" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="38" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -3433,6 +3555,9 @@
       <c r="P38" s="5" t="s">
         <v>338</v>
       </c>
+      <c r="Q38" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="39" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -3483,6 +3608,9 @@
       <c r="P39" s="5" t="s">
         <v>341</v>
       </c>
+      <c r="Q39" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="40" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
@@ -3533,6 +3661,9 @@
       <c r="P40" s="5" t="s">
         <v>346</v>
       </c>
+      <c r="Q40" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="41" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
@@ -3583,11 +3714,14 @@
       <c r="P41" s="5" t="s">
         <v>358</v>
       </c>
+      <c r="Q41" s="5" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="42" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:P1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P41">
+  <autoFilter ref="A1:Q1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q41">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
@@ -3597,7 +3731,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -3685,15 +3819,20 @@
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="A19" s="3"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>34</v>
       </c>
     </row>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marti\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB721C9-0522-4B2C-9FE3-FA1DD0B1EF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B851F56-2D30-4367-AED9-E55BAEBBBB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="21806" windowHeight="13886" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="1" r:id="rId1"/>
     <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyectos!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyectos!$A$1:$R$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="424">
   <si>
     <t>NO.</t>
   </si>
@@ -1132,6 +1132,183 @@
   </si>
   <si>
     <t>• PRIORI: escribe "P" si el proyecto es prioritario (aparece en el ranking del Resumen y su tarjeta se distingue) o "NoP" si no lo es.</t>
+  </si>
+  <si>
+    <t>name_BD</t>
+  </si>
+  <si>
+    <t>La Noria</t>
+  </si>
+  <si>
+    <t>PV Moquel Solar</t>
+  </si>
+  <si>
+    <t>PV Sandom Solar</t>
+  </si>
+  <si>
+    <t>Viento de Bella Unión</t>
+  </si>
+  <si>
+    <t>San Simón Solar</t>
+  </si>
+  <si>
+    <t>Solitario</t>
+  </si>
+  <si>
+    <t>Álvaro Obregón</t>
+  </si>
+  <si>
+    <t>Santa Gertrudis</t>
+  </si>
+  <si>
+    <t>El Guajillo</t>
+  </si>
+  <si>
+    <t>Tres Hermanos</t>
+  </si>
+  <si>
+    <t>Los Girasoles</t>
+  </si>
+  <si>
+    <t>Don Humberto</t>
+  </si>
+  <si>
+    <t>Haab Kiin</t>
+  </si>
+  <si>
+    <t>Planta Solar Cerro Colorado</t>
+  </si>
+  <si>
+    <t>CFV Quasara</t>
+  </si>
+  <si>
+    <t>Tikinmul</t>
+  </si>
+  <si>
+    <t>El Palmar</t>
+  </si>
+  <si>
+    <t>La Pasión</t>
+  </si>
+  <si>
+    <t>San Pedro Solar</t>
+  </si>
+  <si>
+    <t>Energía Limpia el Mezquite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energías Renovables De México Tres (Hecelchakan) </t>
+  </si>
+  <si>
+    <t>Energías Renovables Saas (Peto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energías Renovables Kiin (Tekax) </t>
+  </si>
+  <si>
+    <t>Energías Renovables de Tamaulipas (Altamira)</t>
+  </si>
+  <si>
+    <t>Dalia 3 (Castamay)</t>
+  </si>
+  <si>
+    <t>Fresnillo (PV Atocha)</t>
+  </si>
+  <si>
+    <t>Los Molinos</t>
+  </si>
+  <si>
+    <t>Montecristo</t>
+  </si>
+  <si>
+    <t>Sol de Sonora 70</t>
+  </si>
+  <si>
+    <t>Selka Power Plant 1</t>
+  </si>
+  <si>
+    <t>Concepción Mendizábal M. - Fase I</t>
+  </si>
+  <si>
+    <t>Concepción Mendizábal M. - Fase II</t>
+  </si>
+  <si>
+    <t>Concepción Mendizábal M. - Fase III</t>
+  </si>
+  <si>
+    <t>Global Solar 3 Campeche</t>
+  </si>
+  <si>
+    <t>CFV Las Garzas (**)</t>
+  </si>
+  <si>
+    <t>Cimarrón Solar (**)</t>
+  </si>
+  <si>
+    <t>Sunora (**)</t>
+  </si>
+  <si>
+    <t>La Poza Solar (**)</t>
+  </si>
+  <si>
+    <t>Sierra Madre (El Chorro) (*)</t>
+  </si>
+  <si>
+    <t>Delaro (*)</t>
+  </si>
+  <si>
+    <t>DI_LT</t>
+  </si>
+  <si>
+    <t>DI_P</t>
+  </si>
+  <si>
+    <t>ES_INT</t>
+  </si>
+  <si>
+    <t>A_MIA_P</t>
+  </si>
+  <si>
+    <t>A_MIA_LT</t>
+  </si>
+  <si>
+    <t>A_ETJ_LT</t>
+  </si>
+  <si>
+    <t>A_ETJ_P</t>
+  </si>
+  <si>
+    <t>S_MISSE_C</t>
+  </si>
+  <si>
+    <t>S_MISSE_LT</t>
+  </si>
+  <si>
+    <t>S_CONS</t>
+  </si>
+  <si>
+    <t>INAH_C</t>
+  </si>
+  <si>
+    <t>INAH_LT</t>
+  </si>
+  <si>
+    <t>PEMEX_C</t>
+  </si>
+  <si>
+    <t>PEMEX_LT</t>
+  </si>
+  <si>
+    <t>CONA_C</t>
+  </si>
+  <si>
+    <t>CONA_LT</t>
+  </si>
+  <si>
+    <t>AFAC_C</t>
+  </si>
+  <si>
+    <t>AFAC_LT</t>
   </si>
 </sst>
 </file>
@@ -1205,12 +1382,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1220,10 +1398,14 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{BC78EB9C-0B95-49BA-A215-19B72E1CCE9C}"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Porcentaje 2" xfId="2" xr:uid="{CA71FA13-44C4-4E1C-91BB-9480ABF23869}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1524,28 +1706,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BM42"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="47.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="47.84375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.53515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.69140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.69140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.15234375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.53515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.69140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.84375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.3828125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.69140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.3046875" customWidth="1"/>
+    <col min="22" max="26" width="12.4609375" customWidth="1"/>
+    <col min="27" max="27" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="28" max="36" width="12.4609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" ht="28.3" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1597,8 +1783,94 @@
       <c r="Q1" s="6" t="s">
         <v>361</v>
       </c>
+      <c r="R1" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="AE1" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="AG1" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="AH1" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="AI1" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="AJ1" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="AK1" s="8"/>
+      <c r="AL1" s="8"/>
+      <c r="AM1" s="8"/>
+      <c r="AN1" s="8"/>
+      <c r="AO1" s="8"/>
+      <c r="AP1" s="8"/>
+      <c r="AQ1" s="8"/>
+      <c r="AR1" s="8"/>
+      <c r="AS1" s="8"/>
+      <c r="AT1" s="8"/>
+      <c r="AU1" s="8"/>
+      <c r="AV1" s="8"/>
+      <c r="AW1" s="8"/>
+      <c r="AX1" s="8"/>
+      <c r="AY1" s="8"/>
+      <c r="AZ1" s="8"/>
+      <c r="BA1" s="8"/>
+      <c r="BB1" s="8"/>
+      <c r="BC1" s="8"/>
+      <c r="BD1" s="8"/>
+      <c r="BE1" s="8"/>
+      <c r="BF1" s="8"/>
+      <c r="BG1" s="8"/>
+      <c r="BH1" s="8"/>
+      <c r="BI1" s="8"/>
+      <c r="BJ1" s="8"/>
+      <c r="BK1" s="8"/>
+      <c r="BL1" s="8"/>
+      <c r="BM1" s="8"/>
     </row>
-    <row r="2" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1650,8 +1922,94 @@
       <c r="Q2" s="1" t="s">
         <v>362</v>
       </c>
+      <c r="R2" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="S2" s="9">
+        <v>1</v>
+      </c>
+      <c r="T2" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="U2" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="V2" s="9">
+        <v>1</v>
+      </c>
+      <c r="W2" s="9">
+        <v>1</v>
+      </c>
+      <c r="X2" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AF2" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AG2" s="9">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AJ2" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AK2" s="8"/>
+      <c r="AL2" s="8"/>
+      <c r="AM2" s="8"/>
+      <c r="AN2" s="8"/>
+      <c r="AO2" s="8"/>
+      <c r="AP2" s="8"/>
+      <c r="AQ2" s="8"/>
+      <c r="AR2" s="8"/>
+      <c r="AS2" s="8"/>
+      <c r="AT2" s="8"/>
+      <c r="AU2" s="8"/>
+      <c r="AV2" s="8"/>
+      <c r="AW2" s="8"/>
+      <c r="AX2" s="8"/>
+      <c r="AY2" s="8"/>
+      <c r="AZ2" s="8"/>
+      <c r="BA2" s="8"/>
+      <c r="BB2" s="8"/>
+      <c r="BC2" s="8"/>
+      <c r="BD2" s="8"/>
+      <c r="BE2" s="8"/>
+      <c r="BF2" s="8"/>
+      <c r="BG2" s="8"/>
+      <c r="BH2" s="8"/>
+      <c r="BI2" s="8"/>
+      <c r="BJ2" s="8"/>
+      <c r="BK2" s="8"/>
+      <c r="BL2" s="8"/>
+      <c r="BM2" s="8"/>
     </row>
-    <row r="3" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1703,8 +2061,94 @@
       <c r="Q3" s="1" t="s">
         <v>363</v>
       </c>
+      <c r="R3" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="S3" s="9">
+        <v>1</v>
+      </c>
+      <c r="T3" s="9">
+        <v>1</v>
+      </c>
+      <c r="U3" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="V3" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="W3" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X3" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="Y3" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="Z3" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA3" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB3" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="AH3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="8"/>
+      <c r="AL3" s="8"/>
+      <c r="AM3" s="8"/>
+      <c r="AN3" s="8"/>
+      <c r="AO3" s="8"/>
+      <c r="AP3" s="8"/>
+      <c r="AQ3" s="8"/>
+      <c r="AR3" s="8"/>
+      <c r="AS3" s="8"/>
+      <c r="AT3" s="8"/>
+      <c r="AU3" s="8"/>
+      <c r="AV3" s="8"/>
+      <c r="AW3" s="8"/>
+      <c r="AX3" s="8"/>
+      <c r="AY3" s="8"/>
+      <c r="AZ3" s="8"/>
+      <c r="BA3" s="8"/>
+      <c r="BB3" s="8"/>
+      <c r="BC3" s="8"/>
+      <c r="BD3" s="8"/>
+      <c r="BE3" s="8"/>
+      <c r="BF3" s="8"/>
+      <c r="BG3" s="8"/>
+      <c r="BH3" s="8"/>
+      <c r="BI3" s="8"/>
+      <c r="BJ3" s="8"/>
+      <c r="BK3" s="8"/>
+      <c r="BL3" s="8"/>
+      <c r="BM3" s="8"/>
     </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1756,8 +2200,94 @@
       <c r="Q4" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R4" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="S4" s="9">
+        <v>1</v>
+      </c>
+      <c r="T4" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U4" s="9">
+        <v>1</v>
+      </c>
+      <c r="V4" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W4" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X4" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="Y4" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="Z4" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA4" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB4" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AD4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="8"/>
+      <c r="AL4" s="8"/>
+      <c r="AM4" s="8"/>
+      <c r="AN4" s="8"/>
+      <c r="AO4" s="8"/>
+      <c r="AP4" s="8"/>
+      <c r="AQ4" s="8"/>
+      <c r="AR4" s="8"/>
+      <c r="AS4" s="8"/>
+      <c r="AT4" s="8"/>
+      <c r="AU4" s="8"/>
+      <c r="AV4" s="8"/>
+      <c r="AW4" s="8"/>
+      <c r="AX4" s="8"/>
+      <c r="AY4" s="8"/>
+      <c r="AZ4" s="8"/>
+      <c r="BA4" s="8"/>
+      <c r="BB4" s="8"/>
+      <c r="BC4" s="8"/>
+      <c r="BD4" s="8"/>
+      <c r="BE4" s="8"/>
+      <c r="BF4" s="8"/>
+      <c r="BG4" s="8"/>
+      <c r="BH4" s="8"/>
+      <c r="BI4" s="8"/>
+      <c r="BJ4" s="8"/>
+      <c r="BK4" s="8"/>
+      <c r="BL4" s="8"/>
+      <c r="BM4" s="8"/>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1809,8 +2339,94 @@
       <c r="Q5" s="5" t="s">
         <v>362</v>
       </c>
+      <c r="R5" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="S5" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="T5" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="U5" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="V5" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="W5" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="X5" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y5" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Z5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD5" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AE5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="8"/>
+      <c r="AL5" s="8"/>
+      <c r="AM5" s="8"/>
+      <c r="AN5" s="8"/>
+      <c r="AO5" s="8"/>
+      <c r="AP5" s="8"/>
+      <c r="AQ5" s="8"/>
+      <c r="AR5" s="8"/>
+      <c r="AS5" s="8"/>
+      <c r="AT5" s="8"/>
+      <c r="AU5" s="8"/>
+      <c r="AV5" s="8"/>
+      <c r="AW5" s="8"/>
+      <c r="AX5" s="8"/>
+      <c r="AY5" s="8"/>
+      <c r="AZ5" s="8"/>
+      <c r="BA5" s="8"/>
+      <c r="BB5" s="8"/>
+      <c r="BC5" s="8"/>
+      <c r="BD5" s="8"/>
+      <c r="BE5" s="8"/>
+      <c r="BF5" s="8"/>
+      <c r="BG5" s="8"/>
+      <c r="BH5" s="8"/>
+      <c r="BI5" s="8"/>
+      <c r="BJ5" s="8"/>
+      <c r="BK5" s="8"/>
+      <c r="BL5" s="8"/>
+      <c r="BM5" s="8"/>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1862,8 +2478,94 @@
       <c r="Q6" s="5" t="s">
         <v>362</v>
       </c>
+      <c r="R6" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="S6" s="9">
+        <v>1</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0</v>
+      </c>
+      <c r="U6" s="9">
+        <v>1</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X6" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AD6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AF6" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AG6" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AH6" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AI6" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AJ6" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AK6" s="8"/>
+      <c r="AL6" s="8"/>
+      <c r="AM6" s="8"/>
+      <c r="AN6" s="8"/>
+      <c r="AO6" s="8"/>
+      <c r="AP6" s="8"/>
+      <c r="AQ6" s="8"/>
+      <c r="AR6" s="8"/>
+      <c r="AS6" s="8"/>
+      <c r="AT6" s="8"/>
+      <c r="AU6" s="8"/>
+      <c r="AV6" s="8"/>
+      <c r="AW6" s="8"/>
+      <c r="AX6" s="8"/>
+      <c r="AY6" s="8"/>
+      <c r="AZ6" s="8"/>
+      <c r="BA6" s="8"/>
+      <c r="BB6" s="8"/>
+      <c r="BC6" s="8"/>
+      <c r="BD6" s="8"/>
+      <c r="BE6" s="8"/>
+      <c r="BF6" s="8"/>
+      <c r="BG6" s="8"/>
+      <c r="BH6" s="8"/>
+      <c r="BI6" s="8"/>
+      <c r="BJ6" s="8"/>
+      <c r="BK6" s="8"/>
+      <c r="BL6" s="8"/>
+      <c r="BM6" s="8"/>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1915,8 +2617,94 @@
       <c r="Q7" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R7" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="S7" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="T7" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U7" s="9">
+        <v>1</v>
+      </c>
+      <c r="V7" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="W7" s="9">
+        <v>0</v>
+      </c>
+      <c r="X7" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AA7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AF7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AH7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="8"/>
+      <c r="AL7" s="8"/>
+      <c r="AM7" s="8"/>
+      <c r="AN7" s="8"/>
+      <c r="AO7" s="8"/>
+      <c r="AP7" s="8"/>
+      <c r="AQ7" s="8"/>
+      <c r="AR7" s="8"/>
+      <c r="AS7" s="8"/>
+      <c r="AT7" s="8"/>
+      <c r="AU7" s="8"/>
+      <c r="AV7" s="8"/>
+      <c r="AW7" s="8"/>
+      <c r="AX7" s="8"/>
+      <c r="AY7" s="8"/>
+      <c r="AZ7" s="8"/>
+      <c r="BA7" s="8"/>
+      <c r="BB7" s="8"/>
+      <c r="BC7" s="8"/>
+      <c r="BD7" s="8"/>
+      <c r="BE7" s="8"/>
+      <c r="BF7" s="8"/>
+      <c r="BG7" s="8"/>
+      <c r="BH7" s="8"/>
+      <c r="BI7" s="8"/>
+      <c r="BJ7" s="8"/>
+      <c r="BK7" s="8"/>
+      <c r="BL7" s="8"/>
+      <c r="BM7" s="8"/>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1968,8 +2756,94 @@
       <c r="Q8" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R8" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="S8" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="T8" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U8" s="9">
+        <v>1</v>
+      </c>
+      <c r="V8" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="W8" s="9">
+        <v>0</v>
+      </c>
+      <c r="X8" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AA8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AF8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AH8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="8"/>
+      <c r="AL8" s="8"/>
+      <c r="AM8" s="8"/>
+      <c r="AN8" s="8"/>
+      <c r="AO8" s="8"/>
+      <c r="AP8" s="8"/>
+      <c r="AQ8" s="8"/>
+      <c r="AR8" s="8"/>
+      <c r="AS8" s="8"/>
+      <c r="AT8" s="8"/>
+      <c r="AU8" s="8"/>
+      <c r="AV8" s="8"/>
+      <c r="AW8" s="8"/>
+      <c r="AX8" s="8"/>
+      <c r="AY8" s="8"/>
+      <c r="AZ8" s="8"/>
+      <c r="BA8" s="8"/>
+      <c r="BB8" s="8"/>
+      <c r="BC8" s="8"/>
+      <c r="BD8" s="8"/>
+      <c r="BE8" s="8"/>
+      <c r="BF8" s="8"/>
+      <c r="BG8" s="8"/>
+      <c r="BH8" s="8"/>
+      <c r="BI8" s="8"/>
+      <c r="BJ8" s="8"/>
+      <c r="BK8" s="8"/>
+      <c r="BL8" s="8"/>
+      <c r="BM8" s="8"/>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2021,8 +2895,94 @@
       <c r="Q9" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R9" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="S9" s="9">
+        <v>1</v>
+      </c>
+      <c r="T9" s="9">
+        <v>0</v>
+      </c>
+      <c r="U9" s="9">
+        <v>1</v>
+      </c>
+      <c r="V9" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W9" s="9">
+        <v>0</v>
+      </c>
+      <c r="X9" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA9" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="9">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="9">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="8"/>
+      <c r="AL9" s="8"/>
+      <c r="AM9" s="8"/>
+      <c r="AN9" s="8"/>
+      <c r="AO9" s="8"/>
+      <c r="AP9" s="8"/>
+      <c r="AQ9" s="8"/>
+      <c r="AR9" s="8"/>
+      <c r="AS9" s="8"/>
+      <c r="AT9" s="8"/>
+      <c r="AU9" s="8"/>
+      <c r="AV9" s="8"/>
+      <c r="AW9" s="8"/>
+      <c r="AX9" s="8"/>
+      <c r="AY9" s="8"/>
+      <c r="AZ9" s="8"/>
+      <c r="BA9" s="8"/>
+      <c r="BB9" s="8"/>
+      <c r="BC9" s="8"/>
+      <c r="BD9" s="8"/>
+      <c r="BE9" s="8"/>
+      <c r="BF9" s="8"/>
+      <c r="BG9" s="8"/>
+      <c r="BH9" s="8"/>
+      <c r="BI9" s="8"/>
+      <c r="BJ9" s="8"/>
+      <c r="BK9" s="8"/>
+      <c r="BL9" s="8"/>
+      <c r="BM9" s="8"/>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2074,8 +3034,94 @@
       <c r="Q10" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R10" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="S10" s="9">
+        <v>1</v>
+      </c>
+      <c r="T10" s="9">
+        <v>1</v>
+      </c>
+      <c r="U10" s="9">
+        <v>1</v>
+      </c>
+      <c r="V10" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W10" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="X10" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y10" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Z10" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA10" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="9">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="9">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="8"/>
+      <c r="AL10" s="8"/>
+      <c r="AM10" s="8"/>
+      <c r="AN10" s="8"/>
+      <c r="AO10" s="8"/>
+      <c r="AP10" s="8"/>
+      <c r="AQ10" s="8"/>
+      <c r="AR10" s="8"/>
+      <c r="AS10" s="8"/>
+      <c r="AT10" s="8"/>
+      <c r="AU10" s="8"/>
+      <c r="AV10" s="8"/>
+      <c r="AW10" s="8"/>
+      <c r="AX10" s="8"/>
+      <c r="AY10" s="8"/>
+      <c r="AZ10" s="8"/>
+      <c r="BA10" s="8"/>
+      <c r="BB10" s="8"/>
+      <c r="BC10" s="8"/>
+      <c r="BD10" s="8"/>
+      <c r="BE10" s="8"/>
+      <c r="BF10" s="8"/>
+      <c r="BG10" s="8"/>
+      <c r="BH10" s="8"/>
+      <c r="BI10" s="8"/>
+      <c r="BJ10" s="8"/>
+      <c r="BK10" s="8"/>
+      <c r="BL10" s="8"/>
+      <c r="BM10" s="8"/>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2127,8 +3173,94 @@
       <c r="Q11" s="5" t="s">
         <v>362</v>
       </c>
+      <c r="R11" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="S11" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="T11" s="9">
+        <v>0</v>
+      </c>
+      <c r="U11" s="9">
+        <v>1</v>
+      </c>
+      <c r="V11" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W11" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="X11" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AA11" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AE11" s="9">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="9">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="8"/>
+      <c r="AL11" s="8"/>
+      <c r="AM11" s="8"/>
+      <c r="AN11" s="8"/>
+      <c r="AO11" s="8"/>
+      <c r="AP11" s="8"/>
+      <c r="AQ11" s="8"/>
+      <c r="AR11" s="8"/>
+      <c r="AS11" s="8"/>
+      <c r="AT11" s="8"/>
+      <c r="AU11" s="8"/>
+      <c r="AV11" s="8"/>
+      <c r="AW11" s="8"/>
+      <c r="AX11" s="8"/>
+      <c r="AY11" s="8"/>
+      <c r="AZ11" s="8"/>
+      <c r="BA11" s="8"/>
+      <c r="BB11" s="8"/>
+      <c r="BC11" s="8"/>
+      <c r="BD11" s="8"/>
+      <c r="BE11" s="8"/>
+      <c r="BF11" s="8"/>
+      <c r="BG11" s="8"/>
+      <c r="BH11" s="8"/>
+      <c r="BI11" s="8"/>
+      <c r="BJ11" s="8"/>
+      <c r="BK11" s="8"/>
+      <c r="BL11" s="8"/>
+      <c r="BM11" s="8"/>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2180,8 +3312,94 @@
       <c r="Q12" s="5" t="s">
         <v>362</v>
       </c>
+      <c r="R12" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="S12" s="9">
+        <v>1</v>
+      </c>
+      <c r="T12" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="U12" s="9">
+        <v>1</v>
+      </c>
+      <c r="V12" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W12" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="X12" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y12" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Z12" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AA12" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AB12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD12" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AE12" s="9">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="9">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="9">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI12" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AJ12" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AK12" s="8"/>
+      <c r="AL12" s="8"/>
+      <c r="AM12" s="8"/>
+      <c r="AN12" s="8"/>
+      <c r="AO12" s="8"/>
+      <c r="AP12" s="8"/>
+      <c r="AQ12" s="8"/>
+      <c r="AR12" s="8"/>
+      <c r="AS12" s="8"/>
+      <c r="AT12" s="8"/>
+      <c r="AU12" s="8"/>
+      <c r="AV12" s="8"/>
+      <c r="AW12" s="8"/>
+      <c r="AX12" s="8"/>
+      <c r="AY12" s="8"/>
+      <c r="AZ12" s="8"/>
+      <c r="BA12" s="8"/>
+      <c r="BB12" s="8"/>
+      <c r="BC12" s="8"/>
+      <c r="BD12" s="8"/>
+      <c r="BE12" s="8"/>
+      <c r="BF12" s="8"/>
+      <c r="BG12" s="8"/>
+      <c r="BH12" s="8"/>
+      <c r="BI12" s="8"/>
+      <c r="BJ12" s="8"/>
+      <c r="BK12" s="8"/>
+      <c r="BL12" s="8"/>
+      <c r="BM12" s="8"/>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2233,8 +3451,94 @@
       <c r="Q13" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R13" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="S13" s="9">
+        <v>1</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="X13" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AD13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AF13" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AG13" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AH13" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AI13" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AJ13" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AK13" s="8"/>
+      <c r="AL13" s="8"/>
+      <c r="AM13" s="8"/>
+      <c r="AN13" s="8"/>
+      <c r="AO13" s="8"/>
+      <c r="AP13" s="8"/>
+      <c r="AQ13" s="8"/>
+      <c r="AR13" s="8"/>
+      <c r="AS13" s="8"/>
+      <c r="AT13" s="8"/>
+      <c r="AU13" s="8"/>
+      <c r="AV13" s="8"/>
+      <c r="AW13" s="8"/>
+      <c r="AX13" s="8"/>
+      <c r="AY13" s="8"/>
+      <c r="AZ13" s="8"/>
+      <c r="BA13" s="8"/>
+      <c r="BB13" s="8"/>
+      <c r="BC13" s="8"/>
+      <c r="BD13" s="8"/>
+      <c r="BE13" s="8"/>
+      <c r="BF13" s="8"/>
+      <c r="BG13" s="8"/>
+      <c r="BH13" s="8"/>
+      <c r="BI13" s="8"/>
+      <c r="BJ13" s="8"/>
+      <c r="BK13" s="8"/>
+      <c r="BL13" s="8"/>
+      <c r="BM13" s="8"/>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2286,8 +3590,94 @@
       <c r="Q14" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R14" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="S14" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="T14" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U14" s="9">
+        <v>1</v>
+      </c>
+      <c r="V14" s="9">
+        <v>0</v>
+      </c>
+      <c r="W14" s="9">
+        <v>0</v>
+      </c>
+      <c r="X14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="8"/>
+      <c r="AL14" s="8"/>
+      <c r="AM14" s="8"/>
+      <c r="AN14" s="8"/>
+      <c r="AO14" s="8"/>
+      <c r="AP14" s="8"/>
+      <c r="AQ14" s="8"/>
+      <c r="AR14" s="8"/>
+      <c r="AS14" s="8"/>
+      <c r="AT14" s="8"/>
+      <c r="AU14" s="8"/>
+      <c r="AV14" s="8"/>
+      <c r="AW14" s="8"/>
+      <c r="AX14" s="8"/>
+      <c r="AY14" s="8"/>
+      <c r="AZ14" s="8"/>
+      <c r="BA14" s="8"/>
+      <c r="BB14" s="8"/>
+      <c r="BC14" s="8"/>
+      <c r="BD14" s="8"/>
+      <c r="BE14" s="8"/>
+      <c r="BF14" s="8"/>
+      <c r="BG14" s="8"/>
+      <c r="BH14" s="8"/>
+      <c r="BI14" s="8"/>
+      <c r="BJ14" s="8"/>
+      <c r="BK14" s="8"/>
+      <c r="BL14" s="8"/>
+      <c r="BM14" s="8"/>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2339,8 +3729,94 @@
       <c r="Q15" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R15" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="S15" s="9">
+        <v>1</v>
+      </c>
+      <c r="T15" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="U15" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="V15" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="W15" s="9">
+        <v>0</v>
+      </c>
+      <c r="X15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="8"/>
+      <c r="AL15" s="8"/>
+      <c r="AM15" s="8"/>
+      <c r="AN15" s="8"/>
+      <c r="AO15" s="8"/>
+      <c r="AP15" s="8"/>
+      <c r="AQ15" s="8"/>
+      <c r="AR15" s="8"/>
+      <c r="AS15" s="8"/>
+      <c r="AT15" s="8"/>
+      <c r="AU15" s="8"/>
+      <c r="AV15" s="8"/>
+      <c r="AW15" s="8"/>
+      <c r="AX15" s="8"/>
+      <c r="AY15" s="8"/>
+      <c r="AZ15" s="8"/>
+      <c r="BA15" s="8"/>
+      <c r="BB15" s="8"/>
+      <c r="BC15" s="8"/>
+      <c r="BD15" s="8"/>
+      <c r="BE15" s="8"/>
+      <c r="BF15" s="8"/>
+      <c r="BG15" s="8"/>
+      <c r="BH15" s="8"/>
+      <c r="BI15" s="8"/>
+      <c r="BJ15" s="8"/>
+      <c r="BK15" s="8"/>
+      <c r="BL15" s="8"/>
+      <c r="BM15" s="8"/>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2392,8 +3868,94 @@
       <c r="Q16" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R16" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="S16" s="9">
+        <v>1</v>
+      </c>
+      <c r="T16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U16" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="V16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="W16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AA16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AE16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="8"/>
+      <c r="AL16" s="8"/>
+      <c r="AM16" s="8"/>
+      <c r="AN16" s="8"/>
+      <c r="AO16" s="8"/>
+      <c r="AP16" s="8"/>
+      <c r="AQ16" s="8"/>
+      <c r="AR16" s="8"/>
+      <c r="AS16" s="8"/>
+      <c r="AT16" s="8"/>
+      <c r="AU16" s="8"/>
+      <c r="AV16" s="8"/>
+      <c r="AW16" s="8"/>
+      <c r="AX16" s="8"/>
+      <c r="AY16" s="8"/>
+      <c r="AZ16" s="8"/>
+      <c r="BA16" s="8"/>
+      <c r="BB16" s="8"/>
+      <c r="BC16" s="8"/>
+      <c r="BD16" s="8"/>
+      <c r="BE16" s="8"/>
+      <c r="BF16" s="8"/>
+      <c r="BG16" s="8"/>
+      <c r="BH16" s="8"/>
+      <c r="BI16" s="8"/>
+      <c r="BJ16" s="8"/>
+      <c r="BK16" s="8"/>
+      <c r="BL16" s="8"/>
+      <c r="BM16" s="8"/>
     </row>
-    <row r="17" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2445,8 +4007,94 @@
       <c r="Q17" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R17" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="S17" s="9">
+        <v>1</v>
+      </c>
+      <c r="T17" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="U17" s="9">
+        <v>1</v>
+      </c>
+      <c r="V17" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="W17" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X17" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="Y17" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="Z17" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AA17" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AB17" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="8"/>
+      <c r="AL17" s="8"/>
+      <c r="AM17" s="8"/>
+      <c r="AN17" s="8"/>
+      <c r="AO17" s="8"/>
+      <c r="AP17" s="8"/>
+      <c r="AQ17" s="8"/>
+      <c r="AR17" s="8"/>
+      <c r="AS17" s="8"/>
+      <c r="AT17" s="8"/>
+      <c r="AU17" s="8"/>
+      <c r="AV17" s="8"/>
+      <c r="AW17" s="8"/>
+      <c r="AX17" s="8"/>
+      <c r="AY17" s="8"/>
+      <c r="AZ17" s="8"/>
+      <c r="BA17" s="8"/>
+      <c r="BB17" s="8"/>
+      <c r="BC17" s="8"/>
+      <c r="BD17" s="8"/>
+      <c r="BE17" s="8"/>
+      <c r="BF17" s="8"/>
+      <c r="BG17" s="8"/>
+      <c r="BH17" s="8"/>
+      <c r="BI17" s="8"/>
+      <c r="BJ17" s="8"/>
+      <c r="BK17" s="8"/>
+      <c r="BL17" s="8"/>
+      <c r="BM17" s="8"/>
     </row>
-    <row r="18" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2498,8 +4146,94 @@
       <c r="Q18" s="5" t="s">
         <v>362</v>
       </c>
+      <c r="R18" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="S18" s="9">
+        <v>0.95</v>
+      </c>
+      <c r="T18" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U18" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="V18" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W18" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="X18" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA18" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB18" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AD18" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AE18" s="9">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="9">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AH18" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AI18" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AJ18" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AK18" s="8"/>
+      <c r="AL18" s="8"/>
+      <c r="AM18" s="8"/>
+      <c r="AN18" s="8"/>
+      <c r="AO18" s="8"/>
+      <c r="AP18" s="8"/>
+      <c r="AQ18" s="8"/>
+      <c r="AR18" s="8"/>
+      <c r="AS18" s="8"/>
+      <c r="AT18" s="8"/>
+      <c r="AU18" s="8"/>
+      <c r="AV18" s="8"/>
+      <c r="AW18" s="8"/>
+      <c r="AX18" s="8"/>
+      <c r="AY18" s="8"/>
+      <c r="AZ18" s="8"/>
+      <c r="BA18" s="8"/>
+      <c r="BB18" s="8"/>
+      <c r="BC18" s="8"/>
+      <c r="BD18" s="8"/>
+      <c r="BE18" s="8"/>
+      <c r="BF18" s="8"/>
+      <c r="BG18" s="8"/>
+      <c r="BH18" s="8"/>
+      <c r="BI18" s="8"/>
+      <c r="BJ18" s="8"/>
+      <c r="BK18" s="8"/>
+      <c r="BL18" s="8"/>
+      <c r="BM18" s="8"/>
     </row>
-    <row r="19" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2551,8 +4285,94 @@
       <c r="Q19" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R19" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="S19" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="T19" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U19" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="V19" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="W19" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="X19" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="Y19" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="Z19" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AA19" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AB19" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD19" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AE19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="8"/>
+      <c r="AL19" s="8"/>
+      <c r="AM19" s="8"/>
+      <c r="AN19" s="8"/>
+      <c r="AO19" s="8"/>
+      <c r="AP19" s="8"/>
+      <c r="AQ19" s="8"/>
+      <c r="AR19" s="8"/>
+      <c r="AS19" s="8"/>
+      <c r="AT19" s="8"/>
+      <c r="AU19" s="8"/>
+      <c r="AV19" s="8"/>
+      <c r="AW19" s="8"/>
+      <c r="AX19" s="8"/>
+      <c r="AY19" s="8"/>
+      <c r="AZ19" s="8"/>
+      <c r="BA19" s="8"/>
+      <c r="BB19" s="8"/>
+      <c r="BC19" s="8"/>
+      <c r="BD19" s="8"/>
+      <c r="BE19" s="8"/>
+      <c r="BF19" s="8"/>
+      <c r="BG19" s="8"/>
+      <c r="BH19" s="8"/>
+      <c r="BI19" s="8"/>
+      <c r="BJ19" s="8"/>
+      <c r="BK19" s="8"/>
+      <c r="BL19" s="8"/>
+      <c r="BM19" s="8"/>
     </row>
-    <row r="20" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2604,8 +4424,94 @@
       <c r="Q20" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R20" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="S20" s="9">
+        <v>1</v>
+      </c>
+      <c r="T20" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="U20" s="9">
+        <v>1</v>
+      </c>
+      <c r="V20" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W20" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="X20" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AA20" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AB20" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD20" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AE20" s="9">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="9">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="9">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AJ20" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AK20" s="8"/>
+      <c r="AL20" s="8"/>
+      <c r="AM20" s="8"/>
+      <c r="AN20" s="8"/>
+      <c r="AO20" s="8"/>
+      <c r="AP20" s="8"/>
+      <c r="AQ20" s="8"/>
+      <c r="AR20" s="8"/>
+      <c r="AS20" s="8"/>
+      <c r="AT20" s="8"/>
+      <c r="AU20" s="8"/>
+      <c r="AV20" s="8"/>
+      <c r="AW20" s="8"/>
+      <c r="AX20" s="8"/>
+      <c r="AY20" s="8"/>
+      <c r="AZ20" s="8"/>
+      <c r="BA20" s="8"/>
+      <c r="BB20" s="8"/>
+      <c r="BC20" s="8"/>
+      <c r="BD20" s="8"/>
+      <c r="BE20" s="8"/>
+      <c r="BF20" s="8"/>
+      <c r="BG20" s="8"/>
+      <c r="BH20" s="8"/>
+      <c r="BI20" s="8"/>
+      <c r="BJ20" s="8"/>
+      <c r="BK20" s="8"/>
+      <c r="BL20" s="8"/>
+      <c r="BM20" s="8"/>
     </row>
-    <row r="21" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2657,8 +4563,94 @@
       <c r="Q21" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R21" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="S21" s="9">
+        <v>1</v>
+      </c>
+      <c r="T21" s="9">
+        <v>0</v>
+      </c>
+      <c r="U21" s="9">
+        <v>1</v>
+      </c>
+      <c r="V21" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="W21" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="X21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA21" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD21" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AE21" s="9">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="9">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="9">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI21" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AJ21" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AK21" s="8"/>
+      <c r="AL21" s="8"/>
+      <c r="AM21" s="8"/>
+      <c r="AN21" s="8"/>
+      <c r="AO21" s="8"/>
+      <c r="AP21" s="8"/>
+      <c r="AQ21" s="8"/>
+      <c r="AR21" s="8"/>
+      <c r="AS21" s="8"/>
+      <c r="AT21" s="8"/>
+      <c r="AU21" s="8"/>
+      <c r="AV21" s="8"/>
+      <c r="AW21" s="8"/>
+      <c r="AX21" s="8"/>
+      <c r="AY21" s="8"/>
+      <c r="AZ21" s="8"/>
+      <c r="BA21" s="8"/>
+      <c r="BB21" s="8"/>
+      <c r="BC21" s="8"/>
+      <c r="BD21" s="8"/>
+      <c r="BE21" s="8"/>
+      <c r="BF21" s="8"/>
+      <c r="BG21" s="8"/>
+      <c r="BH21" s="8"/>
+      <c r="BI21" s="8"/>
+      <c r="BJ21" s="8"/>
+      <c r="BK21" s="8"/>
+      <c r="BL21" s="8"/>
+      <c r="BM21" s="8"/>
     </row>
-    <row r="22" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2710,8 +4702,94 @@
       <c r="Q22" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R22" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="S22" s="9">
+        <v>1</v>
+      </c>
+      <c r="T22" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="U22" s="9">
+        <v>1</v>
+      </c>
+      <c r="V22" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="W22" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="X22" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA22" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD22" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AE22" s="9">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="9">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="9">
+        <v>1</v>
+      </c>
+      <c r="AH22" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI22" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AJ22" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AK22" s="8"/>
+      <c r="AL22" s="8"/>
+      <c r="AM22" s="8"/>
+      <c r="AN22" s="8"/>
+      <c r="AO22" s="8"/>
+      <c r="AP22" s="8"/>
+      <c r="AQ22" s="8"/>
+      <c r="AR22" s="8"/>
+      <c r="AS22" s="8"/>
+      <c r="AT22" s="8"/>
+      <c r="AU22" s="8"/>
+      <c r="AV22" s="8"/>
+      <c r="AW22" s="8"/>
+      <c r="AX22" s="8"/>
+      <c r="AY22" s="8"/>
+      <c r="AZ22" s="8"/>
+      <c r="BA22" s="8"/>
+      <c r="BB22" s="8"/>
+      <c r="BC22" s="8"/>
+      <c r="BD22" s="8"/>
+      <c r="BE22" s="8"/>
+      <c r="BF22" s="8"/>
+      <c r="BG22" s="8"/>
+      <c r="BH22" s="8"/>
+      <c r="BI22" s="8"/>
+      <c r="BJ22" s="8"/>
+      <c r="BK22" s="8"/>
+      <c r="BL22" s="8"/>
+      <c r="BM22" s="8"/>
     </row>
-    <row r="23" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2763,8 +4841,94 @@
       <c r="Q23" s="5" t="s">
         <v>362</v>
       </c>
+      <c r="R23" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="S23" s="9">
+        <v>1</v>
+      </c>
+      <c r="T23" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="U23" s="9">
+        <v>1</v>
+      </c>
+      <c r="V23" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="W23" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="X23" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="Y23" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="Z23" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE23" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AF23" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AG23" s="9">
+        <v>1</v>
+      </c>
+      <c r="AH23" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI23" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AJ23" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AK23" s="8"/>
+      <c r="AL23" s="8"/>
+      <c r="AM23" s="8"/>
+      <c r="AN23" s="8"/>
+      <c r="AO23" s="8"/>
+      <c r="AP23" s="8"/>
+      <c r="AQ23" s="8"/>
+      <c r="AR23" s="8"/>
+      <c r="AS23" s="8"/>
+      <c r="AT23" s="8"/>
+      <c r="AU23" s="8"/>
+      <c r="AV23" s="8"/>
+      <c r="AW23" s="8"/>
+      <c r="AX23" s="8"/>
+      <c r="AY23" s="8"/>
+      <c r="AZ23" s="8"/>
+      <c r="BA23" s="8"/>
+      <c r="BB23" s="8"/>
+      <c r="BC23" s="8"/>
+      <c r="BD23" s="8"/>
+      <c r="BE23" s="8"/>
+      <c r="BF23" s="8"/>
+      <c r="BG23" s="8"/>
+      <c r="BH23" s="8"/>
+      <c r="BI23" s="8"/>
+      <c r="BJ23" s="8"/>
+      <c r="BK23" s="8"/>
+      <c r="BL23" s="8"/>
+      <c r="BM23" s="8"/>
     </row>
-    <row r="24" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2816,8 +4980,94 @@
       <c r="Q24" s="5" t="s">
         <v>362</v>
       </c>
+      <c r="R24" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="S24" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="T24" s="9">
+        <v>0.95</v>
+      </c>
+      <c r="U24" s="9">
+        <v>1</v>
+      </c>
+      <c r="V24" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="W24" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X24" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AA24" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AB24" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AF24" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AG24" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="8"/>
+      <c r="AL24" s="8"/>
+      <c r="AM24" s="8"/>
+      <c r="AN24" s="8"/>
+      <c r="AO24" s="8"/>
+      <c r="AP24" s="8"/>
+      <c r="AQ24" s="8"/>
+      <c r="AR24" s="8"/>
+      <c r="AS24" s="8"/>
+      <c r="AT24" s="8"/>
+      <c r="AU24" s="8"/>
+      <c r="AV24" s="8"/>
+      <c r="AW24" s="8"/>
+      <c r="AX24" s="8"/>
+      <c r="AY24" s="8"/>
+      <c r="AZ24" s="8"/>
+      <c r="BA24" s="8"/>
+      <c r="BB24" s="8"/>
+      <c r="BC24" s="8"/>
+      <c r="BD24" s="8"/>
+      <c r="BE24" s="8"/>
+      <c r="BF24" s="8"/>
+      <c r="BG24" s="8"/>
+      <c r="BH24" s="8"/>
+      <c r="BI24" s="8"/>
+      <c r="BJ24" s="8"/>
+      <c r="BK24" s="8"/>
+      <c r="BL24" s="8"/>
+      <c r="BM24" s="8"/>
     </row>
-    <row r="25" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2869,8 +5119,94 @@
       <c r="Q25" s="5" t="s">
         <v>362</v>
       </c>
+      <c r="R25" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="S25" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="T25" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U25" s="9">
+        <v>1</v>
+      </c>
+      <c r="V25" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W25" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X25" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y25" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AA25" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AB25" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AE25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AH25" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AJ25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AK25" s="8"/>
+      <c r="AL25" s="8"/>
+      <c r="AM25" s="8"/>
+      <c r="AN25" s="8"/>
+      <c r="AO25" s="8"/>
+      <c r="AP25" s="8"/>
+      <c r="AQ25" s="8"/>
+      <c r="AR25" s="8"/>
+      <c r="AS25" s="8"/>
+      <c r="AT25" s="8"/>
+      <c r="AU25" s="8"/>
+      <c r="AV25" s="8"/>
+      <c r="AW25" s="8"/>
+      <c r="AX25" s="8"/>
+      <c r="AY25" s="8"/>
+      <c r="AZ25" s="8"/>
+      <c r="BA25" s="8"/>
+      <c r="BB25" s="8"/>
+      <c r="BC25" s="8"/>
+      <c r="BD25" s="8"/>
+      <c r="BE25" s="8"/>
+      <c r="BF25" s="8"/>
+      <c r="BG25" s="8"/>
+      <c r="BH25" s="8"/>
+      <c r="BI25" s="8"/>
+      <c r="BJ25" s="8"/>
+      <c r="BK25" s="8"/>
+      <c r="BL25" s="8"/>
+      <c r="BM25" s="8"/>
     </row>
-    <row r="26" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2922,8 +5258,94 @@
       <c r="Q26" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R26" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="S26" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="T26" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="U26" s="9">
+        <v>1</v>
+      </c>
+      <c r="V26" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="W26" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X26" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AA26" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AB26" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="9">
+        <v>1</v>
+      </c>
+      <c r="AH26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="8"/>
+      <c r="AL26" s="8"/>
+      <c r="AM26" s="8"/>
+      <c r="AN26" s="8"/>
+      <c r="AO26" s="8"/>
+      <c r="AP26" s="8"/>
+      <c r="AQ26" s="8"/>
+      <c r="AR26" s="8"/>
+      <c r="AS26" s="8"/>
+      <c r="AT26" s="8"/>
+      <c r="AU26" s="8"/>
+      <c r="AV26" s="8"/>
+      <c r="AW26" s="8"/>
+      <c r="AX26" s="8"/>
+      <c r="AY26" s="8"/>
+      <c r="AZ26" s="8"/>
+      <c r="BA26" s="8"/>
+      <c r="BB26" s="8"/>
+      <c r="BC26" s="8"/>
+      <c r="BD26" s="8"/>
+      <c r="BE26" s="8"/>
+      <c r="BF26" s="8"/>
+      <c r="BG26" s="8"/>
+      <c r="BH26" s="8"/>
+      <c r="BI26" s="8"/>
+      <c r="BJ26" s="8"/>
+      <c r="BK26" s="8"/>
+      <c r="BL26" s="8"/>
+      <c r="BM26" s="8"/>
     </row>
-    <row r="27" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2975,8 +5397,94 @@
       <c r="Q27" s="5" t="s">
         <v>362</v>
       </c>
+      <c r="R27" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="S27" s="9">
+        <v>1</v>
+      </c>
+      <c r="T27" s="9">
+        <v>1</v>
+      </c>
+      <c r="U27" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="V27" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W27" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="X27" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="Y27" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="Z27" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA27" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB27" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AD27" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AE27" s="9">
+        <v>1</v>
+      </c>
+      <c r="AF27" s="9">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AH27" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AI27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="8"/>
+      <c r="AL27" s="8"/>
+      <c r="AM27" s="8"/>
+      <c r="AN27" s="8"/>
+      <c r="AO27" s="8"/>
+      <c r="AP27" s="8"/>
+      <c r="AQ27" s="8"/>
+      <c r="AR27" s="8"/>
+      <c r="AS27" s="8"/>
+      <c r="AT27" s="8"/>
+      <c r="AU27" s="8"/>
+      <c r="AV27" s="8"/>
+      <c r="AW27" s="8"/>
+      <c r="AX27" s="8"/>
+      <c r="AY27" s="8"/>
+      <c r="AZ27" s="8"/>
+      <c r="BA27" s="8"/>
+      <c r="BB27" s="8"/>
+      <c r="BC27" s="8"/>
+      <c r="BD27" s="8"/>
+      <c r="BE27" s="8"/>
+      <c r="BF27" s="8"/>
+      <c r="BG27" s="8"/>
+      <c r="BH27" s="8"/>
+      <c r="BI27" s="8"/>
+      <c r="BJ27" s="8"/>
+      <c r="BK27" s="8"/>
+      <c r="BL27" s="8"/>
+      <c r="BM27" s="8"/>
     </row>
-    <row r="28" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3028,8 +5536,94 @@
       <c r="Q28" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R28" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="S28" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="T28" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="U28" s="9">
+        <v>1</v>
+      </c>
+      <c r="V28" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="W28" s="9">
+        <v>0</v>
+      </c>
+      <c r="X28" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AA28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AF28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="8"/>
+      <c r="AL28" s="8"/>
+      <c r="AM28" s="8"/>
+      <c r="AN28" s="8"/>
+      <c r="AO28" s="8"/>
+      <c r="AP28" s="8"/>
+      <c r="AQ28" s="8"/>
+      <c r="AR28" s="8"/>
+      <c r="AS28" s="8"/>
+      <c r="AT28" s="8"/>
+      <c r="AU28" s="8"/>
+      <c r="AV28" s="8"/>
+      <c r="AW28" s="8"/>
+      <c r="AX28" s="8"/>
+      <c r="AY28" s="8"/>
+      <c r="AZ28" s="8"/>
+      <c r="BA28" s="8"/>
+      <c r="BB28" s="8"/>
+      <c r="BC28" s="8"/>
+      <c r="BD28" s="8"/>
+      <c r="BE28" s="8"/>
+      <c r="BF28" s="8"/>
+      <c r="BG28" s="8"/>
+      <c r="BH28" s="8"/>
+      <c r="BI28" s="8"/>
+      <c r="BJ28" s="8"/>
+      <c r="BK28" s="8"/>
+      <c r="BL28" s="8"/>
+      <c r="BM28" s="8"/>
     </row>
-    <row r="29" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3081,8 +5675,94 @@
       <c r="Q29" s="5" t="s">
         <v>362</v>
       </c>
+      <c r="R29" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="S29" s="9">
+        <v>1</v>
+      </c>
+      <c r="T29" s="9">
+        <v>1</v>
+      </c>
+      <c r="U29" s="9">
+        <v>1</v>
+      </c>
+      <c r="V29" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W29" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="X29" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="Y29" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="Z29" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA29" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB29" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AD29" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AE29" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AF29" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AG29" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="8"/>
+      <c r="AL29" s="8"/>
+      <c r="AM29" s="8"/>
+      <c r="AN29" s="8"/>
+      <c r="AO29" s="8"/>
+      <c r="AP29" s="8"/>
+      <c r="AQ29" s="8"/>
+      <c r="AR29" s="8"/>
+      <c r="AS29" s="8"/>
+      <c r="AT29" s="8"/>
+      <c r="AU29" s="8"/>
+      <c r="AV29" s="8"/>
+      <c r="AW29" s="8"/>
+      <c r="AX29" s="8"/>
+      <c r="AY29" s="8"/>
+      <c r="AZ29" s="8"/>
+      <c r="BA29" s="8"/>
+      <c r="BB29" s="8"/>
+      <c r="BC29" s="8"/>
+      <c r="BD29" s="8"/>
+      <c r="BE29" s="8"/>
+      <c r="BF29" s="8"/>
+      <c r="BG29" s="8"/>
+      <c r="BH29" s="8"/>
+      <c r="BI29" s="8"/>
+      <c r="BJ29" s="8"/>
+      <c r="BK29" s="8"/>
+      <c r="BL29" s="8"/>
+      <c r="BM29" s="8"/>
     </row>
-    <row r="30" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -3134,8 +5814,94 @@
       <c r="Q30" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R30" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="S30" s="9">
+        <v>1</v>
+      </c>
+      <c r="T30" s="9">
+        <v>0.41</v>
+      </c>
+      <c r="U30" s="9">
+        <v>1</v>
+      </c>
+      <c r="V30" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="W30" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X30" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y30" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA30" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AD30" s="9">
+        <v>0.41</v>
+      </c>
+      <c r="AE30" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AF30" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AG30" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AH30" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AI30" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AJ30" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AK30" s="8"/>
+      <c r="AL30" s="8"/>
+      <c r="AM30" s="8"/>
+      <c r="AN30" s="8"/>
+      <c r="AO30" s="8"/>
+      <c r="AP30" s="8"/>
+      <c r="AQ30" s="8"/>
+      <c r="AR30" s="8"/>
+      <c r="AS30" s="8"/>
+      <c r="AT30" s="8"/>
+      <c r="AU30" s="8"/>
+      <c r="AV30" s="8"/>
+      <c r="AW30" s="8"/>
+      <c r="AX30" s="8"/>
+      <c r="AY30" s="8"/>
+      <c r="AZ30" s="8"/>
+      <c r="BA30" s="8"/>
+      <c r="BB30" s="8"/>
+      <c r="BC30" s="8"/>
+      <c r="BD30" s="8"/>
+      <c r="BE30" s="8"/>
+      <c r="BF30" s="8"/>
+      <c r="BG30" s="8"/>
+      <c r="BH30" s="8"/>
+      <c r="BI30" s="8"/>
+      <c r="BJ30" s="8"/>
+      <c r="BK30" s="8"/>
+      <c r="BL30" s="8"/>
+      <c r="BM30" s="8"/>
     </row>
-    <row r="31" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3187,8 +5953,94 @@
       <c r="Q31" s="5" t="s">
         <v>362</v>
       </c>
+      <c r="R31" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="S31" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="T31" s="9">
+        <v>0</v>
+      </c>
+      <c r="U31" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="V31" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W31" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="X31" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="9">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AH31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="8"/>
+      <c r="AL31" s="8"/>
+      <c r="AM31" s="8"/>
+      <c r="AN31" s="8"/>
+      <c r="AO31" s="8"/>
+      <c r="AP31" s="8"/>
+      <c r="AQ31" s="8"/>
+      <c r="AR31" s="8"/>
+      <c r="AS31" s="8"/>
+      <c r="AT31" s="8"/>
+      <c r="AU31" s="8"/>
+      <c r="AV31" s="8"/>
+      <c r="AW31" s="8"/>
+      <c r="AX31" s="8"/>
+      <c r="AY31" s="8"/>
+      <c r="AZ31" s="8"/>
+      <c r="BA31" s="8"/>
+      <c r="BB31" s="8"/>
+      <c r="BC31" s="8"/>
+      <c r="BD31" s="8"/>
+      <c r="BE31" s="8"/>
+      <c r="BF31" s="8"/>
+      <c r="BG31" s="8"/>
+      <c r="BH31" s="8"/>
+      <c r="BI31" s="8"/>
+      <c r="BJ31" s="8"/>
+      <c r="BK31" s="8"/>
+      <c r="BL31" s="8"/>
+      <c r="BM31" s="8"/>
     </row>
-    <row r="32" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -3240,8 +6092,94 @@
       <c r="Q32" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R32" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="S32" s="9">
+        <v>1</v>
+      </c>
+      <c r="T32" s="9">
+        <v>1</v>
+      </c>
+      <c r="U32" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="V32" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W32" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="X32" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD32" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE32" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="AF32" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="AG32" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AH32" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AI32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="8"/>
+      <c r="AL32" s="8"/>
+      <c r="AM32" s="8"/>
+      <c r="AN32" s="8"/>
+      <c r="AO32" s="8"/>
+      <c r="AP32" s="8"/>
+      <c r="AQ32" s="8"/>
+      <c r="AR32" s="8"/>
+      <c r="AS32" s="8"/>
+      <c r="AT32" s="8"/>
+      <c r="AU32" s="8"/>
+      <c r="AV32" s="8"/>
+      <c r="AW32" s="8"/>
+      <c r="AX32" s="8"/>
+      <c r="AY32" s="8"/>
+      <c r="AZ32" s="8"/>
+      <c r="BA32" s="8"/>
+      <c r="BB32" s="8"/>
+      <c r="BC32" s="8"/>
+      <c r="BD32" s="8"/>
+      <c r="BE32" s="8"/>
+      <c r="BF32" s="8"/>
+      <c r="BG32" s="8"/>
+      <c r="BH32" s="8"/>
+      <c r="BI32" s="8"/>
+      <c r="BJ32" s="8"/>
+      <c r="BK32" s="8"/>
+      <c r="BL32" s="8"/>
+      <c r="BM32" s="8"/>
     </row>
-    <row r="33" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -3293,8 +6231,94 @@
       <c r="Q33" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R33" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="S33" s="9">
+        <v>1</v>
+      </c>
+      <c r="T33" s="9">
+        <v>1</v>
+      </c>
+      <c r="U33" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="V33" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W33" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="X33" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD33" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="AF33" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="AG33" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AH33" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AI33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="8"/>
+      <c r="AL33" s="8"/>
+      <c r="AM33" s="8"/>
+      <c r="AN33" s="8"/>
+      <c r="AO33" s="8"/>
+      <c r="AP33" s="8"/>
+      <c r="AQ33" s="8"/>
+      <c r="AR33" s="8"/>
+      <c r="AS33" s="8"/>
+      <c r="AT33" s="8"/>
+      <c r="AU33" s="8"/>
+      <c r="AV33" s="8"/>
+      <c r="AW33" s="8"/>
+      <c r="AX33" s="8"/>
+      <c r="AY33" s="8"/>
+      <c r="AZ33" s="8"/>
+      <c r="BA33" s="8"/>
+      <c r="BB33" s="8"/>
+      <c r="BC33" s="8"/>
+      <c r="BD33" s="8"/>
+      <c r="BE33" s="8"/>
+      <c r="BF33" s="8"/>
+      <c r="BG33" s="8"/>
+      <c r="BH33" s="8"/>
+      <c r="BI33" s="8"/>
+      <c r="BJ33" s="8"/>
+      <c r="BK33" s="8"/>
+      <c r="BL33" s="8"/>
+      <c r="BM33" s="8"/>
     </row>
-    <row r="34" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -3346,8 +6370,94 @@
       <c r="Q34" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R34" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="S34" s="9">
+        <v>1</v>
+      </c>
+      <c r="T34" s="9">
+        <v>1</v>
+      </c>
+      <c r="U34" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W34" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="X34" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD34" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE34" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="AF34" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="AG34" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AH34" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AI34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="8"/>
+      <c r="AL34" s="8"/>
+      <c r="AM34" s="8"/>
+      <c r="AN34" s="8"/>
+      <c r="AO34" s="8"/>
+      <c r="AP34" s="8"/>
+      <c r="AQ34" s="8"/>
+      <c r="AR34" s="8"/>
+      <c r="AS34" s="8"/>
+      <c r="AT34" s="8"/>
+      <c r="AU34" s="8"/>
+      <c r="AV34" s="8"/>
+      <c r="AW34" s="8"/>
+      <c r="AX34" s="8"/>
+      <c r="AY34" s="8"/>
+      <c r="AZ34" s="8"/>
+      <c r="BA34" s="8"/>
+      <c r="BB34" s="8"/>
+      <c r="BC34" s="8"/>
+      <c r="BD34" s="8"/>
+      <c r="BE34" s="8"/>
+      <c r="BF34" s="8"/>
+      <c r="BG34" s="8"/>
+      <c r="BH34" s="8"/>
+      <c r="BI34" s="8"/>
+      <c r="BJ34" s="8"/>
+      <c r="BK34" s="8"/>
+      <c r="BL34" s="8"/>
+      <c r="BM34" s="8"/>
     </row>
-    <row r="35" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -3399,8 +6509,94 @@
       <c r="Q35" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R35" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="S35" s="9">
+        <v>1</v>
+      </c>
+      <c r="T35" s="9">
+        <v>0</v>
+      </c>
+      <c r="U35" s="9">
+        <v>1</v>
+      </c>
+      <c r="V35" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="W35" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="X35" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="Y35" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA35" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB35" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AD35" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AF35" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AG35" s="9">
+        <v>1</v>
+      </c>
+      <c r="AH35" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI35" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AJ35" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AK35" s="8"/>
+      <c r="AL35" s="8"/>
+      <c r="AM35" s="8"/>
+      <c r="AN35" s="8"/>
+      <c r="AO35" s="8"/>
+      <c r="AP35" s="8"/>
+      <c r="AQ35" s="8"/>
+      <c r="AR35" s="8"/>
+      <c r="AS35" s="8"/>
+      <c r="AT35" s="8"/>
+      <c r="AU35" s="8"/>
+      <c r="AV35" s="8"/>
+      <c r="AW35" s="8"/>
+      <c r="AX35" s="8"/>
+      <c r="AY35" s="8"/>
+      <c r="AZ35" s="8"/>
+      <c r="BA35" s="8"/>
+      <c r="BB35" s="8"/>
+      <c r="BC35" s="8"/>
+      <c r="BD35" s="8"/>
+      <c r="BE35" s="8"/>
+      <c r="BF35" s="8"/>
+      <c r="BG35" s="8"/>
+      <c r="BH35" s="8"/>
+      <c r="BI35" s="8"/>
+      <c r="BJ35" s="8"/>
+      <c r="BK35" s="8"/>
+      <c r="BL35" s="8"/>
+      <c r="BM35" s="8"/>
     </row>
-    <row r="36" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -3452,8 +6648,94 @@
       <c r="Q36" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R36" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="S36" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="U36" s="9">
+        <v>1</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AF36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AH36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="8"/>
+      <c r="AL36" s="8"/>
+      <c r="AM36" s="8"/>
+      <c r="AN36" s="8"/>
+      <c r="AO36" s="8"/>
+      <c r="AP36" s="8"/>
+      <c r="AQ36" s="8"/>
+      <c r="AR36" s="8"/>
+      <c r="AS36" s="8"/>
+      <c r="AT36" s="8"/>
+      <c r="AU36" s="8"/>
+      <c r="AV36" s="8"/>
+      <c r="AW36" s="8"/>
+      <c r="AX36" s="8"/>
+      <c r="AY36" s="8"/>
+      <c r="AZ36" s="8"/>
+      <c r="BA36" s="8"/>
+      <c r="BB36" s="8"/>
+      <c r="BC36" s="8"/>
+      <c r="BD36" s="8"/>
+      <c r="BE36" s="8"/>
+      <c r="BF36" s="8"/>
+      <c r="BG36" s="8"/>
+      <c r="BH36" s="8"/>
+      <c r="BI36" s="8"/>
+      <c r="BJ36" s="8"/>
+      <c r="BK36" s="8"/>
+      <c r="BL36" s="8"/>
+      <c r="BM36" s="8"/>
     </row>
-    <row r="37" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -3505,8 +6787,94 @@
       <c r="Q37" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R37" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="S37" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="T37" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U37" s="9">
+        <v>0</v>
+      </c>
+      <c r="V37" s="9">
+        <v>0</v>
+      </c>
+      <c r="W37" s="9">
+        <v>0</v>
+      </c>
+      <c r="X37" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AA37" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AB37" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD37" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE37" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AF37" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AG37" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AH37" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="8"/>
+      <c r="AL37" s="8"/>
+      <c r="AM37" s="8"/>
+      <c r="AN37" s="8"/>
+      <c r="AO37" s="8"/>
+      <c r="AP37" s="8"/>
+      <c r="AQ37" s="8"/>
+      <c r="AR37" s="8"/>
+      <c r="AS37" s="8"/>
+      <c r="AT37" s="8"/>
+      <c r="AU37" s="8"/>
+      <c r="AV37" s="8"/>
+      <c r="AW37" s="8"/>
+      <c r="AX37" s="8"/>
+      <c r="AY37" s="8"/>
+      <c r="AZ37" s="8"/>
+      <c r="BA37" s="8"/>
+      <c r="BB37" s="8"/>
+      <c r="BC37" s="8"/>
+      <c r="BD37" s="8"/>
+      <c r="BE37" s="8"/>
+      <c r="BF37" s="8"/>
+      <c r="BG37" s="8"/>
+      <c r="BH37" s="8"/>
+      <c r="BI37" s="8"/>
+      <c r="BJ37" s="8"/>
+      <c r="BK37" s="8"/>
+      <c r="BL37" s="8"/>
+      <c r="BM37" s="8"/>
     </row>
-    <row r="38" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -3558,8 +6926,94 @@
       <c r="Q38" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R38" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="S38" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="T38" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U38" s="9">
+        <v>0</v>
+      </c>
+      <c r="V38" s="9">
+        <v>0</v>
+      </c>
+      <c r="W38" s="9">
+        <v>0</v>
+      </c>
+      <c r="X38" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AA38" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AB38" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD38" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE38" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AF38" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AG38" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AH38" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="8"/>
+      <c r="AL38" s="8"/>
+      <c r="AM38" s="8"/>
+      <c r="AN38" s="8"/>
+      <c r="AO38" s="8"/>
+      <c r="AP38" s="8"/>
+      <c r="AQ38" s="8"/>
+      <c r="AR38" s="8"/>
+      <c r="AS38" s="8"/>
+      <c r="AT38" s="8"/>
+      <c r="AU38" s="8"/>
+      <c r="AV38" s="8"/>
+      <c r="AW38" s="8"/>
+      <c r="AX38" s="8"/>
+      <c r="AY38" s="8"/>
+      <c r="AZ38" s="8"/>
+      <c r="BA38" s="8"/>
+      <c r="BB38" s="8"/>
+      <c r="BC38" s="8"/>
+      <c r="BD38" s="8"/>
+      <c r="BE38" s="8"/>
+      <c r="BF38" s="8"/>
+      <c r="BG38" s="8"/>
+      <c r="BH38" s="8"/>
+      <c r="BI38" s="8"/>
+      <c r="BJ38" s="8"/>
+      <c r="BK38" s="8"/>
+      <c r="BL38" s="8"/>
+      <c r="BM38" s="8"/>
     </row>
-    <row r="39" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -3611,8 +7065,94 @@
       <c r="Q39" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R39" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="S39" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD39" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE39" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AF39" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AG39" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AH39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="8"/>
+      <c r="AL39" s="8"/>
+      <c r="AM39" s="8"/>
+      <c r="AN39" s="8"/>
+      <c r="AO39" s="8"/>
+      <c r="AP39" s="8"/>
+      <c r="AQ39" s="8"/>
+      <c r="AR39" s="8"/>
+      <c r="AS39" s="8"/>
+      <c r="AT39" s="8"/>
+      <c r="AU39" s="8"/>
+      <c r="AV39" s="8"/>
+      <c r="AW39" s="8"/>
+      <c r="AX39" s="8"/>
+      <c r="AY39" s="8"/>
+      <c r="AZ39" s="8"/>
+      <c r="BA39" s="8"/>
+      <c r="BB39" s="8"/>
+      <c r="BC39" s="8"/>
+      <c r="BD39" s="8"/>
+      <c r="BE39" s="8"/>
+      <c r="BF39" s="8"/>
+      <c r="BG39" s="8"/>
+      <c r="BH39" s="8"/>
+      <c r="BI39" s="8"/>
+      <c r="BJ39" s="8"/>
+      <c r="BK39" s="8"/>
+      <c r="BL39" s="8"/>
+      <c r="BM39" s="8"/>
     </row>
-    <row r="40" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -3664,8 +7204,94 @@
       <c r="Q40" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R40" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="S40" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="T40" s="9">
+        <v>0</v>
+      </c>
+      <c r="U40" s="9">
+        <v>0</v>
+      </c>
+      <c r="V40" s="9">
+        <v>0</v>
+      </c>
+      <c r="W40" s="9">
+        <v>0</v>
+      </c>
+      <c r="X40" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK40" s="8"/>
+      <c r="AL40" s="8"/>
+      <c r="AM40" s="8"/>
+      <c r="AN40" s="8"/>
+      <c r="AO40" s="8"/>
+      <c r="AP40" s="8"/>
+      <c r="AQ40" s="8"/>
+      <c r="AR40" s="8"/>
+      <c r="AS40" s="8"/>
+      <c r="AT40" s="8"/>
+      <c r="AU40" s="8"/>
+      <c r="AV40" s="8"/>
+      <c r="AW40" s="8"/>
+      <c r="AX40" s="8"/>
+      <c r="AY40" s="8"/>
+      <c r="AZ40" s="8"/>
+      <c r="BA40" s="8"/>
+      <c r="BB40" s="8"/>
+      <c r="BC40" s="8"/>
+      <c r="BD40" s="8"/>
+      <c r="BE40" s="8"/>
+      <c r="BF40" s="8"/>
+      <c r="BG40" s="8"/>
+      <c r="BH40" s="8"/>
+      <c r="BI40" s="8"/>
+      <c r="BJ40" s="8"/>
+      <c r="BK40" s="8"/>
+      <c r="BL40" s="8"/>
+      <c r="BM40" s="8"/>
     </row>
-    <row r="41" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -3717,14 +7343,96 @@
       <c r="Q41" s="5" t="s">
         <v>363</v>
       </c>
+      <c r="R41" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="S41" s="9">
+        <v>1</v>
+      </c>
+      <c r="T41" s="9">
+        <v>1</v>
+      </c>
+      <c r="U41" s="9">
+        <v>1</v>
+      </c>
+      <c r="V41" s="9">
+        <v>1</v>
+      </c>
+      <c r="W41" s="9">
+        <v>1</v>
+      </c>
+      <c r="X41" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z41" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AA41" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AB41" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AD41" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="AE41" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AF41" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AG41" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AH41" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AI41" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="8"/>
+      <c r="AL41" s="8"/>
+      <c r="AM41" s="8"/>
+      <c r="AN41" s="8"/>
+      <c r="AO41" s="8"/>
+      <c r="AP41" s="8"/>
+      <c r="AQ41" s="8"/>
+      <c r="AR41" s="8"/>
+      <c r="AS41" s="8"/>
+      <c r="AT41" s="8"/>
+      <c r="AU41" s="8"/>
+      <c r="AV41" s="8"/>
+      <c r="AW41" s="8"/>
+      <c r="AX41" s="8"/>
+      <c r="AY41" s="8"/>
+      <c r="AZ41" s="8"/>
+      <c r="BA41" s="8"/>
+      <c r="BB41" s="8"/>
+      <c r="BC41" s="8"/>
+      <c r="BD41" s="8"/>
+      <c r="BE41" s="8"/>
+      <c r="BF41" s="8"/>
+      <c r="BG41" s="8"/>
+      <c r="BH41" s="8"/>
+      <c r="BI41" s="8"/>
+      <c r="BJ41" s="8"/>
+      <c r="BK41" s="8"/>
+      <c r="BL41" s="8"/>
+      <c r="BM41" s="8"/>
     </row>
-    <row r="42" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:65" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <autoFilter ref="A1:Q1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q41">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:R1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3732,106 +7440,106 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
         <v>34</v>
       </c>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -1029,7 +1029,7 @@
     <t>101.7 MW / 305.1 MWh</t>
   </si>
   <si>
-    <t>$381,545,675.00</t>
+    <t>$925,310,833.00</t>
   </si>
   <si>
     <t>CONCEPCIÓN MENDIZÁBAL MENDOZA FASE II</t>
@@ -1041,13 +1041,13 @@
     <t>54 MW / 162 MWh</t>
   </si>
   <si>
-    <t>$198,977,154.00</t>
+    <t>$925,310,833.00</t>
   </si>
   <si>
     <t>CONCEPCIÓN MENDIZÁBAL MENDOZA FASE III</t>
   </si>
   <si>
-    <t>$376,737,492.00</t>
+    <t>$925,310,833.00</t>
   </si>
   <si>
     <t>35.00%</t>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -1029,25 +1029,25 @@
     <t>101.7 MW / 305.1 MWh</t>
   </si>
   <si>
+    <t>VER FASE II</t>
+  </si>
+  <si>
+    <t>CONCEPCIÓN MENDIZÁBAL MENDOZA FASE II</t>
+  </si>
+  <si>
+    <t>180 MW</t>
+  </si>
+  <si>
+    <t>54 MW / 162 MWh</t>
+  </si>
+  <si>
     <t>$925,310,833.00</t>
   </si>
   <si>
-    <t>CONCEPCIÓN MENDIZÁBAL MENDOZA FASE II</t>
-  </si>
-  <si>
-    <t>180 MW</t>
-  </si>
-  <si>
-    <t>54 MW / 162 MWh</t>
-  </si>
-  <si>
-    <t>$925,310,833.00</t>
-  </si>
-  <si>
     <t>CONCEPCIÓN MENDIZÁBAL MENDOZA FASE III</t>
   </si>
   <si>
-    <t>$925,310,833.00</t>
+    <t>VER FASE II</t>
   </si>
   <si>
     <t>35.00%</t>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CPEL-PROYECTOS\MIXTOS\REUNIONES_SEMANALES_RESPALDO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29F8FE8-67FC-4850-8D5A-9C0CFCC0A3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B592B5F0-E09C-4CFB-B497-7D47784F0540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="724" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2868,13 +2868,13 @@
         <v>122</v>
       </c>
       <c r="AD6" s="6">
-        <v>0.77000000000000024</v>
+        <v>0.80000000000000027</v>
       </c>
       <c r="AE6" s="6">
-        <v>0.52500000000000002</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="AF6" s="6">
-        <v>0.7210000000000002</v>
+        <v>0.75100000000000022</v>
       </c>
       <c r="AG6" s="6">
         <v>1</v>
@@ -2904,7 +2904,7 @@
         <v>0.9</v>
       </c>
       <c r="AP6" s="6">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AQ6" s="6">
         <v>0.9</v>
@@ -3822,13 +3822,13 @@
         <v>158</v>
       </c>
       <c r="AD12" s="6">
-        <v>0.83500000000000019</v>
+        <v>0.84000000000000019</v>
       </c>
       <c r="AE12" s="6">
-        <v>0.7300000000000002</v>
+        <v>0.73500000000000021</v>
       </c>
       <c r="AF12" s="6">
-        <v>0.81400000000000017</v>
+        <v>0.81900000000000017</v>
       </c>
       <c r="AG12" s="6">
         <v>1</v>
@@ -3858,7 +3858,7 @@
         <v>1</v>
       </c>
       <c r="AP12" s="6">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="AQ12" s="6">
         <v>0.6</v>
@@ -3981,13 +3981,13 @@
         <v>30</v>
       </c>
       <c r="AD13" s="6">
-        <v>0.77000000000000024</v>
+        <v>0.75000000000000022</v>
       </c>
       <c r="AE13" s="6">
-        <v>0.6050000000000002</v>
+        <v>0.58500000000000019</v>
       </c>
       <c r="AF13" s="6">
-        <v>0.73700000000000032</v>
+        <v>0.7170000000000003</v>
       </c>
       <c r="AG13" s="6">
         <v>1</v>
@@ -4017,7 +4017,7 @@
         <v>0.8</v>
       </c>
       <c r="AP13" s="6">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AQ13" s="6">
         <v>0.8</v>
@@ -5094,13 +5094,13 @@
         <v>28</v>
       </c>
       <c r="AD20" s="6">
-        <v>0.77000000000000024</v>
+        <v>0.75000000000000022</v>
       </c>
       <c r="AE20" s="6">
-        <v>0.77000000000000024</v>
+        <v>0.75000000000000022</v>
       </c>
       <c r="AF20" s="6">
-        <v>0.77000000000000024</v>
+        <v>0.75000000000000022</v>
       </c>
       <c r="AG20" s="6">
         <v>0.8</v>
@@ -5130,7 +5130,7 @@
         <v>0.8</v>
       </c>
       <c r="AP20" s="6">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AQ20" s="6">
         <v>0.5</v>
@@ -5253,13 +5253,13 @@
         <v>47</v>
       </c>
       <c r="AD21" s="6">
-        <v>0.7300000000000002</v>
+        <v>0.74000000000000021</v>
       </c>
       <c r="AE21" s="6">
-        <v>0.63000000000000012</v>
+        <v>0.64000000000000012</v>
       </c>
       <c r="AF21" s="6">
-        <v>0.71000000000000019</v>
+        <v>0.7200000000000002</v>
       </c>
       <c r="AG21" s="6">
         <v>1</v>
@@ -5289,7 +5289,7 @@
         <v>1</v>
       </c>
       <c r="AP21" s="6">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AQ21" s="6">
         <v>0.5</v>
@@ -5412,13 +5412,13 @@
         <v>49</v>
       </c>
       <c r="AD22" s="6">
+        <v>0.7200000000000002</v>
+      </c>
+      <c r="AE22" s="6">
+        <v>0.67000000000000015</v>
+      </c>
+      <c r="AF22" s="6">
         <v>0.71000000000000019</v>
-      </c>
-      <c r="AE22" s="6">
-        <v>0.66000000000000014</v>
-      </c>
-      <c r="AF22" s="6">
-        <v>0.70000000000000018</v>
       </c>
       <c r="AG22" s="6">
         <v>1</v>
@@ -5448,7 +5448,7 @@
         <v>1</v>
       </c>
       <c r="AP22" s="6">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AQ22" s="6">
         <v>0.5</v>
@@ -5889,13 +5889,13 @@
         <v>223</v>
       </c>
       <c r="AD25" s="6">
-        <v>0.81000000000000028</v>
+        <v>0.79000000000000026</v>
       </c>
       <c r="AE25" s="6">
-        <v>0.55500000000000005</v>
+        <v>0.53500000000000014</v>
       </c>
       <c r="AF25" s="6">
-        <v>0.75900000000000023</v>
+        <v>0.73900000000000032</v>
       </c>
       <c r="AG25" s="6">
         <v>0.9</v>
@@ -5925,7 +5925,7 @@
         <v>0.8</v>
       </c>
       <c r="AP25" s="6">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AQ25" s="6">
         <v>1</v>
@@ -6684,13 +6684,13 @@
         <v>32</v>
       </c>
       <c r="AD30" s="6">
-        <v>0.79000000000000026</v>
+        <v>0.82000000000000028</v>
       </c>
       <c r="AE30" s="6">
-        <v>0.67000000000000015</v>
+        <v>0.70000000000000018</v>
       </c>
       <c r="AF30" s="6">
-        <v>0.76600000000000024</v>
+        <v>0.79600000000000026</v>
       </c>
       <c r="AG30" s="6">
         <v>1</v>
@@ -6720,7 +6720,7 @@
         <v>1</v>
       </c>
       <c r="AP30" s="6">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AQ30" s="6">
         <v>0.7</v>
@@ -7479,13 +7479,13 @@
         <v>20</v>
       </c>
       <c r="AD35" s="6">
-        <v>0.8450000000000002</v>
+        <v>0.87500000000000022</v>
       </c>
       <c r="AE35" s="6">
-        <v>0.77000000000000024</v>
+        <v>0.80000000000000027</v>
       </c>
       <c r="AF35" s="6">
-        <v>0.83000000000000018</v>
+        <v>0.86000000000000021</v>
       </c>
       <c r="AG35" s="6">
         <v>1</v>
@@ -7515,7 +7515,7 @@
         <v>1</v>
       </c>
       <c r="AP35" s="6">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AQ35" s="6">
         <v>0.9</v>
@@ -8602,11 +8602,7 @@
       <c r="P53" s="51"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AX1" xr:uid="{782B78D9-47D9-4EBC-8BEA-A91BF1F0B98F}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AX41">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:AX1" xr:uid="{782B78D9-47D9-4EBC-8BEA-A91BF1F0B98F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="597" r:id="rId1"/>
 </worksheet>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CPEL-PROYECTOS\MIXTOS\REUNIONES_SEMANALES_RESPALDO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B592B5F0-E09C-4CFB-B497-7D47784F0540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E68E7F5-32D0-4D85-9490-A7979854667F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="724" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2192,31 +2192,31 @@
         <v>0.3</v>
       </c>
       <c r="S2" s="3">
-        <f t="shared" ref="S2:S41" si="0">Z2*R2</f>
+        <f>Z2*R2</f>
         <v>24</v>
       </c>
       <c r="T2" s="3">
-        <f t="shared" ref="T2:T41" si="1">S2*3</f>
+        <f>S2*3</f>
         <v>72</v>
       </c>
       <c r="U2" s="5">
-        <f t="shared" ref="U2:U41" si="2">AA2/Z2</f>
+        <f>AA2/Z2</f>
         <v>0.3</v>
       </c>
       <c r="V2" s="3">
-        <f t="shared" ref="V2:V41" si="3">Z2*U2</f>
+        <f>Z2*U2</f>
         <v>24</v>
       </c>
       <c r="W2" s="3">
-        <f t="shared" ref="W2:W41" si="4">V2*3</f>
+        <f>V2*3</f>
         <v>72</v>
       </c>
       <c r="X2" s="4">
-        <f t="shared" ref="X2:X41" si="5">O2/Z2</f>
+        <f>O2/Z2</f>
         <v>1174138.6675</v>
       </c>
       <c r="Y2" s="4">
-        <f t="shared" ref="Y2:Y41" si="6">O2/AA2</f>
+        <f>O2/AA2</f>
         <v>3913795.5583333336</v>
       </c>
       <c r="Z2" s="3">
@@ -2351,31 +2351,31 @@
         <v>0.3</v>
       </c>
       <c r="S3" s="3">
-        <f t="shared" si="0"/>
+        <f>Z3*R3</f>
         <v>90.45</v>
       </c>
       <c r="T3" s="3">
-        <f t="shared" si="1"/>
+        <f>S3*3</f>
         <v>271.35000000000002</v>
       </c>
       <c r="U3" s="5">
-        <f t="shared" si="2"/>
+        <f>AA3/Z3</f>
         <v>0.30016583747927034</v>
       </c>
       <c r="V3" s="3">
-        <f t="shared" si="3"/>
+        <f>Z3*U3</f>
         <v>90.5</v>
       </c>
       <c r="W3" s="3">
-        <f t="shared" si="4"/>
+        <f>V3*3</f>
         <v>271.5</v>
       </c>
       <c r="X3" s="4">
-        <f t="shared" si="5"/>
+        <f>O3/Z3</f>
         <v>1697290.8441127695</v>
       </c>
       <c r="Y3" s="4">
-        <f t="shared" si="6"/>
+        <f>O3/AA3</f>
         <v>5654510.3812154699</v>
       </c>
       <c r="Z3" s="3">
@@ -2510,31 +2510,31 @@
         <v>0.3</v>
       </c>
       <c r="S4" s="3">
-        <f t="shared" si="0"/>
+        <f>Z4*R4</f>
         <v>60</v>
       </c>
       <c r="T4" s="3">
-        <f t="shared" si="1"/>
+        <f>S4*3</f>
         <v>180</v>
       </c>
       <c r="U4" s="5">
-        <f t="shared" si="2"/>
+        <f>AA4/Z4</f>
         <v>0.32500000000000001</v>
       </c>
       <c r="V4" s="3">
-        <f t="shared" si="3"/>
+        <f>Z4*U4</f>
         <v>65</v>
       </c>
       <c r="W4" s="3">
-        <f t="shared" si="4"/>
+        <f>V4*3</f>
         <v>195</v>
       </c>
       <c r="X4" s="4">
-        <f t="shared" si="5"/>
+        <f>O4/Z4</f>
         <v>1342145.7775000001</v>
       </c>
       <c r="Y4" s="4">
-        <f t="shared" si="6"/>
+        <f>O4/AA4</f>
         <v>4129679.3153846152</v>
       </c>
       <c r="Z4" s="3">
@@ -2669,31 +2669,31 @@
         <v>0.3</v>
       </c>
       <c r="S5" s="3">
-        <f t="shared" si="0"/>
+        <f>Z5*R5</f>
         <v>27</v>
       </c>
       <c r="T5" s="3">
-        <f t="shared" si="1"/>
+        <f>S5*3</f>
         <v>81</v>
       </c>
       <c r="U5" s="5">
-        <f t="shared" si="2"/>
+        <f>AA5/Z5</f>
         <v>1</v>
       </c>
       <c r="V5" s="3">
-        <f t="shared" si="3"/>
+        <f>Z5*U5</f>
         <v>90</v>
       </c>
       <c r="W5" s="3">
-        <f t="shared" si="4"/>
+        <f>V5*3</f>
         <v>270</v>
       </c>
       <c r="X5" s="4">
-        <f t="shared" si="5"/>
+        <f>O5/Z5</f>
         <v>1692535.4111111111</v>
       </c>
       <c r="Y5" s="4">
-        <f t="shared" si="6"/>
+        <f>O5/AA5</f>
         <v>1692535.4111111111</v>
       </c>
       <c r="Z5" s="3">
@@ -2828,31 +2828,31 @@
         <v>0.3</v>
       </c>
       <c r="S6" s="3">
-        <f t="shared" si="0"/>
+        <f>Z6*R6</f>
         <v>16.2</v>
       </c>
       <c r="T6" s="3">
-        <f t="shared" si="1"/>
+        <f>S6*3</f>
         <v>48.599999999999994</v>
       </c>
       <c r="U6" s="5">
-        <f t="shared" si="2"/>
+        <f>AA6/Z6</f>
         <v>0.34074074074074073</v>
       </c>
       <c r="V6" s="3">
-        <f t="shared" si="3"/>
+        <f>Z6*U6</f>
         <v>18.399999999999999</v>
       </c>
       <c r="W6" s="3">
-        <f t="shared" si="4"/>
+        <f>V6*3</f>
         <v>55.199999999999996</v>
       </c>
       <c r="X6" s="4">
-        <f t="shared" si="5"/>
+        <f>O6/Z6</f>
         <v>1116269.9592592593</v>
       </c>
       <c r="Y6" s="4">
-        <f t="shared" si="6"/>
+        <f>O6/AA6</f>
         <v>3276009.6630434785</v>
       </c>
       <c r="Z6" s="3">
@@ -2868,13 +2868,13 @@
         <v>122</v>
       </c>
       <c r="AD6" s="6">
-        <v>0.80000000000000027</v>
+        <v>0.77000000000000024</v>
       </c>
       <c r="AE6" s="6">
-        <v>0.55500000000000005</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="AF6" s="6">
-        <v>0.75100000000000022</v>
+        <v>0.7210000000000002</v>
       </c>
       <c r="AG6" s="6">
         <v>1</v>
@@ -2904,7 +2904,7 @@
         <v>0.9</v>
       </c>
       <c r="AP6" s="6">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AQ6" s="6">
         <v>0.9</v>
@@ -2987,31 +2987,31 @@
         <v>0.3</v>
       </c>
       <c r="S7" s="3">
-        <f t="shared" si="0"/>
+        <f>Z7*R7</f>
         <v>150.9</v>
       </c>
       <c r="T7" s="3">
-        <f t="shared" si="1"/>
+        <f>S7*3</f>
         <v>452.70000000000005</v>
       </c>
       <c r="U7" s="5">
-        <f t="shared" si="2"/>
+        <f>AA7/Z7</f>
         <v>0.30019880715705766</v>
       </c>
       <c r="V7" s="3">
-        <f t="shared" si="3"/>
+        <f>Z7*U7</f>
         <v>151</v>
       </c>
       <c r="W7" s="3">
-        <f t="shared" si="4"/>
+        <f>V7*3</f>
         <v>453</v>
       </c>
       <c r="X7" s="4">
-        <f t="shared" si="5"/>
+        <f>O7/Z7</f>
         <v>1591100.8155069584</v>
       </c>
       <c r="Y7" s="4">
-        <f t="shared" si="6"/>
+        <f>O7/AA7</f>
         <v>5300157.0211920533</v>
       </c>
       <c r="Z7" s="3">
@@ -3146,31 +3146,31 @@
         <v>0.3</v>
       </c>
       <c r="S8" s="3">
-        <f t="shared" si="0"/>
+        <f>Z8*R8</f>
         <v>140.4</v>
       </c>
       <c r="T8" s="3">
-        <f t="shared" si="1"/>
+        <f>S8*3</f>
         <v>421.20000000000005</v>
       </c>
       <c r="U8" s="5">
-        <f t="shared" si="2"/>
+        <f>AA8/Z8</f>
         <v>0.3</v>
       </c>
       <c r="V8" s="3">
-        <f t="shared" si="3"/>
+        <f>Z8*U8</f>
         <v>140.4</v>
       </c>
       <c r="W8" s="3">
-        <f t="shared" si="4"/>
+        <f>V8*3</f>
         <v>421.20000000000005</v>
       </c>
       <c r="X8" s="4">
-        <f t="shared" si="5"/>
+        <f>O8/Z8</f>
         <v>1632951.1431623932</v>
       </c>
       <c r="Y8" s="4">
-        <f t="shared" si="6"/>
+        <f>O8/AA8</f>
         <v>5443170.4772079773</v>
       </c>
       <c r="Z8" s="3">
@@ -3305,31 +3305,31 @@
         <v>0.3</v>
       </c>
       <c r="S9" s="3">
-        <f t="shared" si="0"/>
+        <f>Z9*R9</f>
         <v>22.5</v>
       </c>
       <c r="T9" s="3">
-        <f t="shared" si="1"/>
+        <f>S9*3</f>
         <v>67.5</v>
       </c>
       <c r="U9" s="5">
-        <f t="shared" si="2"/>
+        <f>AA9/Z9</f>
         <v>0.3</v>
       </c>
       <c r="V9" s="3">
-        <f t="shared" si="3"/>
+        <f>Z9*U9</f>
         <v>22.5</v>
       </c>
       <c r="W9" s="3">
-        <f t="shared" si="4"/>
+        <f>V9*3</f>
         <v>67.5</v>
       </c>
       <c r="X9" s="4">
-        <f t="shared" si="5"/>
+        <f>O9/Z9</f>
         <v>1044594.5066666667</v>
       </c>
       <c r="Y9" s="4">
-        <f t="shared" si="6"/>
+        <f>O9/AA9</f>
         <v>3481981.6888888888</v>
       </c>
       <c r="Z9" s="3">
@@ -3464,31 +3464,31 @@
         <v>0.3</v>
       </c>
       <c r="S10" s="3">
-        <f t="shared" si="0"/>
+        <f>Z10*R10</f>
         <v>33</v>
       </c>
       <c r="T10" s="3">
-        <f t="shared" si="1"/>
+        <f>S10*3</f>
         <v>99</v>
       </c>
       <c r="U10" s="5">
-        <f t="shared" si="2"/>
+        <f>AA10/Z10</f>
         <v>0.3</v>
       </c>
       <c r="V10" s="3">
-        <f t="shared" si="3"/>
+        <f>Z10*U10</f>
         <v>33</v>
       </c>
       <c r="W10" s="3">
-        <f t="shared" si="4"/>
+        <f>V10*3</f>
         <v>99</v>
       </c>
       <c r="X10" s="4">
-        <f t="shared" si="5"/>
+        <f>O10/Z10</f>
         <v>1090311.6636363636</v>
       </c>
       <c r="Y10" s="4">
-        <f t="shared" si="6"/>
+        <f>O10/AA10</f>
         <v>3634372.2121212119</v>
       </c>
       <c r="Z10" s="3">
@@ -3623,31 +3623,31 @@
         <v>0.3</v>
       </c>
       <c r="S11" s="3">
-        <f t="shared" si="0"/>
+        <f>Z11*R11</f>
         <v>5.76</v>
       </c>
       <c r="T11" s="3">
-        <f t="shared" si="1"/>
+        <f>S11*3</f>
         <v>17.28</v>
       </c>
       <c r="U11" s="5">
-        <f t="shared" si="2"/>
+        <f>AA11/Z11</f>
         <v>0.31770833333333331</v>
       </c>
       <c r="V11" s="3">
-        <f t="shared" si="3"/>
+        <f>Z11*U11</f>
         <v>6.1</v>
       </c>
       <c r="W11" s="3">
-        <f t="shared" si="4"/>
+        <f>V11*3</f>
         <v>18.299999999999997</v>
       </c>
       <c r="X11" s="4">
-        <f t="shared" si="5"/>
+        <f>O11/Z11</f>
         <v>977532.88020833337</v>
       </c>
       <c r="Y11" s="4">
-        <f t="shared" si="6"/>
+        <f>O11/AA11</f>
         <v>3076824.8032786888</v>
       </c>
       <c r="Z11" s="3">
@@ -3782,31 +3782,31 @@
         <v>0.3</v>
       </c>
       <c r="S12" s="3">
-        <f t="shared" si="0"/>
+        <f>Z12*R12</f>
         <v>36.96</v>
       </c>
       <c r="T12" s="3">
-        <f t="shared" si="1"/>
+        <f>S12*3</f>
         <v>110.88</v>
       </c>
       <c r="U12" s="5">
-        <f t="shared" si="2"/>
+        <f>AA12/Z12</f>
         <v>0.3</v>
       </c>
       <c r="V12" s="3">
-        <f t="shared" si="3"/>
+        <f>Z12*U12</f>
         <v>36.96</v>
       </c>
       <c r="W12" s="3">
-        <f t="shared" si="4"/>
+        <f>V12*3</f>
         <v>110.88</v>
       </c>
       <c r="X12" s="4">
-        <f t="shared" si="5"/>
+        <f>O12/Z12</f>
         <v>1290017.9886363635</v>
       </c>
       <c r="Y12" s="4">
-        <f t="shared" si="6"/>
+        <f>O12/AA12</f>
         <v>4300059.9621212119</v>
       </c>
       <c r="Z12" s="3">
@@ -3822,13 +3822,13 @@
         <v>158</v>
       </c>
       <c r="AD12" s="6">
-        <v>0.84000000000000019</v>
+        <v>0.83500000000000019</v>
       </c>
       <c r="AE12" s="6">
-        <v>0.73500000000000021</v>
+        <v>0.7300000000000002</v>
       </c>
       <c r="AF12" s="6">
-        <v>0.81900000000000017</v>
+        <v>0.81400000000000017</v>
       </c>
       <c r="AG12" s="6">
         <v>1</v>
@@ -3858,7 +3858,7 @@
         <v>1</v>
       </c>
       <c r="AP12" s="6">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="AQ12" s="6">
         <v>0.6</v>
@@ -3941,31 +3941,31 @@
         <v>0.3</v>
       </c>
       <c r="S13" s="3">
-        <f t="shared" si="0"/>
+        <f>Z13*R13</f>
         <v>136.70400000000001</v>
       </c>
       <c r="T13" s="3">
-        <f t="shared" si="1"/>
+        <f>S13*3</f>
         <v>410.11200000000002</v>
       </c>
       <c r="U13" s="5">
-        <f t="shared" si="2"/>
+        <f>AA13/Z13</f>
         <v>0.29999122191011235</v>
       </c>
       <c r="V13" s="3">
-        <f t="shared" si="3"/>
+        <f>Z13*U13</f>
         <v>136.69999999999999</v>
       </c>
       <c r="W13" s="3">
-        <f t="shared" si="4"/>
+        <f>V13*3</f>
         <v>410.09999999999997</v>
       </c>
       <c r="X13" s="4">
-        <f t="shared" si="5"/>
+        <f>O13/Z13</f>
         <v>923518.54634831462</v>
       </c>
       <c r="Y13" s="4">
-        <f t="shared" si="6"/>
+        <f>O13/AA13</f>
         <v>3078485.2318946598</v>
       </c>
       <c r="Z13" s="3">
@@ -3981,13 +3981,13 @@
         <v>30</v>
       </c>
       <c r="AD13" s="6">
-        <v>0.75000000000000022</v>
+        <v>0.77000000000000024</v>
       </c>
       <c r="AE13" s="6">
-        <v>0.58500000000000019</v>
+        <v>0.6050000000000002</v>
       </c>
       <c r="AF13" s="6">
-        <v>0.7170000000000003</v>
+        <v>0.73700000000000032</v>
       </c>
       <c r="AG13" s="6">
         <v>1</v>
@@ -4017,7 +4017,7 @@
         <v>0.8</v>
       </c>
       <c r="AP13" s="6">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AQ13" s="6">
         <v>0.8</v>
@@ -4100,31 +4100,31 @@
         <v>0.3</v>
       </c>
       <c r="S14" s="3">
-        <f t="shared" si="0"/>
+        <f>Z14*R14</f>
         <v>45</v>
       </c>
       <c r="T14" s="3">
-        <f t="shared" si="1"/>
+        <f>S14*3</f>
         <v>135</v>
       </c>
       <c r="U14" s="5">
-        <f t="shared" si="2"/>
+        <f>AA14/Z14</f>
         <v>0.3</v>
       </c>
       <c r="V14" s="3">
-        <f t="shared" si="3"/>
+        <f>Z14*U14</f>
         <v>45</v>
       </c>
       <c r="W14" s="3">
-        <f t="shared" si="4"/>
+        <f>V14*3</f>
         <v>135</v>
       </c>
       <c r="X14" s="4">
-        <f t="shared" si="5"/>
+        <f>O14/Z14</f>
         <v>1102348.6546666666</v>
       </c>
       <c r="Y14" s="4">
-        <f t="shared" si="6"/>
+        <f>O14/AA14</f>
         <v>3674495.5155555555</v>
       </c>
       <c r="Z14" s="3">
@@ -4259,31 +4259,31 @@
         <v>0.3</v>
       </c>
       <c r="S15" s="3">
-        <f t="shared" si="0"/>
+        <f>Z15*R15</f>
         <v>51</v>
       </c>
       <c r="T15" s="3">
-        <f t="shared" si="1"/>
+        <f>S15*3</f>
         <v>153</v>
       </c>
       <c r="U15" s="5">
-        <f t="shared" si="2"/>
+        <f>AA15/Z15</f>
         <v>0.3</v>
       </c>
       <c r="V15" s="3">
-        <f t="shared" si="3"/>
+        <f>Z15*U15</f>
         <v>51</v>
       </c>
       <c r="W15" s="3">
-        <f t="shared" si="4"/>
+        <f>V15*3</f>
         <v>153</v>
       </c>
       <c r="X15" s="4">
-        <f t="shared" si="5"/>
+        <f>O15/Z15</f>
         <v>1243209.5547058824</v>
       </c>
       <c r="Y15" s="4">
-        <f t="shared" si="6"/>
+        <f>O15/AA15</f>
         <v>4144031.849019608</v>
       </c>
       <c r="Z15" s="3">
@@ -4418,31 +4418,31 @@
         <v>0.3</v>
       </c>
       <c r="S16" s="3">
-        <f t="shared" si="0"/>
+        <f>Z16*R16</f>
         <v>36</v>
       </c>
       <c r="T16" s="3">
-        <f t="shared" si="1"/>
+        <f>S16*3</f>
         <v>108</v>
       </c>
       <c r="U16" s="5">
-        <f t="shared" si="2"/>
+        <f>AA16/Z16</f>
         <v>0.3</v>
       </c>
       <c r="V16" s="3">
-        <f t="shared" si="3"/>
+        <f>Z16*U16</f>
         <v>36</v>
       </c>
       <c r="W16" s="3">
-        <f t="shared" si="4"/>
+        <f>V16*3</f>
         <v>108</v>
       </c>
       <c r="X16" s="4">
-        <f t="shared" si="5"/>
+        <f>O16/Z16</f>
         <v>1485070.3158333334</v>
       </c>
       <c r="Y16" s="4">
-        <f t="shared" si="6"/>
+        <f>O16/AA16</f>
         <v>4950234.3861111114</v>
       </c>
       <c r="Z16" s="3">
@@ -4577,31 +4577,31 @@
         <v>0.3</v>
       </c>
       <c r="S17" s="3">
-        <f t="shared" si="0"/>
+        <f>Z17*R17</f>
         <v>19.8</v>
       </c>
       <c r="T17" s="3">
-        <f t="shared" si="1"/>
+        <f>S17*3</f>
         <v>59.400000000000006</v>
       </c>
       <c r="U17" s="5">
-        <f t="shared" si="2"/>
+        <f>AA17/Z17</f>
         <v>0.3</v>
       </c>
       <c r="V17" s="3">
-        <f t="shared" si="3"/>
+        <f>Z17*U17</f>
         <v>19.8</v>
       </c>
       <c r="W17" s="3">
-        <f t="shared" si="4"/>
+        <f>V17*3</f>
         <v>59.400000000000006</v>
       </c>
       <c r="X17" s="4">
-        <f t="shared" si="5"/>
+        <f>O17/Z17</f>
         <v>1491807.1409090909</v>
       </c>
       <c r="Y17" s="4">
-        <f t="shared" si="6"/>
+        <f>O17/AA17</f>
         <v>4972690.4696969697</v>
       </c>
       <c r="Z17" s="3">
@@ -4736,31 +4736,31 @@
         <v>0.3</v>
       </c>
       <c r="S18" s="3">
-        <f t="shared" si="0"/>
+        <f>Z18*R18</f>
         <v>29.46</v>
       </c>
       <c r="T18" s="3">
-        <f t="shared" si="1"/>
+        <f>S18*3</f>
         <v>88.38</v>
       </c>
       <c r="U18" s="5">
-        <f t="shared" si="2"/>
+        <f>AA18/Z18</f>
         <v>0.3</v>
       </c>
       <c r="V18" s="3">
-        <f t="shared" si="3"/>
+        <f>Z18*U18</f>
         <v>29.46</v>
       </c>
       <c r="W18" s="3">
-        <f t="shared" si="4"/>
+        <f>V18*3</f>
         <v>88.38</v>
       </c>
       <c r="X18" s="4">
-        <f t="shared" si="5"/>
+        <f>O18/Z18</f>
         <v>923875.08044806519</v>
       </c>
       <c r="Y18" s="4">
-        <f t="shared" si="6"/>
+        <f>O18/AA18</f>
         <v>3079583.6014935505</v>
       </c>
       <c r="Z18" s="3">
@@ -4895,31 +4895,31 @@
         <v>0.3</v>
       </c>
       <c r="S19" s="3">
-        <f t="shared" si="0"/>
+        <f>Z19*R19</f>
         <v>90</v>
       </c>
       <c r="T19" s="3">
-        <f t="shared" si="1"/>
+        <f>S19*3</f>
         <v>270</v>
       </c>
       <c r="U19" s="5">
-        <f t="shared" si="2"/>
+        <f>AA19/Z19</f>
         <v>0.3</v>
       </c>
       <c r="V19" s="3">
-        <f t="shared" si="3"/>
+        <f>Z19*U19</f>
         <v>90</v>
       </c>
       <c r="W19" s="3">
-        <f t="shared" si="4"/>
+        <f>V19*3</f>
         <v>270</v>
       </c>
       <c r="X19" s="4">
-        <f t="shared" si="5"/>
+        <f>O19/Z19</f>
         <v>1876953.09</v>
       </c>
       <c r="Y19" s="4">
-        <f t="shared" si="6"/>
+        <f>O19/AA19</f>
         <v>6256510.2999999998</v>
       </c>
       <c r="Z19" s="3">
@@ -5054,31 +5054,31 @@
         <v>0.3</v>
       </c>
       <c r="S20" s="3">
-        <f t="shared" si="0"/>
+        <f>Z20*R20</f>
         <v>21.599999999999998</v>
       </c>
       <c r="T20" s="3">
-        <f t="shared" si="1"/>
+        <f>S20*3</f>
         <v>64.8</v>
       </c>
       <c r="U20" s="5">
-        <f t="shared" si="2"/>
+        <f>AA20/Z20</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="V20" s="3">
-        <f t="shared" si="3"/>
+        <f>Z20*U20</f>
         <v>21.6</v>
       </c>
       <c r="W20" s="3">
-        <f t="shared" si="4"/>
+        <f>V20*3</f>
         <v>64.800000000000011</v>
       </c>
       <c r="X20" s="4">
-        <f t="shared" si="5"/>
+        <f>O20/Z20</f>
         <v>1549144.2083333333</v>
       </c>
       <c r="Y20" s="4">
-        <f t="shared" si="6"/>
+        <f>O20/AA20</f>
         <v>5163814.0277777771</v>
       </c>
       <c r="Z20" s="3">
@@ -5094,13 +5094,13 @@
         <v>28</v>
       </c>
       <c r="AD20" s="6">
-        <v>0.75000000000000022</v>
+        <v>0.77000000000000024</v>
       </c>
       <c r="AE20" s="6">
-        <v>0.75000000000000022</v>
+        <v>0.77000000000000024</v>
       </c>
       <c r="AF20" s="6">
-        <v>0.75000000000000022</v>
+        <v>0.77000000000000024</v>
       </c>
       <c r="AG20" s="6">
         <v>0.8</v>
@@ -5130,7 +5130,7 @@
         <v>0.8</v>
       </c>
       <c r="AP20" s="6">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AQ20" s="6">
         <v>0.5</v>
@@ -5213,31 +5213,31 @@
         <v>0.3</v>
       </c>
       <c r="S21" s="3">
-        <f t="shared" si="0"/>
+        <f>Z21*R21</f>
         <v>21.599999999999998</v>
       </c>
       <c r="T21" s="3">
-        <f t="shared" si="1"/>
+        <f>S21*3</f>
         <v>64.8</v>
       </c>
       <c r="U21" s="5">
-        <f t="shared" si="2"/>
+        <f>AA21/Z21</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="V21" s="3">
-        <f t="shared" si="3"/>
+        <f>Z21*U21</f>
         <v>21.6</v>
       </c>
       <c r="W21" s="3">
-        <f t="shared" si="4"/>
+        <f>V21*3</f>
         <v>64.800000000000011</v>
       </c>
       <c r="X21" s="4">
-        <f t="shared" si="5"/>
+        <f>O21/Z21</f>
         <v>1498517.5833333333</v>
       </c>
       <c r="Y21" s="4">
-        <f t="shared" si="6"/>
+        <f>O21/AA21</f>
         <v>4995058.611111111</v>
       </c>
       <c r="Z21" s="3">
@@ -5253,13 +5253,13 @@
         <v>47</v>
       </c>
       <c r="AD21" s="6">
-        <v>0.74000000000000021</v>
+        <v>0.7300000000000002</v>
       </c>
       <c r="AE21" s="6">
-        <v>0.64000000000000012</v>
+        <v>0.63000000000000012</v>
       </c>
       <c r="AF21" s="6">
-        <v>0.7200000000000002</v>
+        <v>0.71000000000000019</v>
       </c>
       <c r="AG21" s="6">
         <v>1</v>
@@ -5289,7 +5289,7 @@
         <v>1</v>
       </c>
       <c r="AP21" s="6">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AQ21" s="6">
         <v>0.5</v>
@@ -5372,31 +5372,31 @@
         <v>0.3</v>
       </c>
       <c r="S22" s="3">
-        <f t="shared" si="0"/>
+        <f>Z22*R22</f>
         <v>16.8</v>
       </c>
       <c r="T22" s="3">
-        <f t="shared" si="1"/>
+        <f>S22*3</f>
         <v>50.400000000000006</v>
       </c>
       <c r="U22" s="5">
-        <f t="shared" si="2"/>
+        <f>AA22/Z22</f>
         <v>0.3</v>
       </c>
       <c r="V22" s="3">
-        <f t="shared" si="3"/>
+        <f>Z22*U22</f>
         <v>16.8</v>
       </c>
       <c r="W22" s="3">
-        <f t="shared" si="4"/>
+        <f>V22*3</f>
         <v>50.400000000000006</v>
       </c>
       <c r="X22" s="4">
-        <f t="shared" si="5"/>
+        <f>O22/Z22</f>
         <v>1535700.5892857143</v>
       </c>
       <c r="Y22" s="4">
-        <f t="shared" si="6"/>
+        <f>O22/AA22</f>
         <v>5119001.9642857136</v>
       </c>
       <c r="Z22" s="3">
@@ -5412,13 +5412,13 @@
         <v>49</v>
       </c>
       <c r="AD22" s="6">
-        <v>0.7200000000000002</v>
+        <v>0.71000000000000019</v>
       </c>
       <c r="AE22" s="6">
-        <v>0.67000000000000015</v>
+        <v>0.66000000000000014</v>
       </c>
       <c r="AF22" s="6">
-        <v>0.71000000000000019</v>
+        <v>0.70000000000000018</v>
       </c>
       <c r="AG22" s="6">
         <v>1</v>
@@ -5448,7 +5448,7 @@
         <v>1</v>
       </c>
       <c r="AP22" s="6">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AQ22" s="6">
         <v>0.5</v>
@@ -5531,31 +5531,31 @@
         <v>0.3</v>
       </c>
       <c r="S23" s="3">
-        <f t="shared" si="0"/>
+        <f>Z23*R23</f>
         <v>23.4</v>
       </c>
       <c r="T23" s="3">
-        <f t="shared" si="1"/>
+        <f>S23*3</f>
         <v>70.199999999999989</v>
       </c>
       <c r="U23" s="5">
-        <f t="shared" si="2"/>
+        <f>AA23/Z23</f>
         <v>0.32935897435897438</v>
       </c>
       <c r="V23" s="3">
-        <f t="shared" si="3"/>
+        <f>Z23*U23</f>
         <v>25.69</v>
       </c>
       <c r="W23" s="3">
-        <f t="shared" si="4"/>
+        <f>V23*3</f>
         <v>77.070000000000007</v>
       </c>
       <c r="X23" s="4">
-        <f t="shared" si="5"/>
+        <f>O23/Z23</f>
         <v>1440397.7307692308</v>
       </c>
       <c r="Y23" s="4">
-        <f t="shared" si="6"/>
+        <f>O23/AA23</f>
         <v>4373336.8236667961</v>
       </c>
       <c r="Z23" s="3">
@@ -5690,31 +5690,31 @@
         <v>0.3</v>
       </c>
       <c r="S24" s="3">
-        <f t="shared" si="0"/>
+        <f>Z24*R24</f>
         <v>36</v>
       </c>
       <c r="T24" s="3">
-        <f t="shared" si="1"/>
+        <f>S24*3</f>
         <v>108</v>
       </c>
       <c r="U24" s="5">
-        <f t="shared" si="2"/>
+        <f>AA24/Z24</f>
         <v>0.34083333333333332</v>
       </c>
       <c r="V24" s="3">
-        <f t="shared" si="3"/>
+        <f>Z24*U24</f>
         <v>40.9</v>
       </c>
       <c r="W24" s="3">
-        <f t="shared" si="4"/>
+        <f>V24*3</f>
         <v>122.69999999999999</v>
       </c>
       <c r="X24" s="4">
-        <f t="shared" si="5"/>
+        <f>O24/Z24</f>
         <v>955097.63250000007</v>
       </c>
       <c r="Y24" s="4">
-        <f t="shared" si="6"/>
+        <f>O24/AA24</f>
         <v>2802242.4425427876</v>
       </c>
       <c r="Z24" s="3">
@@ -5849,31 +5849,31 @@
         <v>0.3</v>
       </c>
       <c r="S25" s="3">
-        <f t="shared" si="0"/>
+        <f>Z25*R25</f>
         <v>30</v>
       </c>
       <c r="T25" s="3">
-        <f t="shared" si="1"/>
+        <f>S25*3</f>
         <v>90</v>
       </c>
       <c r="U25" s="5">
-        <f t="shared" si="2"/>
+        <f>AA25/Z25</f>
         <v>0.3</v>
       </c>
       <c r="V25" s="3">
-        <f t="shared" si="3"/>
+        <f>Z25*U25</f>
         <v>30</v>
       </c>
       <c r="W25" s="3">
-        <f t="shared" si="4"/>
+        <f>V25*3</f>
         <v>90</v>
       </c>
       <c r="X25" s="4">
-        <f t="shared" si="5"/>
+        <f>O25/Z25</f>
         <v>985648.28</v>
       </c>
       <c r="Y25" s="4">
-        <f t="shared" si="6"/>
+        <f>O25/AA25</f>
         <v>3285494.2666666666</v>
       </c>
       <c r="Z25" s="3">
@@ -5889,13 +5889,13 @@
         <v>223</v>
       </c>
       <c r="AD25" s="6">
-        <v>0.79000000000000026</v>
+        <v>0.81000000000000028</v>
       </c>
       <c r="AE25" s="6">
-        <v>0.53500000000000014</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="AF25" s="6">
-        <v>0.73900000000000032</v>
+        <v>0.75900000000000023</v>
       </c>
       <c r="AG25" s="6">
         <v>0.9</v>
@@ -5925,7 +5925,7 @@
         <v>0.8</v>
       </c>
       <c r="AP25" s="6">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AQ25" s="6">
         <v>1</v>
@@ -6008,31 +6008,31 @@
         <v>0.3</v>
       </c>
       <c r="S26" s="3">
-        <f t="shared" si="0"/>
+        <f>Z26*R26</f>
         <v>30</v>
       </c>
       <c r="T26" s="3">
-        <f t="shared" si="1"/>
+        <f>S26*3</f>
         <v>90</v>
       </c>
       <c r="U26" s="5">
-        <f t="shared" si="2"/>
+        <f>AA26/Z26</f>
         <v>0.3</v>
       </c>
       <c r="V26" s="3">
-        <f t="shared" si="3"/>
+        <f>Z26*U26</f>
         <v>30</v>
       </c>
       <c r="W26" s="3">
-        <f t="shared" si="4"/>
+        <f>V26*3</f>
         <v>90</v>
       </c>
       <c r="X26" s="4">
-        <f t="shared" si="5"/>
+        <f>O26/Z26</f>
         <v>999328.58</v>
       </c>
       <c r="Y26" s="4">
-        <f t="shared" si="6"/>
+        <f>O26/AA26</f>
         <v>3331095.2666666666</v>
       </c>
       <c r="Z26" s="3">
@@ -6167,31 +6167,31 @@
         <v>0.3</v>
       </c>
       <c r="S27" s="3">
-        <f t="shared" si="0"/>
+        <f>Z27*R27</f>
         <v>51.3</v>
       </c>
       <c r="T27" s="3">
-        <f t="shared" si="1"/>
+        <f>S27*3</f>
         <v>153.89999999999998</v>
       </c>
       <c r="U27" s="5">
-        <f t="shared" si="2"/>
+        <f>AA27/Z27</f>
         <v>0.3</v>
       </c>
       <c r="V27" s="3">
-        <f t="shared" si="3"/>
+        <f>Z27*U27</f>
         <v>51.3</v>
       </c>
       <c r="W27" s="3">
-        <f t="shared" si="4"/>
+        <f>V27*3</f>
         <v>153.89999999999998</v>
       </c>
       <c r="X27" s="4">
-        <f t="shared" si="5"/>
+        <f>O27/Z27</f>
         <v>1862193.350877193</v>
       </c>
       <c r="Y27" s="4">
-        <f t="shared" si="6"/>
+        <f>O27/AA27</f>
         <v>6207311.1695906436</v>
       </c>
       <c r="Z27" s="3">
@@ -6326,31 +6326,31 @@
         <v>0.3</v>
       </c>
       <c r="S28" s="3">
-        <f t="shared" si="0"/>
+        <f>Z28*R28</f>
         <v>153</v>
       </c>
       <c r="T28" s="3">
-        <f t="shared" si="1"/>
+        <f>S28*3</f>
         <v>459</v>
       </c>
       <c r="U28" s="5">
-        <f t="shared" si="2"/>
+        <f>AA28/Z28</f>
         <v>0.3</v>
       </c>
       <c r="V28" s="3">
-        <f t="shared" si="3"/>
+        <f>Z28*U28</f>
         <v>153</v>
       </c>
       <c r="W28" s="3">
-        <f t="shared" si="4"/>
+        <f>V28*3</f>
         <v>459</v>
       </c>
       <c r="X28" s="4">
-        <f t="shared" si="5"/>
+        <f>O28/Z28</f>
         <v>1744882.0290196077</v>
       </c>
       <c r="Y28" s="4">
-        <f t="shared" si="6"/>
+        <f>O28/AA28</f>
         <v>5816273.430065359</v>
       </c>
       <c r="Z28" s="3">
@@ -6485,31 +6485,31 @@
         <v>0.3</v>
       </c>
       <c r="S29" s="3">
-        <f t="shared" si="0"/>
+        <f>Z29*R29</f>
         <v>21</v>
       </c>
       <c r="T29" s="3">
-        <f t="shared" si="1"/>
+        <f>S29*3</f>
         <v>63</v>
       </c>
       <c r="U29" s="5">
-        <f t="shared" si="2"/>
+        <f>AA29/Z29</f>
         <v>0.31428571428571428</v>
       </c>
       <c r="V29" s="3">
-        <f t="shared" si="3"/>
+        <f>Z29*U29</f>
         <v>22</v>
       </c>
       <c r="W29" s="3">
-        <f t="shared" si="4"/>
+        <f>V29*3</f>
         <v>66</v>
       </c>
       <c r="X29" s="4">
-        <f t="shared" si="5"/>
+        <f>O29/Z29</f>
         <v>955539.85714285716</v>
       </c>
       <c r="Y29" s="4">
-        <f t="shared" si="6"/>
+        <f>O29/AA29</f>
         <v>3040354.0909090908</v>
       </c>
       <c r="Z29" s="3">
@@ -6644,31 +6644,31 @@
         <v>0.3</v>
       </c>
       <c r="S30" s="3">
-        <f t="shared" si="0"/>
+        <f>Z30*R30</f>
         <v>22.5</v>
       </c>
       <c r="T30" s="3">
-        <f t="shared" si="1"/>
+        <f>S30*3</f>
         <v>67.5</v>
       </c>
       <c r="U30" s="5">
-        <f t="shared" si="2"/>
+        <f>AA30/Z30</f>
         <v>0.34133333333333338</v>
       </c>
       <c r="V30" s="3">
-        <f t="shared" si="3"/>
+        <f>Z30*U30</f>
         <v>25.600000000000005</v>
       </c>
       <c r="W30" s="3">
-        <f t="shared" si="4"/>
+        <f>V30*3</f>
         <v>76.800000000000011</v>
       </c>
       <c r="X30" s="4">
-        <f t="shared" si="5"/>
+        <f>O30/Z30</f>
         <v>1147822.7426666666</v>
       </c>
       <c r="Y30" s="4">
-        <f t="shared" si="6"/>
+        <f>O30/AA30</f>
         <v>3362761.94140625</v>
       </c>
       <c r="Z30" s="3">
@@ -6684,13 +6684,13 @@
         <v>32</v>
       </c>
       <c r="AD30" s="6">
-        <v>0.82000000000000028</v>
+        <v>0.79000000000000026</v>
       </c>
       <c r="AE30" s="6">
-        <v>0.70000000000000018</v>
+        <v>0.67000000000000015</v>
       </c>
       <c r="AF30" s="6">
-        <v>0.79600000000000026</v>
+        <v>0.76600000000000024</v>
       </c>
       <c r="AG30" s="6">
         <v>1</v>
@@ -6720,7 +6720,7 @@
         <v>1</v>
       </c>
       <c r="AP30" s="6">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AQ30" s="6">
         <v>0.7</v>
@@ -6803,31 +6803,31 @@
         <v>0.3</v>
       </c>
       <c r="S31" s="3">
-        <f t="shared" si="0"/>
+        <f>Z31*R31</f>
         <v>42.42</v>
       </c>
       <c r="T31" s="3">
-        <f t="shared" si="1"/>
+        <f>S31*3</f>
         <v>127.26</v>
       </c>
       <c r="U31" s="5">
-        <f t="shared" si="2"/>
+        <f>AA31/Z31</f>
         <v>0.3</v>
       </c>
       <c r="V31" s="3">
-        <f t="shared" si="3"/>
+        <f>Z31*U31</f>
         <v>42.42</v>
       </c>
       <c r="W31" s="3">
-        <f t="shared" si="4"/>
+        <f>V31*3</f>
         <v>127.26</v>
       </c>
       <c r="X31" s="4">
-        <f t="shared" si="5"/>
+        <f>O31/Z31</f>
         <v>1040124.3203677511</v>
       </c>
       <c r="Y31" s="4">
-        <f t="shared" si="6"/>
+        <f>O31/AA31</f>
         <v>3467081.0678925035</v>
       </c>
       <c r="Z31" s="3">
@@ -6962,31 +6962,31 @@
         <v>0.3</v>
       </c>
       <c r="S32" s="3">
-        <f t="shared" si="0"/>
+        <f>Z32*R32</f>
         <v>101.7</v>
       </c>
       <c r="T32" s="3">
-        <f t="shared" si="1"/>
+        <f>S32*3</f>
         <v>305.10000000000002</v>
       </c>
       <c r="U32" s="5">
-        <f t="shared" si="2"/>
+        <f>AA32/Z32</f>
         <v>0.3</v>
       </c>
       <c r="V32" s="3">
-        <f t="shared" si="3"/>
+        <f>Z32*U32</f>
         <v>101.7</v>
       </c>
       <c r="W32" s="3">
-        <f t="shared" si="4"/>
+        <f>V32*3</f>
         <v>305.10000000000002</v>
       </c>
       <c r="X32" s="4" t="e">
-        <f t="shared" si="5"/>
+        <f>O32/Z32</f>
         <v>#VALUE!</v>
       </c>
       <c r="Y32" s="4" t="e">
-        <f t="shared" si="6"/>
+        <f>O32/AA32</f>
         <v>#VALUE!</v>
       </c>
       <c r="Z32" s="3">
@@ -7121,31 +7121,31 @@
         <v>0.3</v>
       </c>
       <c r="S33" s="3">
-        <f t="shared" si="0"/>
+        <f>Z33*R33</f>
         <v>54</v>
       </c>
       <c r="T33" s="3">
-        <f t="shared" si="1"/>
+        <f>S33*3</f>
         <v>162</v>
       </c>
       <c r="U33" s="5">
-        <f t="shared" si="2"/>
+        <f>AA33/Z33</f>
         <v>0.3</v>
       </c>
       <c r="V33" s="3">
-        <f t="shared" si="3"/>
+        <f>Z33*U33</f>
         <v>54</v>
       </c>
       <c r="W33" s="3">
-        <f t="shared" si="4"/>
+        <f>V33*3</f>
         <v>162</v>
       </c>
       <c r="X33" s="4">
-        <f t="shared" si="5"/>
+        <f>O33/Z33</f>
         <v>5140615.7388888886</v>
       </c>
       <c r="Y33" s="4">
-        <f t="shared" si="6"/>
+        <f>O33/AA33</f>
         <v>17135385.796296295</v>
       </c>
       <c r="Z33" s="3">
@@ -7280,31 +7280,31 @@
         <v>0.3</v>
       </c>
       <c r="S34" s="3">
-        <f t="shared" si="0"/>
+        <f>Z34*R34</f>
         <v>101.7</v>
       </c>
       <c r="T34" s="3">
-        <f t="shared" si="1"/>
+        <f>S34*3</f>
         <v>305.10000000000002</v>
       </c>
       <c r="U34" s="5">
-        <f t="shared" si="2"/>
+        <f>AA34/Z34</f>
         <v>0.3</v>
       </c>
       <c r="V34" s="3">
-        <f t="shared" si="3"/>
+        <f>Z34*U34</f>
         <v>101.7</v>
       </c>
       <c r="W34" s="3">
-        <f t="shared" si="4"/>
+        <f>V34*3</f>
         <v>305.10000000000002</v>
       </c>
       <c r="X34" s="4" t="e">
-        <f t="shared" si="5"/>
+        <f>O34/Z34</f>
         <v>#VALUE!</v>
       </c>
       <c r="Y34" s="4" t="e">
-        <f t="shared" si="6"/>
+        <f>O34/AA34</f>
         <v>#VALUE!</v>
       </c>
       <c r="Z34" s="3">
@@ -7439,31 +7439,31 @@
         <v>0.3</v>
       </c>
       <c r="S35" s="9">
-        <f t="shared" si="0"/>
+        <f>Z35*R35</f>
         <v>37.5</v>
       </c>
       <c r="T35" s="9">
-        <f t="shared" si="1"/>
+        <f>S35*3</f>
         <v>112.5</v>
       </c>
       <c r="U35" s="10">
-        <f t="shared" si="2"/>
+        <f>AA35/Z35</f>
         <v>0.3</v>
       </c>
       <c r="V35" s="9">
-        <f t="shared" si="3"/>
+        <f>Z35*U35</f>
         <v>37.5</v>
       </c>
       <c r="W35" s="9">
-        <f t="shared" si="4"/>
+        <f>V35*3</f>
         <v>112.5</v>
       </c>
       <c r="X35" s="11">
-        <f t="shared" si="5"/>
+        <f>O35/Z35</f>
         <v>1288848.5736</v>
       </c>
       <c r="Y35" s="11">
-        <f t="shared" si="6"/>
+        <f>O35/AA35</f>
         <v>4296161.9119999995</v>
       </c>
       <c r="Z35" s="9">
@@ -7479,13 +7479,13 @@
         <v>20</v>
       </c>
       <c r="AD35" s="6">
-        <v>0.87500000000000022</v>
+        <v>0.8450000000000002</v>
       </c>
       <c r="AE35" s="6">
-        <v>0.80000000000000027</v>
+        <v>0.77000000000000024</v>
       </c>
       <c r="AF35" s="6">
-        <v>0.86000000000000021</v>
+        <v>0.83000000000000018</v>
       </c>
       <c r="AG35" s="6">
         <v>1</v>
@@ -7515,7 +7515,7 @@
         <v>1</v>
       </c>
       <c r="AP35" s="6">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AQ35" s="6">
         <v>0.9</v>
@@ -7598,31 +7598,31 @@
         <v>0.3</v>
       </c>
       <c r="S36" s="3">
-        <f t="shared" si="0"/>
+        <f>Z36*R36</f>
         <v>81</v>
       </c>
       <c r="T36" s="3">
-        <f t="shared" si="1"/>
+        <f>S36*3</f>
         <v>243</v>
       </c>
       <c r="U36" s="5">
-        <f t="shared" si="2"/>
+        <f>AA36/Z36</f>
         <v>0.3</v>
       </c>
       <c r="V36" s="3">
-        <f t="shared" si="3"/>
+        <f>Z36*U36</f>
         <v>81</v>
       </c>
       <c r="W36" s="3">
-        <f t="shared" si="4"/>
+        <f>V36*3</f>
         <v>243</v>
       </c>
       <c r="X36" s="4" t="e">
-        <f t="shared" si="5"/>
+        <f>O36/Z36</f>
         <v>#VALUE!</v>
       </c>
       <c r="Y36" s="4" t="e">
-        <f t="shared" si="6"/>
+        <f>O36/AA36</f>
         <v>#VALUE!</v>
       </c>
       <c r="Z36" s="14">
@@ -7757,31 +7757,31 @@
         <v>0.3</v>
       </c>
       <c r="S37" s="3">
-        <f t="shared" si="0"/>
+        <f>Z37*R37</f>
         <v>90</v>
       </c>
       <c r="T37" s="3">
-        <f t="shared" si="1"/>
+        <f>S37*3</f>
         <v>270</v>
       </c>
       <c r="U37" s="5">
-        <f t="shared" si="2"/>
+        <f>AA37/Z37</f>
         <v>0.3</v>
       </c>
       <c r="V37" s="3">
-        <f t="shared" si="3"/>
+        <f>Z37*U37</f>
         <v>90</v>
       </c>
       <c r="W37" s="3">
-        <f t="shared" si="4"/>
+        <f>V37*3</f>
         <v>270</v>
       </c>
       <c r="X37" s="4" t="e">
-        <f t="shared" si="5"/>
+        <f>O37/Z37</f>
         <v>#VALUE!</v>
       </c>
       <c r="Y37" s="4" t="e">
-        <f t="shared" si="6"/>
+        <f>O37/AA37</f>
         <v>#VALUE!</v>
       </c>
       <c r="Z37" s="14">
@@ -7916,31 +7916,31 @@
         <v>0.3</v>
       </c>
       <c r="S38" s="3">
-        <f t="shared" si="0"/>
+        <f>Z38*R38</f>
         <v>90</v>
       </c>
       <c r="T38" s="3">
-        <f t="shared" si="1"/>
+        <f>S38*3</f>
         <v>270</v>
       </c>
       <c r="U38" s="5">
-        <f t="shared" si="2"/>
+        <f>AA38/Z38</f>
         <v>0.3</v>
       </c>
       <c r="V38" s="3">
-        <f t="shared" si="3"/>
+        <f>Z38*U38</f>
         <v>90</v>
       </c>
       <c r="W38" s="3">
-        <f t="shared" si="4"/>
+        <f>V38*3</f>
         <v>270</v>
       </c>
       <c r="X38" s="4" t="e">
-        <f t="shared" si="5"/>
+        <f>O38/Z38</f>
         <v>#VALUE!</v>
       </c>
       <c r="Y38" s="4" t="e">
-        <f t="shared" si="6"/>
+        <f>O38/AA38</f>
         <v>#VALUE!</v>
       </c>
       <c r="Z38" s="14">
@@ -8075,31 +8075,31 @@
         <v>0.3</v>
       </c>
       <c r="S39" s="3">
-        <f t="shared" si="0"/>
+        <f>Z39*R39</f>
         <v>90</v>
       </c>
       <c r="T39" s="3">
-        <f t="shared" si="1"/>
+        <f>S39*3</f>
         <v>270</v>
       </c>
       <c r="U39" s="5">
-        <f t="shared" si="2"/>
+        <f>AA39/Z39</f>
         <v>0.3</v>
       </c>
       <c r="V39" s="3">
-        <f t="shared" si="3"/>
+        <f>Z39*U39</f>
         <v>90</v>
       </c>
       <c r="W39" s="3">
-        <f t="shared" si="4"/>
+        <f>V39*3</f>
         <v>270</v>
       </c>
       <c r="X39" s="4" t="e">
-        <f t="shared" si="5"/>
+        <f>O39/Z39</f>
         <v>#VALUE!</v>
       </c>
       <c r="Y39" s="4" t="e">
-        <f t="shared" si="6"/>
+        <f>O39/AA39</f>
         <v>#VALUE!</v>
       </c>
       <c r="Z39" s="14">
@@ -8234,31 +8234,31 @@
         <v>0.3</v>
       </c>
       <c r="S40" s="3">
-        <f t="shared" si="0"/>
+        <f>Z40*R40</f>
         <v>174</v>
       </c>
       <c r="T40" s="3">
-        <f t="shared" si="1"/>
+        <f>S40*3</f>
         <v>522</v>
       </c>
       <c r="U40" s="5">
-        <f t="shared" si="2"/>
+        <f>AA40/Z40</f>
         <v>0.3</v>
       </c>
       <c r="V40" s="3">
-        <f t="shared" si="3"/>
+        <f>Z40*U40</f>
         <v>174</v>
       </c>
       <c r="W40" s="3">
-        <f t="shared" si="4"/>
+        <f>V40*3</f>
         <v>522</v>
       </c>
       <c r="X40" s="4" t="e">
-        <f t="shared" si="5"/>
+        <f>O40/Z40</f>
         <v>#VALUE!</v>
       </c>
       <c r="Y40" s="4" t="e">
-        <f t="shared" si="6"/>
+        <f>O40/AA40</f>
         <v>#VALUE!</v>
       </c>
       <c r="Z40" s="18">
@@ -8393,31 +8393,31 @@
         <v>0.3</v>
       </c>
       <c r="S41" s="3">
-        <f t="shared" si="0"/>
+        <f>Z41*R41</f>
         <v>35.1</v>
       </c>
       <c r="T41" s="3">
-        <f t="shared" si="1"/>
+        <f>S41*3</f>
         <v>105.30000000000001</v>
       </c>
       <c r="U41" s="5">
-        <f t="shared" si="2"/>
+        <f>AA41/Z41</f>
         <v>0.3</v>
       </c>
       <c r="V41" s="3">
-        <f t="shared" si="3"/>
+        <f>Z41*U41</f>
         <v>35.1</v>
       </c>
       <c r="W41" s="3">
-        <f t="shared" si="4"/>
+        <f>V41*3</f>
         <v>105.30000000000001</v>
       </c>
       <c r="X41" s="4" t="e">
-        <f t="shared" si="5"/>
+        <f>O41/Z41</f>
         <v>#VALUE!</v>
       </c>
       <c r="Y41" s="4" t="e">
-        <f t="shared" si="6"/>
+        <f>O41/AA41</f>
         <v>#VALUE!</v>
       </c>
       <c r="Z41" s="18">
@@ -8602,7 +8602,11 @@
       <c r="P53" s="51"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AX1" xr:uid="{782B78D9-47D9-4EBC-8BEA-A91BF1F0B98F}"/>
+  <autoFilter ref="A1:AX1" xr:uid="{782B78D9-47D9-4EBC-8BEA-A91BF1F0B98F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AX41">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="597" r:id="rId1"/>
 </worksheet>

--- a/cartera-mixtos/data/DATOS_MIXTOS.xlsx
+++ b/cartera-mixtos/data/DATOS_MIXTOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CPEL-PROYECTOS\MIXTOS\REUNIONES_SEMANALES_RESPALDO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E68E7F5-32D0-4D85-9490-A7979854667F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0740B168-168B-4946-9605-9C6286F827BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="724" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2192,31 +2192,31 @@
         <v>0.3</v>
       </c>
       <c r="S2" s="3">
-        <f>Z2*R2</f>
+        <f t="shared" ref="S2:S41" si="0">Z2*R2</f>
         <v>24</v>
       </c>
       <c r="T2" s="3">
-        <f>S2*3</f>
+        <f t="shared" ref="T2:T41" si="1">S2*3</f>
         <v>72</v>
       </c>
       <c r="U2" s="5">
-        <f>AA2/Z2</f>
+        <f t="shared" ref="U2:U41" si="2">AA2/Z2</f>
         <v>0.3</v>
       </c>
       <c r="V2" s="3">
-        <f>Z2*U2</f>
+        <f t="shared" ref="V2:V41" si="3">Z2*U2</f>
         <v>24</v>
       </c>
       <c r="W2" s="3">
-        <f>V2*3</f>
+        <f t="shared" ref="W2:W41" si="4">V2*3</f>
         <v>72</v>
       </c>
       <c r="X2" s="4">
-        <f>O2/Z2</f>
+        <f t="shared" ref="X2:X41" si="5">O2/Z2</f>
         <v>1174138.6675</v>
       </c>
       <c r="Y2" s="4">
-        <f>O2/AA2</f>
+        <f t="shared" ref="Y2:Y41" si="6">O2/AA2</f>
         <v>3913795.5583333336</v>
       </c>
       <c r="Z2" s="3">
@@ -2351,31 +2351,31 @@
         <v>0.3</v>
       </c>
       <c r="S3" s="3">
-        <f>Z3*R3</f>
+        <f t="shared" si="0"/>
         <v>90.45</v>
       </c>
       <c r="T3" s="3">
-        <f>S3*3</f>
+        <f t="shared" si="1"/>
         <v>271.35000000000002</v>
       </c>
       <c r="U3" s="5">
-        <f>AA3/Z3</f>
+        <f t="shared" si="2"/>
         <v>0.30016583747927034</v>
       </c>
       <c r="V3" s="3">
-        <f>Z3*U3</f>
+        <f t="shared" si="3"/>
         <v>90.5</v>
       </c>
       <c r="W3" s="3">
-        <f>V3*3</f>
+        <f t="shared" si="4"/>
         <v>271.5</v>
       </c>
       <c r="X3" s="4">
-        <f>O3/Z3</f>
+        <f t="shared" si="5"/>
         <v>1697290.8441127695</v>
       </c>
       <c r="Y3" s="4">
-        <f>O3/AA3</f>
+        <f t="shared" si="6"/>
         <v>5654510.3812154699</v>
       </c>
       <c r="Z3" s="3">
@@ -2510,31 +2510,31 @@
         <v>0.3</v>
       </c>
       <c r="S4" s="3">
-        <f>Z4*R4</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="T4" s="3">
-        <f>S4*3</f>
+        <f t="shared" si="1"/>
         <v>180</v>
       </c>
       <c r="U4" s="5">
-        <f>AA4/Z4</f>
+        <f t="shared" si="2"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="V4" s="3">
-        <f>Z4*U4</f>
+        <f t="shared" si="3"/>
         <v>65</v>
       </c>
       <c r="W4" s="3">
-        <f>V4*3</f>
+        <f t="shared" si="4"/>
         <v>195</v>
       </c>
       <c r="X4" s="4">
-        <f>O4/Z4</f>
+        <f t="shared" si="5"/>
         <v>1342145.7775000001</v>
       </c>
       <c r="Y4" s="4">
-        <f>O4/AA4</f>
+        <f t="shared" si="6"/>
         <v>4129679.3153846152</v>
       </c>
       <c r="Z4" s="3">
@@ -2669,31 +2669,31 @@
         <v>0.3</v>
       </c>
       <c r="S5" s="3">
-        <f>Z5*R5</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="T5" s="3">
-        <f>S5*3</f>
+        <f t="shared" si="1"/>
         <v>81</v>
       </c>
       <c r="U5" s="5">
-        <f>AA5/Z5</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="V5" s="3">
-        <f>Z5*U5</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="W5" s="3">
-        <f>V5*3</f>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="X5" s="4">
-        <f>O5/Z5</f>
+        <f t="shared" si="5"/>
         <v>1692535.4111111111</v>
       </c>
       <c r="Y5" s="4">
-        <f>O5/AA5</f>
+        <f t="shared" si="6"/>
         <v>1692535.4111111111</v>
       </c>
       <c r="Z5" s="3">
@@ -2828,31 +2828,31 @@
         <v>0.3</v>
       </c>
       <c r="S6" s="3">
-        <f>Z6*R6</f>
+        <f t="shared" si="0"/>
         <v>16.2</v>
       </c>
       <c r="T6" s="3">
-        <f>S6*3</f>
+        <f t="shared" si="1"/>
         <v>48.599999999999994</v>
       </c>
       <c r="U6" s="5">
-        <f>AA6/Z6</f>
+        <f t="shared" si="2"/>
         <v>0.34074074074074073</v>
       </c>
       <c r="V6" s="3">
-        <f>Z6*U6</f>
+        <f t="shared" si="3"/>
         <v>18.399999999999999</v>
       </c>
       <c r="W6" s="3">
-        <f>V6*3</f>
+        <f t="shared" si="4"/>
         <v>55.199999999999996</v>
       </c>
       <c r="X6" s="4">
-        <f>O6/Z6</f>
+        <f t="shared" si="5"/>
         <v>1116269.9592592593</v>
       </c>
       <c r="Y6" s="4">
-        <f>O6/AA6</f>
+        <f t="shared" si="6"/>
         <v>3276009.6630434785</v>
       </c>
       <c r="Z6" s="3">
@@ -2868,13 +2868,13 @@
         <v>122</v>
       </c>
       <c r="AD6" s="6">
-        <v>0.77000000000000024</v>
+        <v>0.80000000000000027</v>
       </c>
       <c r="AE6" s="6">
-        <v>0.52500000000000002</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="AF6" s="6">
-        <v>0.7210000000000002</v>
+        <v>0.75100000000000022</v>
       </c>
       <c r="AG6" s="6">
         <v>1</v>
@@ -2904,7 +2904,7 @@
         <v>0.9</v>
       </c>
       <c r="AP6" s="6">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AQ6" s="6">
         <v>0.9</v>
@@ -2987,31 +2987,31 @@
         <v>0.3</v>
       </c>
       <c r="S7" s="3">
-        <f>Z7*R7</f>
+        <f t="shared" si="0"/>
         <v>150.9</v>
       </c>
       <c r="T7" s="3">
-        <f>S7*3</f>
+        <f t="shared" si="1"/>
         <v>452.70000000000005</v>
       </c>
       <c r="U7" s="5">
-        <f>AA7/Z7</f>
+        <f t="shared" si="2"/>
         <v>0.30019880715705766</v>
       </c>
       <c r="V7" s="3">
-        <f>Z7*U7</f>
+        <f t="shared" si="3"/>
         <v>151</v>
       </c>
       <c r="W7" s="3">
-        <f>V7*3</f>
+        <f t="shared" si="4"/>
         <v>453</v>
       </c>
       <c r="X7" s="4">
-        <f>O7/Z7</f>
+        <f t="shared" si="5"/>
         <v>1591100.8155069584</v>
       </c>
       <c r="Y7" s="4">
-        <f>O7/AA7</f>
+        <f t="shared" si="6"/>
         <v>5300157.0211920533</v>
       </c>
       <c r="Z7" s="3">
@@ -3146,31 +3146,31 @@
         <v>0.3</v>
       </c>
       <c r="S8" s="3">
-        <f>Z8*R8</f>
+        <f t="shared" si="0"/>
         <v>140.4</v>
       </c>
       <c r="T8" s="3">
-        <f>S8*3</f>
+        <f t="shared" si="1"/>
         <v>421.20000000000005</v>
       </c>
       <c r="U8" s="5">
-        <f>AA8/Z8</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V8" s="3">
-        <f>Z8*U8</f>
+        <f t="shared" si="3"/>
         <v>140.4</v>
       </c>
       <c r="W8" s="3">
-        <f>V8*3</f>
+        <f t="shared" si="4"/>
         <v>421.20000000000005</v>
       </c>
       <c r="X8" s="4">
-        <f>O8/Z8</f>
+        <f t="shared" si="5"/>
         <v>1632951.1431623932</v>
       </c>
       <c r="Y8" s="4">
-        <f>O8/AA8</f>
+        <f t="shared" si="6"/>
         <v>5443170.4772079773</v>
       </c>
       <c r="Z8" s="3">
@@ -3305,31 +3305,31 @@
         <v>0.3</v>
       </c>
       <c r="S9" s="3">
-        <f>Z9*R9</f>
+        <f t="shared" si="0"/>
         <v>22.5</v>
       </c>
       <c r="T9" s="3">
-        <f>S9*3</f>
+        <f t="shared" si="1"/>
         <v>67.5</v>
       </c>
       <c r="U9" s="5">
-        <f>AA9/Z9</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V9" s="3">
-        <f>Z9*U9</f>
+        <f t="shared" si="3"/>
         <v>22.5</v>
       </c>
       <c r="W9" s="3">
-        <f>V9*3</f>
+        <f t="shared" si="4"/>
         <v>67.5</v>
       </c>
       <c r="X9" s="4">
-        <f>O9/Z9</f>
+        <f t="shared" si="5"/>
         <v>1044594.5066666667</v>
       </c>
       <c r="Y9" s="4">
-        <f>O9/AA9</f>
+        <f t="shared" si="6"/>
         <v>3481981.6888888888</v>
       </c>
       <c r="Z9" s="3">
@@ -3464,31 +3464,31 @@
         <v>0.3</v>
       </c>
       <c r="S10" s="3">
-        <f>Z10*R10</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="T10" s="3">
-        <f>S10*3</f>
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="U10" s="5">
-        <f>AA10/Z10</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V10" s="3">
-        <f>Z10*U10</f>
+        <f t="shared" si="3"/>
         <v>33</v>
       </c>
       <c r="W10" s="3">
-        <f>V10*3</f>
+        <f t="shared" si="4"/>
         <v>99</v>
       </c>
       <c r="X10" s="4">
-        <f>O10/Z10</f>
+        <f t="shared" si="5"/>
         <v>1090311.6636363636</v>
       </c>
       <c r="Y10" s="4">
-        <f>O10/AA10</f>
+        <f t="shared" si="6"/>
         <v>3634372.2121212119</v>
       </c>
       <c r="Z10" s="3">
@@ -3623,31 +3623,31 @@
         <v>0.3</v>
       </c>
       <c r="S11" s="3">
-        <f>Z11*R11</f>
+        <f t="shared" si="0"/>
         <v>5.76</v>
       </c>
       <c r="T11" s="3">
-        <f>S11*3</f>
+        <f t="shared" si="1"/>
         <v>17.28</v>
       </c>
       <c r="U11" s="5">
-        <f>AA11/Z11</f>
+        <f t="shared" si="2"/>
         <v>0.31770833333333331</v>
       </c>
       <c r="V11" s="3">
-        <f>Z11*U11</f>
+        <f t="shared" si="3"/>
         <v>6.1</v>
       </c>
       <c r="W11" s="3">
-        <f>V11*3</f>
+        <f t="shared" si="4"/>
         <v>18.299999999999997</v>
       </c>
       <c r="X11" s="4">
-        <f>O11/Z11</f>
+        <f t="shared" si="5"/>
         <v>977532.88020833337</v>
       </c>
       <c r="Y11" s="4">
-        <f>O11/AA11</f>
+        <f t="shared" si="6"/>
         <v>3076824.8032786888</v>
       </c>
       <c r="Z11" s="3">
@@ -3782,31 +3782,31 @@
         <v>0.3</v>
       </c>
       <c r="S12" s="3">
-        <f>Z12*R12</f>
+        <f t="shared" si="0"/>
         <v>36.96</v>
       </c>
       <c r="T12" s="3">
-        <f>S12*3</f>
+        <f t="shared" si="1"/>
         <v>110.88</v>
       </c>
       <c r="U12" s="5">
-        <f>AA12/Z12</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V12" s="3">
-        <f>Z12*U12</f>
+        <f t="shared" si="3"/>
         <v>36.96</v>
       </c>
       <c r="W12" s="3">
-        <f>V12*3</f>
+        <f t="shared" si="4"/>
         <v>110.88</v>
       </c>
       <c r="X12" s="4">
-        <f>O12/Z12</f>
+        <f t="shared" si="5"/>
         <v>1290017.9886363635</v>
       </c>
       <c r="Y12" s="4">
-        <f>O12/AA12</f>
+        <f t="shared" si="6"/>
         <v>4300059.9621212119</v>
       </c>
       <c r="Z12" s="3">
@@ -3822,13 +3822,13 @@
         <v>158</v>
       </c>
       <c r="AD12" s="6">
-        <v>0.83500000000000019</v>
+        <v>0.84000000000000019</v>
       </c>
       <c r="AE12" s="6">
-        <v>0.7300000000000002</v>
+        <v>0.73500000000000021</v>
       </c>
       <c r="AF12" s="6">
-        <v>0.81400000000000017</v>
+        <v>0.81900000000000017</v>
       </c>
       <c r="AG12" s="6">
         <v>1</v>
@@ -3858,7 +3858,7 @@
         <v>1</v>
       </c>
       <c r="AP12" s="6">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="AQ12" s="6">
         <v>0.6</v>
@@ -3941,31 +3941,31 @@
         <v>0.3</v>
       </c>
       <c r="S13" s="3">
-        <f>Z13*R13</f>
+        <f t="shared" si="0"/>
         <v>136.70400000000001</v>
       </c>
       <c r="T13" s="3">
-        <f>S13*3</f>
+        <f t="shared" si="1"/>
         <v>410.11200000000002</v>
       </c>
       <c r="U13" s="5">
-        <f>AA13/Z13</f>
+        <f t="shared" si="2"/>
         <v>0.29999122191011235</v>
       </c>
       <c r="V13" s="3">
-        <f>Z13*U13</f>
+        <f t="shared" si="3"/>
         <v>136.69999999999999</v>
       </c>
       <c r="W13" s="3">
-        <f>V13*3</f>
+        <f t="shared" si="4"/>
         <v>410.09999999999997</v>
       </c>
       <c r="X13" s="4">
-        <f>O13/Z13</f>
+        <f t="shared" si="5"/>
         <v>923518.54634831462</v>
       </c>
       <c r="Y13" s="4">
-        <f>O13/AA13</f>
+        <f t="shared" si="6"/>
         <v>3078485.2318946598</v>
       </c>
       <c r="Z13" s="3">
@@ -3981,13 +3981,13 @@
         <v>30</v>
       </c>
       <c r="AD13" s="6">
-        <v>0.77000000000000024</v>
+        <v>0.75000000000000022</v>
       </c>
       <c r="AE13" s="6">
-        <v>0.6050000000000002</v>
+        <v>0.58500000000000019</v>
       </c>
       <c r="AF13" s="6">
-        <v>0.73700000000000032</v>
+        <v>0.7170000000000003</v>
       </c>
       <c r="AG13" s="6">
         <v>1</v>
@@ -4017,7 +4017,7 @@
         <v>0.8</v>
       </c>
       <c r="AP13" s="6">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AQ13" s="6">
         <v>0.8</v>
@@ -4100,31 +4100,31 @@
         <v>0.3</v>
       </c>
       <c r="S14" s="3">
-        <f>Z14*R14</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="T14" s="3">
-        <f>S14*3</f>
+        <f t="shared" si="1"/>
         <v>135</v>
       </c>
       <c r="U14" s="5">
-        <f>AA14/Z14</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V14" s="3">
-        <f>Z14*U14</f>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="W14" s="3">
-        <f>V14*3</f>
+        <f t="shared" si="4"/>
         <v>135</v>
       </c>
       <c r="X14" s="4">
-        <f>O14/Z14</f>
+        <f t="shared" si="5"/>
         <v>1102348.6546666666</v>
       </c>
       <c r="Y14" s="4">
-        <f>O14/AA14</f>
+        <f t="shared" si="6"/>
         <v>3674495.5155555555</v>
       </c>
       <c r="Z14" s="3">
@@ -4259,31 +4259,31 @@
         <v>0.3</v>
       </c>
       <c r="S15" s="3">
-        <f>Z15*R15</f>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="T15" s="3">
-        <f>S15*3</f>
+        <f t="shared" si="1"/>
         <v>153</v>
       </c>
       <c r="U15" s="5">
-        <f>AA15/Z15</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V15" s="3">
-        <f>Z15*U15</f>
+        <f t="shared" si="3"/>
         <v>51</v>
       </c>
       <c r="W15" s="3">
-        <f>V15*3</f>
+        <f t="shared" si="4"/>
         <v>153</v>
       </c>
       <c r="X15" s="4">
-        <f>O15/Z15</f>
+        <f t="shared" si="5"/>
         <v>1243209.5547058824</v>
       </c>
       <c r="Y15" s="4">
-        <f>O15/AA15</f>
+        <f t="shared" si="6"/>
         <v>4144031.849019608</v>
       </c>
       <c r="Z15" s="3">
@@ -4418,31 +4418,31 @@
         <v>0.3</v>
       </c>
       <c r="S16" s="3">
-        <f>Z16*R16</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="T16" s="3">
-        <f>S16*3</f>
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
       <c r="U16" s="5">
-        <f>AA16/Z16</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V16" s="3">
-        <f>Z16*U16</f>
+        <f t="shared" si="3"/>
         <v>36</v>
       </c>
       <c r="W16" s="3">
-        <f>V16*3</f>
+        <f t="shared" si="4"/>
         <v>108</v>
       </c>
       <c r="X16" s="4">
-        <f>O16/Z16</f>
+        <f t="shared" si="5"/>
         <v>1485070.3158333334</v>
       </c>
       <c r="Y16" s="4">
-        <f>O16/AA16</f>
+        <f t="shared" si="6"/>
         <v>4950234.3861111114</v>
       </c>
       <c r="Z16" s="3">
@@ -4577,31 +4577,31 @@
         <v>0.3</v>
       </c>
       <c r="S17" s="3">
-        <f>Z17*R17</f>
+        <f t="shared" si="0"/>
         <v>19.8</v>
       </c>
       <c r="T17" s="3">
-        <f>S17*3</f>
+        <f t="shared" si="1"/>
         <v>59.400000000000006</v>
       </c>
       <c r="U17" s="5">
-        <f>AA17/Z17</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V17" s="3">
-        <f>Z17*U17</f>
+        <f t="shared" si="3"/>
         <v>19.8</v>
       </c>
       <c r="W17" s="3">
-        <f>V17*3</f>
+        <f t="shared" si="4"/>
         <v>59.400000000000006</v>
       </c>
       <c r="X17" s="4">
-        <f>O17/Z17</f>
+        <f t="shared" si="5"/>
         <v>1491807.1409090909</v>
       </c>
       <c r="Y17" s="4">
-        <f>O17/AA17</f>
+        <f t="shared" si="6"/>
         <v>4972690.4696969697</v>
       </c>
       <c r="Z17" s="3">
@@ -4736,31 +4736,31 @@
         <v>0.3</v>
       </c>
       <c r="S18" s="3">
-        <f>Z18*R18</f>
+        <f t="shared" si="0"/>
         <v>29.46</v>
       </c>
       <c r="T18" s="3">
-        <f>S18*3</f>
+        <f t="shared" si="1"/>
         <v>88.38</v>
       </c>
       <c r="U18" s="5">
-        <f>AA18/Z18</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V18" s="3">
-        <f>Z18*U18</f>
+        <f t="shared" si="3"/>
         <v>29.46</v>
       </c>
       <c r="W18" s="3">
-        <f>V18*3</f>
+        <f t="shared" si="4"/>
         <v>88.38</v>
       </c>
       <c r="X18" s="4">
-        <f>O18/Z18</f>
+        <f t="shared" si="5"/>
         <v>923875.08044806519</v>
       </c>
       <c r="Y18" s="4">
-        <f>O18/AA18</f>
+        <f t="shared" si="6"/>
         <v>3079583.6014935505</v>
       </c>
       <c r="Z18" s="3">
@@ -4895,31 +4895,31 @@
         <v>0.3</v>
       </c>
       <c r="S19" s="3">
-        <f>Z19*R19</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="T19" s="3">
-        <f>S19*3</f>
+        <f t="shared" si="1"/>
         <v>270</v>
       </c>
       <c r="U19" s="5">
-        <f>AA19/Z19</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V19" s="3">
-        <f>Z19*U19</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="W19" s="3">
-        <f>V19*3</f>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="X19" s="4">
-        <f>O19/Z19</f>
+        <f t="shared" si="5"/>
         <v>1876953.09</v>
       </c>
       <c r="Y19" s="4">
-        <f>O19/AA19</f>
+        <f t="shared" si="6"/>
         <v>6256510.2999999998</v>
       </c>
       <c r="Z19" s="3">
@@ -5054,31 +5054,31 @@
         <v>0.3</v>
       </c>
       <c r="S20" s="3">
-        <f>Z20*R20</f>
+        <f t="shared" si="0"/>
         <v>21.599999999999998</v>
       </c>
       <c r="T20" s="3">
-        <f>S20*3</f>
+        <f t="shared" si="1"/>
         <v>64.8</v>
       </c>
       <c r="U20" s="5">
-        <f>AA20/Z20</f>
+        <f t="shared" si="2"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="V20" s="3">
-        <f>Z20*U20</f>
+        <f t="shared" si="3"/>
         <v>21.6</v>
       </c>
       <c r="W20" s="3">
-        <f>V20*3</f>
+        <f t="shared" si="4"/>
         <v>64.800000000000011</v>
       </c>
       <c r="X20" s="4">
-        <f>O20/Z20</f>
+        <f t="shared" si="5"/>
         <v>1549144.2083333333</v>
       </c>
       <c r="Y20" s="4">
-        <f>O20/AA20</f>
+        <f t="shared" si="6"/>
         <v>5163814.0277777771</v>
       </c>
       <c r="Z20" s="3">
@@ -5094,13 +5094,13 @@
         <v>28</v>
       </c>
       <c r="AD20" s="6">
-        <v>0.77000000000000024</v>
+        <v>0.75000000000000022</v>
       </c>
       <c r="AE20" s="6">
-        <v>0.77000000000000024</v>
+        <v>0.75000000000000022</v>
       </c>
       <c r="AF20" s="6">
-        <v>0.77000000000000024</v>
+        <v>0.75000000000000022</v>
       </c>
       <c r="AG20" s="6">
         <v>0.8</v>
@@ -5130,7 +5130,7 @@
         <v>0.8</v>
       </c>
       <c r="AP20" s="6">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AQ20" s="6">
         <v>0.5</v>
@@ -5213,31 +5213,31 @@
         <v>0.3</v>
       </c>
       <c r="S21" s="3">
-        <f>Z21*R21</f>
+        <f t="shared" si="0"/>
         <v>21.599999999999998</v>
       </c>
       <c r="T21" s="3">
-        <f>S21*3</f>
+        <f t="shared" si="1"/>
         <v>64.8</v>
       </c>
       <c r="U21" s="5">
-        <f>AA21/Z21</f>
+        <f t="shared" si="2"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="V21" s="3">
-        <f>Z21*U21</f>
+        <f t="shared" si="3"/>
         <v>21.6</v>
       </c>
       <c r="W21" s="3">
-        <f>V21*3</f>
+        <f t="shared" si="4"/>
         <v>64.800000000000011</v>
       </c>
       <c r="X21" s="4">
-        <f>O21/Z21</f>
+        <f t="shared" si="5"/>
         <v>1498517.5833333333</v>
       </c>
       <c r="Y21" s="4">
-        <f>O21/AA21</f>
+        <f t="shared" si="6"/>
         <v>4995058.611111111</v>
       </c>
       <c r="Z21" s="3">
@@ -5253,13 +5253,13 @@
         <v>47</v>
       </c>
       <c r="AD21" s="6">
-        <v>0.7300000000000002</v>
+        <v>0.74000000000000021</v>
       </c>
       <c r="AE21" s="6">
-        <v>0.63000000000000012</v>
+        <v>0.64000000000000012</v>
       </c>
       <c r="AF21" s="6">
-        <v>0.71000000000000019</v>
+        <v>0.7200000000000002</v>
       </c>
       <c r="AG21" s="6">
         <v>1</v>
@@ -5289,7 +5289,7 @@
         <v>1</v>
       </c>
       <c r="AP21" s="6">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AQ21" s="6">
         <v>0.5</v>
@@ -5372,31 +5372,31 @@
         <v>0.3</v>
       </c>
       <c r="S22" s="3">
-        <f>Z22*R22</f>
+        <f t="shared" si="0"/>
         <v>16.8</v>
       </c>
       <c r="T22" s="3">
-        <f>S22*3</f>
+        <f t="shared" si="1"/>
         <v>50.400000000000006</v>
       </c>
       <c r="U22" s="5">
-        <f>AA22/Z22</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V22" s="3">
-        <f>Z22*U22</f>
+        <f t="shared" si="3"/>
         <v>16.8</v>
       </c>
       <c r="W22" s="3">
-        <f>V22*3</f>
+        <f t="shared" si="4"/>
         <v>50.400000000000006</v>
       </c>
       <c r="X22" s="4">
-        <f>O22/Z22</f>
+        <f t="shared" si="5"/>
         <v>1535700.5892857143</v>
       </c>
       <c r="Y22" s="4">
-        <f>O22/AA22</f>
+        <f t="shared" si="6"/>
         <v>5119001.9642857136</v>
       </c>
       <c r="Z22" s="3">
@@ -5412,13 +5412,13 @@
         <v>49</v>
       </c>
       <c r="AD22" s="6">
+        <v>0.7200000000000002</v>
+      </c>
+      <c r="AE22" s="6">
+        <v>0.67000000000000015</v>
+      </c>
+      <c r="AF22" s="6">
         <v>0.71000000000000019</v>
-      </c>
-      <c r="AE22" s="6">
-        <v>0.66000000000000014</v>
-      </c>
-      <c r="AF22" s="6">
-        <v>0.70000000000000018</v>
       </c>
       <c r="AG22" s="6">
         <v>1</v>
@@ -5448,7 +5448,7 @@
         <v>1</v>
       </c>
       <c r="AP22" s="6">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AQ22" s="6">
         <v>0.5</v>
@@ -5531,31 +5531,31 @@
         <v>0.3</v>
       </c>
       <c r="S23" s="3">
-        <f>Z23*R23</f>
+        <f t="shared" si="0"/>
         <v>23.4</v>
       </c>
       <c r="T23" s="3">
-        <f>S23*3</f>
+        <f t="shared" si="1"/>
         <v>70.199999999999989</v>
       </c>
       <c r="U23" s="5">
-        <f>AA23/Z23</f>
+        <f t="shared" si="2"/>
         <v>0.32935897435897438</v>
       </c>
       <c r="V23" s="3">
-        <f>Z23*U23</f>
+        <f t="shared" si="3"/>
         <v>25.69</v>
       </c>
       <c r="W23" s="3">
-        <f>V23*3</f>
+        <f t="shared" si="4"/>
         <v>77.070000000000007</v>
       </c>
       <c r="X23" s="4">
-        <f>O23/Z23</f>
+        <f t="shared" si="5"/>
         <v>1440397.7307692308</v>
       </c>
       <c r="Y23" s="4">
-        <f>O23/AA23</f>
+        <f t="shared" si="6"/>
         <v>4373336.8236667961</v>
       </c>
       <c r="Z23" s="3">
@@ -5690,31 +5690,31 @@
         <v>0.3</v>
       </c>
       <c r="S24" s="3">
-        <f>Z24*R24</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="T24" s="3">
-        <f>S24*3</f>
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
       <c r="U24" s="5">
-        <f>AA24/Z24</f>
+        <f t="shared" si="2"/>
         <v>0.34083333333333332</v>
       </c>
       <c r="V24" s="3">
-        <f>Z24*U24</f>
+        <f t="shared" si="3"/>
         <v>40.9</v>
       </c>
       <c r="W24" s="3">
-        <f>V24*3</f>
+        <f t="shared" si="4"/>
         <v>122.69999999999999</v>
       </c>
       <c r="X24" s="4">
-        <f>O24/Z24</f>
+        <f t="shared" si="5"/>
         <v>955097.63250000007</v>
       </c>
       <c r="Y24" s="4">
-        <f>O24/AA24</f>
+        <f t="shared" si="6"/>
         <v>2802242.4425427876</v>
       </c>
       <c r="Z24" s="3">
@@ -5849,31 +5849,31 @@
         <v>0.3</v>
       </c>
       <c r="S25" s="3">
-        <f>Z25*R25</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="T25" s="3">
-        <f>S25*3</f>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="U25" s="5">
-        <f>AA25/Z25</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V25" s="3">
-        <f>Z25*U25</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="W25" s="3">
-        <f>V25*3</f>
+        <f t="shared" si="4"/>
         <v>90</v>
       </c>
       <c r="X25" s="4">
-        <f>O25/Z25</f>
+        <f t="shared" si="5"/>
         <v>985648.28</v>
       </c>
       <c r="Y25" s="4">
-        <f>O25/AA25</f>
+        <f t="shared" si="6"/>
         <v>3285494.2666666666</v>
       </c>
       <c r="Z25" s="3">
@@ -5889,13 +5889,13 @@
         <v>223</v>
       </c>
       <c r="AD25" s="6">
-        <v>0.81000000000000028</v>
+        <v>0.79000000000000026</v>
       </c>
       <c r="AE25" s="6">
-        <v>0.55500000000000005</v>
+        <v>0.53500000000000014</v>
       </c>
       <c r="AF25" s="6">
-        <v>0.75900000000000023</v>
+        <v>0.73900000000000032</v>
       </c>
       <c r="AG25" s="6">
         <v>0.9</v>
@@ -5925,7 +5925,7 @@
         <v>0.8</v>
       </c>
       <c r="AP25" s="6">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AQ25" s="6">
         <v>1</v>
@@ -6008,31 +6008,31 @@
         <v>0.3</v>
       </c>
       <c r="S26" s="3">
-        <f>Z26*R26</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="T26" s="3">
-        <f>S26*3</f>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="U26" s="5">
-        <f>AA26/Z26</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V26" s="3">
-        <f>Z26*U26</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="W26" s="3">
-        <f>V26*3</f>
+        <f t="shared" si="4"/>
         <v>90</v>
       </c>
       <c r="X26" s="4">
-        <f>O26/Z26</f>
+        <f t="shared" si="5"/>
         <v>999328.58</v>
       </c>
       <c r="Y26" s="4">
-        <f>O26/AA26</f>
+        <f t="shared" si="6"/>
         <v>3331095.2666666666</v>
       </c>
       <c r="Z26" s="3">
@@ -6167,31 +6167,31 @@
         <v>0.3</v>
       </c>
       <c r="S27" s="3">
-        <f>Z27*R27</f>
+        <f t="shared" si="0"/>
         <v>51.3</v>
       </c>
       <c r="T27" s="3">
-        <f>S27*3</f>
+        <f t="shared" si="1"/>
         <v>153.89999999999998</v>
       </c>
       <c r="U27" s="5">
-        <f>AA27/Z27</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V27" s="3">
-        <f>Z27*U27</f>
+        <f t="shared" si="3"/>
         <v>51.3</v>
       </c>
       <c r="W27" s="3">
-        <f>V27*3</f>
+        <f t="shared" si="4"/>
         <v>153.89999999999998</v>
       </c>
       <c r="X27" s="4">
-        <f>O27/Z27</f>
+        <f t="shared" si="5"/>
         <v>1862193.350877193</v>
       </c>
       <c r="Y27" s="4">
-        <f>O27/AA27</f>
+        <f t="shared" si="6"/>
         <v>6207311.1695906436</v>
       </c>
       <c r="Z27" s="3">
@@ -6326,31 +6326,31 @@
         <v>0.3</v>
       </c>
       <c r="S28" s="3">
-        <f>Z28*R28</f>
+        <f t="shared" si="0"/>
         <v>153</v>
       </c>
       <c r="T28" s="3">
-        <f>S28*3</f>
+        <f t="shared" si="1"/>
         <v>459</v>
       </c>
       <c r="U28" s="5">
-        <f>AA28/Z28</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V28" s="3">
-        <f>Z28*U28</f>
+        <f t="shared" si="3"/>
         <v>153</v>
       </c>
       <c r="W28" s="3">
-        <f>V28*3</f>
+        <f t="shared" si="4"/>
         <v>459</v>
       </c>
       <c r="X28" s="4">
-        <f>O28/Z28</f>
+        <f t="shared" si="5"/>
         <v>1744882.0290196077</v>
       </c>
       <c r="Y28" s="4">
-        <f>O28/AA28</f>
+        <f t="shared" si="6"/>
         <v>5816273.430065359</v>
       </c>
       <c r="Z28" s="3">
@@ -6485,31 +6485,31 @@
         <v>0.3</v>
       </c>
       <c r="S29" s="3">
-        <f>Z29*R29</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="T29" s="3">
-        <f>S29*3</f>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="U29" s="5">
-        <f>AA29/Z29</f>
+        <f t="shared" si="2"/>
         <v>0.31428571428571428</v>
       </c>
       <c r="V29" s="3">
-        <f>Z29*U29</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="W29" s="3">
-        <f>V29*3</f>
+        <f t="shared" si="4"/>
         <v>66</v>
       </c>
       <c r="X29" s="4">
-        <f>O29/Z29</f>
+        <f t="shared" si="5"/>
         <v>955539.85714285716</v>
       </c>
       <c r="Y29" s="4">
-        <f>O29/AA29</f>
+        <f t="shared" si="6"/>
         <v>3040354.0909090908</v>
       </c>
       <c r="Z29" s="3">
@@ -6644,31 +6644,31 @@
         <v>0.3</v>
       </c>
       <c r="S30" s="3">
-        <f>Z30*R30</f>
+        <f t="shared" si="0"/>
         <v>22.5</v>
       </c>
       <c r="T30" s="3">
-        <f>S30*3</f>
+        <f t="shared" si="1"/>
         <v>67.5</v>
       </c>
       <c r="U30" s="5">
-        <f>AA30/Z30</f>
+        <f t="shared" si="2"/>
         <v>0.34133333333333338</v>
       </c>
       <c r="V30" s="3">
-        <f>Z30*U30</f>
+        <f t="shared" si="3"/>
         <v>25.600000000000005</v>
       </c>
       <c r="W30" s="3">
-        <f>V30*3</f>
+        <f t="shared" si="4"/>
         <v>76.800000000000011</v>
       </c>
       <c r="X30" s="4">
-        <f>O30/Z30</f>
+        <f t="shared" si="5"/>
         <v>1147822.7426666666</v>
       </c>
       <c r="Y30" s="4">
-        <f>O30/AA30</f>
+        <f t="shared" si="6"/>
         <v>3362761.94140625</v>
       </c>
       <c r="Z30" s="3">
@@ -6684,13 +6684,13 @@
         <v>32</v>
       </c>
       <c r="AD30" s="6">
-        <v>0.79000000000000026</v>
+        <v>0.82000000000000028</v>
       </c>
       <c r="AE30" s="6">
-        <v>0.67000000000000015</v>
+        <v>0.70000000000000018</v>
       </c>
       <c r="AF30" s="6">
-        <v>0.76600000000000024</v>
+        <v>0.79600000000000026</v>
       </c>
       <c r="AG30" s="6">
         <v>1</v>
@@ -6720,7 +6720,7 @@
         <v>1</v>
       </c>
       <c r="AP30" s="6">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AQ30" s="6">
         <v>0.7</v>
@@ -6803,31 +6803,31 @@
         <v>0.3</v>
       </c>
       <c r="S31" s="3">
-        <f>Z31*R31</f>
+        <f t="shared" si="0"/>
         <v>42.42</v>
       </c>
       <c r="T31" s="3">
-        <f>S31*3</f>
+        <f t="shared" si="1"/>
         <v>127.26</v>
       </c>
       <c r="U31" s="5">
-        <f>AA31/Z31</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V31" s="3">
-        <f>Z31*U31</f>
+        <f t="shared" si="3"/>
         <v>42.42</v>
       </c>
       <c r="W31" s="3">
-        <f>V31*3</f>
+        <f t="shared" si="4"/>
         <v>127.26</v>
       </c>
       <c r="X31" s="4">
-        <f>O31/Z31</f>
+        <f t="shared" si="5"/>
         <v>1040124.3203677511</v>
       </c>
       <c r="Y31" s="4">
-        <f>O31/AA31</f>
+        <f t="shared" si="6"/>
         <v>3467081.0678925035</v>
       </c>
       <c r="Z31" s="3">
@@ -6962,31 +6962,31 @@
         <v>0.3</v>
       </c>
       <c r="S32" s="3">
-        <f>Z32*R32</f>
+        <f t="shared" si="0"/>
         <v>101.7</v>
       </c>
       <c r="T32" s="3">
-        <f>S32*3</f>
+        <f t="shared" si="1"/>
         <v>305.10000000000002</v>
       </c>
       <c r="U32" s="5">
-        <f>AA32/Z32</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V32" s="3">
-        <f>Z32*U32</f>
+        <f t="shared" si="3"/>
         <v>101.7</v>
       </c>
       <c r="W32" s="3">
-        <f>V32*3</f>
+        <f t="shared" si="4"/>
         <v>305.10000000000002</v>
       </c>
       <c r="X32" s="4" t="e">
-        <f>O32/Z32</f>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="Y32" s="4" t="e">
-        <f>O32/AA32</f>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="Z32" s="3">
@@ -7121,31 +7121,31 @@
         <v>0.3</v>
       </c>
       <c r="S33" s="3">
-        <f>Z33*R33</f>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="T33" s="3">
-        <f>S33*3</f>
+        <f t="shared" si="1"/>
         <v>162</v>
       </c>
       <c r="U33" s="5">
-        <f>AA33/Z33</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V33" s="3">
-        <f>Z33*U33</f>
+        <f t="shared" si="3"/>
         <v>54</v>
       </c>
       <c r="W33" s="3">
-        <f>V33*3</f>
+        <f t="shared" si="4"/>
         <v>162</v>
       </c>
       <c r="X33" s="4">
-        <f>O33/Z33</f>
+        <f t="shared" si="5"/>
         <v>5140615.7388888886</v>
       </c>
       <c r="Y33" s="4">
-        <f>O33/AA33</f>
+        <f t="shared" si="6"/>
         <v>17135385.796296295</v>
       </c>
       <c r="Z33" s="3">
@@ -7280,31 +7280,31 @@
         <v>0.3</v>
       </c>
       <c r="S34" s="3">
-        <f>Z34*R34</f>
+        <f t="shared" si="0"/>
         <v>101.7</v>
       </c>
       <c r="T34" s="3">
-        <f>S34*3</f>
+        <f t="shared" si="1"/>
         <v>305.10000000000002</v>
       </c>
       <c r="U34" s="5">
-        <f>AA34/Z34</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V34" s="3">
-        <f>Z34*U34</f>
+        <f t="shared" si="3"/>
         <v>101.7</v>
       </c>
       <c r="W34" s="3">
-        <f>V34*3</f>
+        <f t="shared" si="4"/>
         <v>305.10000000000002</v>
       </c>
       <c r="X34" s="4" t="e">
-        <f>O34/Z34</f>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="Y34" s="4" t="e">
-        <f>O34/AA34</f>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="Z34" s="3">
@@ -7439,31 +7439,31 @@
         <v>0.3</v>
       </c>
       <c r="S35" s="9">
-        <f>Z35*R35</f>
+        <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
       <c r="T35" s="9">
-        <f>S35*3</f>
+        <f t="shared" si="1"/>
         <v>112.5</v>
       </c>
       <c r="U35" s="10">
-        <f>AA35/Z35</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V35" s="9">
-        <f>Z35*U35</f>
+        <f t="shared" si="3"/>
         <v>37.5</v>
       </c>
       <c r="W35" s="9">
-        <f>V35*3</f>
+        <f t="shared" si="4"/>
         <v>112.5</v>
       </c>
       <c r="X35" s="11">
-        <f>O35/Z35</f>
+        <f t="shared" si="5"/>
         <v>1288848.5736</v>
       </c>
       <c r="Y35" s="11">
-        <f>O35/AA35</f>
+        <f t="shared" si="6"/>
         <v>4296161.9119999995</v>
       </c>
       <c r="Z35" s="9">
@@ -7479,13 +7479,13 @@
         <v>20</v>
       </c>
       <c r="AD35" s="6">
-        <v>0.8450000000000002</v>
+        <v>0.87500000000000022</v>
       </c>
       <c r="AE35" s="6">
-        <v>0.77000000000000024</v>
+        <v>0.80000000000000027</v>
       </c>
       <c r="AF35" s="6">
-        <v>0.83000000000000018</v>
+        <v>0.86000000000000021</v>
       </c>
       <c r="AG35" s="6">
         <v>1</v>
@@ -7515,7 +7515,7 @@
         <v>1</v>
       </c>
       <c r="AP35" s="6">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AQ35" s="6">
         <v>0.9</v>
@@ -7598,31 +7598,31 @@
         <v>0.3</v>
       </c>
       <c r="S36" s="3">
-        <f>Z36*R36</f>
+        <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="T36" s="3">
-        <f>S36*3</f>
+        <f t="shared" si="1"/>
         <v>243</v>
       </c>
       <c r="U36" s="5">
-        <f>AA36/Z36</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V36" s="3">
-        <f>Z36*U36</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="W36" s="3">
-        <f>V36*3</f>
+        <f t="shared" si="4"/>
         <v>243</v>
       </c>
       <c r="X36" s="4" t="e">
-        <f>O36/Z36</f>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="Y36" s="4" t="e">
-        <f>O36/AA36</f>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="Z36" s="14">
@@ -7757,31 +7757,31 @@
         <v>0.3</v>
       </c>
       <c r="S37" s="3">
-        <f>Z37*R37</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="T37" s="3">
-        <f>S37*3</f>
+        <f t="shared" si="1"/>
         <v>270</v>
       </c>
       <c r="U37" s="5">
-        <f>AA37/Z37</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V37" s="3">
-        <f>Z37*U37</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="W37" s="3">
-        <f>V37*3</f>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="X37" s="4" t="e">
-        <f>O37/Z37</f>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="Y37" s="4" t="e">
-        <f>O37/AA37</f>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="Z37" s="14">
@@ -7916,31 +7916,31 @@
         <v>0.3</v>
       </c>
       <c r="S38" s="3">
-        <f>Z38*R38</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="T38" s="3">
-        <f>S38*3</f>
+        <f t="shared" si="1"/>
         <v>270</v>
       </c>
       <c r="U38" s="5">
-        <f>AA38/Z38</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V38" s="3">
-        <f>Z38*U38</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="W38" s="3">
-        <f>V38*3</f>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="X38" s="4" t="e">
-        <f>O38/Z38</f>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="Y38" s="4" t="e">
-        <f>O38/AA38</f>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="Z38" s="14">
@@ -8075,31 +8075,31 @@
         <v>0.3</v>
       </c>
       <c r="S39" s="3">
-        <f>Z39*R39</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="T39" s="3">
-        <f>S39*3</f>
+        <f t="shared" si="1"/>
         <v>270</v>
       </c>
       <c r="U39" s="5">
-        <f>AA39/Z39</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V39" s="3">
-        <f>Z39*U39</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="W39" s="3">
-        <f>V39*3</f>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="X39" s="4" t="e">
-        <f>O39/Z39</f>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="Y39" s="4" t="e">
-        <f>O39/AA39</f>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="Z39" s="14">
@@ -8234,31 +8234,31 @@
         <v>0.3</v>
       </c>
       <c r="S40" s="3">
-        <f>Z40*R40</f>
+        <f t="shared" si="0"/>
         <v>174</v>
       </c>
       <c r="T40" s="3">
-        <f>S40*3</f>
+        <f t="shared" si="1"/>
         <v>522</v>
       </c>
       <c r="U40" s="5">
-        <f>AA40/Z40</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V40" s="3">
-        <f>Z40*U40</f>
+        <f t="shared" si="3"/>
         <v>174</v>
       </c>
       <c r="W40" s="3">
-        <f>V40*3</f>
+        <f t="shared" si="4"/>
         <v>522</v>
       </c>
       <c r="X40" s="4" t="e">
-        <f>O40/Z40</f>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="Y40" s="4" t="e">
-        <f>O40/AA40</f>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="Z40" s="18">
@@ -8393,31 +8393,31 @@
         <v>0.3</v>
       </c>
       <c r="S41" s="3">
-        <f>Z41*R41</f>
+        <f t="shared" si="0"/>
         <v>35.1</v>
       </c>
       <c r="T41" s="3">
-        <f>S41*3</f>
+        <f t="shared" si="1"/>
         <v>105.30000000000001</v>
       </c>
       <c r="U41" s="5">
-        <f>AA41/Z41</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="V41" s="3">
-        <f>Z41*U41</f>
+        <f t="shared" si="3"/>
         <v>35.1</v>
       </c>
       <c r="W41" s="3">
-        <f>V41*3</f>
+        <f t="shared" si="4"/>
         <v>105.30000000000001</v>
       </c>
       <c r="X41" s="4" t="e">
-        <f>O41/Z41</f>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="Y41" s="4" t="e">
-        <f>O41/AA41</f>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="Z41" s="18">
@@ -8602,11 +8602,7 @@
       <c r="P53" s="51"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AX1" xr:uid="{782B78D9-47D9-4EBC-8BEA-A91BF1F0B98F}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AX41">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:AX1" xr:uid="{782B78D9-47D9-4EBC-8BEA-A91BF1F0B98F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="597" r:id="rId1"/>
 </worksheet>
